--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA194"/>
+  <dimension ref="A1:AA203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12631,7 +12631,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>106004</v>
+        <v>106020</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -12639,21 +12639,21 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>99069512</v>
+        <v>194876138</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ADP160</t>
+          <t>SSU030</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ADP160CF</t>
+          <t>SSU030CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ADP160CF</t>
+          <t>SSU030CF</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12663,24 +12663,24 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>MOCASSIM</t>
+          <t>TENIS</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>CLASSICO</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>439.9</v>
+        <v>299.9</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>148.03</v>
+        <v>99.92</v>
       </c>
       <c r="M181" t="n">
         <v>1</v>
@@ -12692,30 +12692,27 @@
         <v>4</v>
       </c>
       <c r="T181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V181" t="n">
         <v>4</v>
       </c>
       <c r="W181" t="n">
-        <v>3</v>
-      </c>
-      <c r="X181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z181" t="n">
         <v>24</v>
       </c>
       <c r="AA181" t="n">
-        <v>3552.72</v>
+        <v>2398.08</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>106004</v>
+        <v>106020</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -12723,21 +12720,21 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>56456539</v>
+        <v>151143141</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ASF950</t>
+          <t>SSU030</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ASF950TP</t>
+          <t>SSU030OW</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ASF950TP</t>
+          <t>SSU030OW</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -12747,24 +12744,24 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>SANDALIA</t>
+          <t>TENIS</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>INVERNO</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>399.9</v>
+        <v>299.9</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>124.86</v>
+        <v>99.92</v>
       </c>
       <c r="M182" t="n">
         <v>1</v>
@@ -12773,33 +12770,30 @@
         <v>2</v>
       </c>
       <c r="S182" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T182" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U182" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V182" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W182" t="n">
-        <v>3</v>
-      </c>
-      <c r="X182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z182" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AA182" t="n">
-        <v>2996.64</v>
+        <v>3597.12</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>106004</v>
+        <v>106020</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -12807,36 +12801,36 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>63032743</v>
+        <v>151143142</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PRAD44</t>
+          <t>SSU030</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PRAD44TP</t>
+          <t>SSU030PT</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>PRAD44TP</t>
+          <t>SSU030PT</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FEMININO</t>
+          <t>MASCULINO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>SANDALIA BIRKEN</t>
+          <t>TENIS</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>CLASSICO</t>
+          <t>INVERNO</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -12844,43 +12838,43 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>119.46</v>
+        <v>99.92</v>
       </c>
       <c r="M183" t="n">
         <v>1</v>
       </c>
-      <c r="N183" t="n">
-        <v>2</v>
-      </c>
-      <c r="O183" t="n">
+      <c r="R183" t="n">
+        <v>2</v>
+      </c>
+      <c r="S183" t="n">
         <v>6</v>
       </c>
-      <c r="P183" t="n">
+      <c r="T183" t="n">
         <v>10</v>
       </c>
-      <c r="Q183" t="n">
+      <c r="U183" t="n">
         <v>8</v>
       </c>
-      <c r="R183" t="n">
+      <c r="V183" t="n">
         <v>6</v>
       </c>
-      <c r="S183" t="n">
+      <c r="W183" t="n">
         <v>4</v>
       </c>
       <c r="Z183" t="n">
         <v>36</v>
       </c>
       <c r="AA183" t="n">
-        <v>4300.56</v>
+        <v>3597.12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>106004</v>
+        <v>106020</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -12888,21 +12882,21 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>62522833</v>
+        <v>212925785</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SLB034</t>
+          <t>SSU119</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SLB034PT</t>
+          <t>SSU119TN</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SLB034PT</t>
+          <t>SSU119TN</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -12921,15 +12915,15 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>599.9</v>
+        <v>299.9</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>200.54</v>
+        <v>99.92</v>
       </c>
       <c r="M184" t="n">
         <v>1</v>
@@ -12959,12 +12953,12 @@
         <v>18</v>
       </c>
       <c r="AA184" t="n">
-        <v>3609.72</v>
+        <v>1798.56</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>106004</v>
+        <v>106016</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -12972,83 +12966,62 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>164567877</v>
+        <v>226773781</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>SLB034</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>SLB034TN</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>SLB034TN</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>MASCULINO</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>TENIS</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>INVERNO</t>
-        </is>
-      </c>
-      <c r="J185" t="n">
-        <v>599.9</v>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>PAB078CF</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>PAB078CF</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="n"/>
+      <c r="H185" s="2" t="n"/>
+      <c r="I185" s="2" t="n"/>
+      <c r="J185" s="2" t="n"/>
+      <c r="K185" s="2" t="n"/>
       <c r="L185" t="n">
-        <v>200.54</v>
+        <v>149.31</v>
       </c>
       <c r="M185" t="n">
         <v>1</v>
       </c>
+      <c r="N185" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" t="n">
+        <v>3</v>
+      </c>
+      <c r="P185" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>4</v>
+      </c>
       <c r="R185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S185" t="n">
-        <v>3</v>
-      </c>
-      <c r="T185" t="n">
-        <v>4</v>
-      </c>
-      <c r="U185" t="n">
-        <v>4</v>
-      </c>
-      <c r="V185" t="n">
-        <v>3</v>
-      </c>
-      <c r="W185" t="n">
-        <v>2</v>
-      </c>
-      <c r="X185" t="n">
         <v>1</v>
       </c>
       <c r="Z185" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA185" t="n">
-        <v>3609.72</v>
+        <v>2239.65</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>106004</v>
+        <v>106016</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -13056,83 +13029,62 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>209207783</v>
+        <v>227869440</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>SVZ500</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>SVZ500CF</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>SVZ500CF</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>MASCULINO</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>TENIS</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>CLASSICO</t>
-        </is>
-      </c>
-      <c r="J186" t="n">
-        <v>539.9</v>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="n"/>
+      <c r="H186" s="2" t="n"/>
+      <c r="I186" s="2" t="n"/>
+      <c r="J186" s="2" t="n"/>
+      <c r="K186" s="2" t="n"/>
       <c r="L186" t="n">
-        <v>174.65</v>
+        <v>149.31</v>
       </c>
       <c r="M186" t="n">
         <v>1</v>
       </c>
+      <c r="N186" t="n">
+        <v>1</v>
+      </c>
+      <c r="O186" t="n">
+        <v>2</v>
+      </c>
+      <c r="P186" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>3</v>
+      </c>
       <c r="R186" t="n">
         <v>2</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
-      </c>
-      <c r="T186" t="n">
-        <v>5</v>
-      </c>
-      <c r="U186" t="n">
-        <v>5</v>
-      </c>
-      <c r="V186" t="n">
-        <v>4</v>
-      </c>
-      <c r="W186" t="n">
-        <v>3</v>
-      </c>
-      <c r="X186" t="n">
         <v>1</v>
       </c>
       <c r="Z186" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AA186" t="n">
-        <v>4191.6</v>
+        <v>1791.72</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>106004</v>
+        <v>106016</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -13140,21 +13092,21 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>226799440</v>
+        <v>226799259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>WSCR54</t>
+          <t>WCL202</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>WSCR54BC</t>
+          <t>WCL202CA</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>WSCR54BC</t>
+          <t>WCL202CA</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -13163,7 +13115,7 @@
       <c r="J187" s="2" t="n"/>
       <c r="K187" s="2" t="n"/>
       <c r="L187" t="n">
-        <v>211.68</v>
+        <v>124.7</v>
       </c>
       <c r="M187" t="n">
         <v>1</v>
@@ -13172,13 +13124,13 @@
         <v>1</v>
       </c>
       <c r="O187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R187" t="n">
         <v>2</v>
@@ -13187,15 +13139,15 @@
         <v>1</v>
       </c>
       <c r="Z187" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA187" t="n">
-        <v>3175.2</v>
+        <v>1496.4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>106004</v>
+        <v>106016</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -13203,21 +13155,21 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>226799445</v>
+        <v>226799260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>WSCR57</t>
+          <t>WCL203</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>WSCR57BI</t>
+          <t>WCL203CF</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>WSCR57BI</t>
+          <t>WCL203CF</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -13226,7 +13178,7 @@
       <c r="J188" s="2" t="n"/>
       <c r="K188" s="2" t="n"/>
       <c r="L188" t="n">
-        <v>159.25</v>
+        <v>145.33</v>
       </c>
       <c r="M188" t="n">
         <v>1</v>
@@ -13253,12 +13205,12 @@
         <v>18</v>
       </c>
       <c r="AA188" t="n">
-        <v>2866.5</v>
+        <v>2615.94</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>106004</v>
+        <v>106016</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -13266,21 +13218,21 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>226799459</v>
+        <v>226799261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>WSCR89</t>
+          <t>WCL204</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>WSCR89TN</t>
+          <t>WCL204CA</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>WSCR89TN</t>
+          <t>WCL204CA</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -13289,7 +13241,7 @@
       <c r="J189" s="2" t="n"/>
       <c r="K189" s="2" t="n"/>
       <c r="L189" t="n">
-        <v>161.58</v>
+        <v>154.12</v>
       </c>
       <c r="M189" t="n">
         <v>1</v>
@@ -13316,12 +13268,12 @@
         <v>18</v>
       </c>
       <c r="AA189" t="n">
-        <v>2908.44</v>
+        <v>2774.16</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>106006</v>
+        <v>106004</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -13329,56 +13281,83 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>226772776</v>
+        <v>99069512</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ASF182</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>ASF182MM</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>ASF182MM</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="n"/>
-      <c r="H190" s="2" t="n"/>
-      <c r="I190" s="2" t="n"/>
-      <c r="J190" s="2" t="n"/>
-      <c r="K190" s="2" t="n"/>
+          <t>ADP160</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>ADP160CF</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ADP160CF</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="L190" t="n">
-        <v>64.34999999999999</v>
+        <v>148.03</v>
       </c>
       <c r="M190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>4</v>
+      <c r="R190" t="n">
+        <v>2</v>
       </c>
       <c r="S190" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="T190" t="n">
+        <v>5</v>
       </c>
       <c r="U190" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="V190" t="n">
+        <v>4</v>
       </c>
       <c r="W190" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="X190" t="n">
+        <v>1</v>
       </c>
       <c r="Z190" t="n">
         <v>24</v>
       </c>
       <c r="AA190" t="n">
-        <v>1544.4</v>
+        <v>3552.72</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>106006</v>
+        <v>106004</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -13386,21 +13365,21 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1213706</v>
+        <v>56456539</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ASF182</t>
+          <t>ASF950</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ASF182PT</t>
+          <t>ASF950TP</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ASF182PT</t>
+          <t>ASF950TP</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -13415,11 +13394,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>CLASSICO</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>199.9</v>
+        <v>399.9</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -13427,33 +13406,42 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>64.34999999999999</v>
+        <v>124.86</v>
       </c>
       <c r="M191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>4</v>
+      <c r="R191" t="n">
+        <v>2</v>
       </c>
       <c r="S191" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="T191" t="n">
+        <v>5</v>
       </c>
       <c r="U191" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="V191" t="n">
+        <v>4</v>
       </c>
       <c r="W191" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="X191" t="n">
+        <v>1</v>
       </c>
       <c r="Z191" t="n">
         <v>24</v>
       </c>
       <c r="AA191" t="n">
-        <v>1544.4</v>
+        <v>2996.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>106017</v>
+        <v>106004</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -13461,21 +13449,21 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>156352241</v>
+        <v>63032743</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>PABR56</t>
+          <t>PRAD44</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PABR56CM</t>
+          <t>PRAD44TP</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PABR56CM</t>
+          <t>PRAD44TP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -13485,7 +13473,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ANABELA</t>
+          <t>SANDALIA BIRKEN</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -13502,7 +13490,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>121.28</v>
+        <v>119.46</v>
       </c>
       <c r="M192" t="n">
         <v>1</v>
@@ -13511,30 +13499,30 @@
         <v>2</v>
       </c>
       <c r="O192" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P192" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q192" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R192" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S192" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z192" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AA192" t="n">
-        <v>2183.04</v>
+        <v>4300.56</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>106017</v>
+        <v>106004</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -13542,31 +13530,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>156352242</v>
+        <v>62522833</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>PABR56</t>
+          <t>SLB034</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PABR56MH</t>
+          <t>SLB034PT</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>PABR56MH</t>
+          <t>SLB034PT</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>FEMININO</t>
+          <t>MASCULINO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>ANABELA</t>
+          <t>TENIS</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -13575,7 +13563,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>299.9</v>
+        <v>599.9</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -13583,39 +13571,42 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>121.28</v>
+        <v>200.54</v>
       </c>
       <c r="M193" t="n">
         <v>1</v>
       </c>
-      <c r="N193" t="n">
-        <v>2</v>
-      </c>
-      <c r="O193" t="n">
-        <v>3</v>
-      </c>
-      <c r="P193" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>4</v>
-      </c>
       <c r="R193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S193" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="T193" t="n">
+        <v>4</v>
+      </c>
+      <c r="U193" t="n">
+        <v>4</v>
+      </c>
+      <c r="V193" t="n">
+        <v>3</v>
+      </c>
+      <c r="W193" t="n">
+        <v>2</v>
+      </c>
+      <c r="X193" t="n">
+        <v>1</v>
       </c>
       <c r="Z193" t="n">
         <v>18</v>
       </c>
       <c r="AA193" t="n">
-        <v>2183.04</v>
+        <v>3609.72</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>106017</v>
+        <v>106004</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -13623,56 +13614,707 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>226773817</v>
+        <v>164567877</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>PABR80</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>PABR80FD</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>PABR80FD</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="n"/>
-      <c r="H194" s="2" t="n"/>
-      <c r="I194" s="2" t="n"/>
-      <c r="J194" s="2" t="n"/>
-      <c r="K194" s="2" t="n"/>
+          <t>SLB034</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>SLB034TN</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>SLB034TN</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="L194" t="n">
-        <v>142.1</v>
+        <v>200.54</v>
       </c>
       <c r="M194" t="n">
         <v>1</v>
       </c>
-      <c r="N194" t="n">
-        <v>2</v>
-      </c>
-      <c r="O194" t="n">
-        <v>3</v>
-      </c>
-      <c r="P194" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>4</v>
-      </c>
       <c r="R194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S194" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="T194" t="n">
+        <v>4</v>
+      </c>
+      <c r="U194" t="n">
+        <v>4</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3</v>
+      </c>
+      <c r="W194" t="n">
+        <v>2</v>
+      </c>
+      <c r="X194" t="n">
+        <v>1</v>
       </c>
       <c r="Z194" t="n">
         <v>18</v>
       </c>
       <c r="AA194" t="n">
+        <v>3609.72</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>106004</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>209207783</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SVZ500</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SVZ500CF</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SVZ500CF</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>539.9</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>174.65</v>
+      </c>
+      <c r="M195" t="n">
+        <v>1</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2</v>
+      </c>
+      <c r="S195" t="n">
+        <v>4</v>
+      </c>
+      <c r="T195" t="n">
+        <v>5</v>
+      </c>
+      <c r="U195" t="n">
+        <v>5</v>
+      </c>
+      <c r="V195" t="n">
+        <v>4</v>
+      </c>
+      <c r="W195" t="n">
+        <v>3</v>
+      </c>
+      <c r="X195" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>4191.6</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>106004</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>226799440</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>WSCR54</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="n"/>
+      <c r="H196" s="2" t="n"/>
+      <c r="I196" s="2" t="n"/>
+      <c r="J196" s="2" t="n"/>
+      <c r="K196" s="2" t="n"/>
+      <c r="L196" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="M196" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="n">
+        <v>3</v>
+      </c>
+      <c r="P196" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>4</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2</v>
+      </c>
+      <c r="S196" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3175.2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>106004</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>226799445</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>WSCR57</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="n"/>
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
+      <c r="J197" s="2" t="n"/>
+      <c r="K197" s="2" t="n"/>
+      <c r="L197" t="n">
+        <v>159.25</v>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="n">
+        <v>3</v>
+      </c>
+      <c r="P197" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>4</v>
+      </c>
+      <c r="R197" t="n">
+        <v>3</v>
+      </c>
+      <c r="S197" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>2866.5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>106004</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>226799459</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>WSCR89</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="n"/>
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2" t="n"/>
+      <c r="J198" s="2" t="n"/>
+      <c r="K198" s="2" t="n"/>
+      <c r="L198" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" t="n">
+        <v>3</v>
+      </c>
+      <c r="P198" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>4</v>
+      </c>
+      <c r="R198" t="n">
+        <v>3</v>
+      </c>
+      <c r="S198" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>2908.44</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>106006</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>226772776</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="n"/>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
+      <c r="K199" s="2" t="n"/>
+      <c r="L199" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>4</v>
+      </c>
+      <c r="S199" t="n">
+        <v>8</v>
+      </c>
+      <c r="U199" t="n">
+        <v>8</v>
+      </c>
+      <c r="W199" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>1544.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>106006</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1213706</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>4</v>
+      </c>
+      <c r="S200" t="n">
+        <v>8</v>
+      </c>
+      <c r="U200" t="n">
+        <v>8</v>
+      </c>
+      <c r="W200" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>1544.4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>106017</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>156352241</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PABR56</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>PABR56CM</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>PABR56CM</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2</v>
+      </c>
+      <c r="O201" t="n">
+        <v>3</v>
+      </c>
+      <c r="P201" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>4</v>
+      </c>
+      <c r="R201" t="n">
+        <v>3</v>
+      </c>
+      <c r="S201" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>2183.04</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>106017</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>156352242</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PABR56</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>PABR56MH</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>PABR56MH</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M202" t="n">
+        <v>1</v>
+      </c>
+      <c r="N202" t="n">
+        <v>2</v>
+      </c>
+      <c r="O202" t="n">
+        <v>3</v>
+      </c>
+      <c r="P202" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>4</v>
+      </c>
+      <c r="R202" t="n">
+        <v>3</v>
+      </c>
+      <c r="S202" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>2183.04</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>106017</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>FQ - BARRA SH. 1</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>226773817</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PABR80</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
+      <c r="J203" s="2" t="n"/>
+      <c r="K203" s="2" t="n"/>
+      <c r="L203" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2</v>
+      </c>
+      <c r="O203" t="n">
+        <v>3</v>
+      </c>
+      <c r="P203" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>4</v>
+      </c>
+      <c r="R203" t="n">
+        <v>3</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA203" t="n">
         <v>2557.8</v>
       </c>
     </row>
@@ -14195,15 +14837,26 @@
           <t>CALCADOS KARYBY LTDA</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>B2_RelB2bCarrinhoExcel-18h58.xlsx</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEM ARQUIVO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>75</v>
       </c>
+      <c r="G14" t="n">
+        <v>75</v>
+      </c>
       <c r="H14" t="n">
+        <v>10917.87</v>
+      </c>
+      <c r="I14" t="n">
         <v>10917.87</v>
       </c>
     </row>
@@ -14332,15 +14985,26 @@
           <t>ZOTTO CALCADOS LTDA</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>B1_2_RelB2bCarrinhoExcel-18h58.xlsx</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEM ARQUIVO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>114</v>
       </c>
+      <c r="G18" t="n">
+        <v>114</v>
+      </c>
       <c r="H18" t="n">
+        <v>11390.88</v>
+      </c>
+      <c r="I18" t="n">
         <v>11390.88</v>
       </c>
     </row>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA203"/>
+  <dimension ref="A1:AA274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14316,6 +14316,4731 @@
       </c>
       <c r="AA203" t="n">
         <v>2557.8</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>105718</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>226773909</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PAX634</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
+      <c r="K204" s="2" t="n"/>
+      <c r="L204" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="M204" t="n">
+        <v>1</v>
+      </c>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="n">
+        <v>2</v>
+      </c>
+      <c r="P204" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>4</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>1521.45</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>105718</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>226774175</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="n"/>
+      <c r="H205" s="2" t="n"/>
+      <c r="I205" s="2" t="n"/>
+      <c r="J205" s="2" t="n"/>
+      <c r="K205" s="2" t="n"/>
+      <c r="L205" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M205" t="n">
+        <v>1</v>
+      </c>
+      <c r="N205" t="n">
+        <v>2</v>
+      </c>
+      <c r="O205" t="n">
+        <v>2</v>
+      </c>
+      <c r="P205" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>4</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>1063.95</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>105718</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>226774176</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="n"/>
+      <c r="H206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+      <c r="J206" s="2" t="n"/>
+      <c r="K206" s="2" t="n"/>
+      <c r="L206" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M206" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" t="n">
+        <v>2</v>
+      </c>
+      <c r="P206" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>4</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2</v>
+      </c>
+      <c r="S206" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>1063.95</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>105718</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>226774179</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PRA730</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>PRA730CA</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>PRA730CA</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="n"/>
+      <c r="H207" s="2" t="n"/>
+      <c r="I207" s="2" t="n"/>
+      <c r="J207" s="2" t="n"/>
+      <c r="K207" s="2" t="n"/>
+      <c r="L207" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="M207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" t="n">
+        <v>2</v>
+      </c>
+      <c r="O207" t="n">
+        <v>2</v>
+      </c>
+      <c r="P207" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>4</v>
+      </c>
+      <c r="R207" t="n">
+        <v>2</v>
+      </c>
+      <c r="S207" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>1633.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>105718</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>226799120</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>TBC207</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="n"/>
+      <c r="H208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
+      <c r="K208" s="2" t="n"/>
+      <c r="L208" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="M208" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" t="n">
+        <v>2</v>
+      </c>
+      <c r="O208" t="n">
+        <v>3</v>
+      </c>
+      <c r="P208" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>4</v>
+      </c>
+      <c r="R208" t="n">
+        <v>3</v>
+      </c>
+      <c r="S208" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>1025.28</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>105725</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>42444814</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>GBE969</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>GBE969CN</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>GBE969CN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>232.46</v>
+      </c>
+      <c r="M209" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>464.92</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>105725</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>20992</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>GBE969</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>GBE969PT</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>GBE969PT</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>232.46</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>697.38</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>105961</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>56456539</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ASF950</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ASF950TP</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ASF950TP</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>124.86</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="R211" t="n">
+        <v>1</v>
+      </c>
+      <c r="S211" t="n">
+        <v>1</v>
+      </c>
+      <c r="T211" t="n">
+        <v>2</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>1123.74</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>105961</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>226799440</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>WSCR54</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="n"/>
+      <c r="H212" s="2" t="n"/>
+      <c r="I212" s="2" t="n"/>
+      <c r="J212" s="2" t="n"/>
+      <c r="K212" s="2" t="n"/>
+      <c r="L212" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="M212" t="n">
+        <v>1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" t="n">
+        <v>2</v>
+      </c>
+      <c r="P212" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>3</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2</v>
+      </c>
+      <c r="S212" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>2540.16</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>105961</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>226799445</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>WSCR57</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="n"/>
+      <c r="H213" s="2" t="n"/>
+      <c r="I213" s="2" t="n"/>
+      <c r="J213" s="2" t="n"/>
+      <c r="K213" s="2" t="n"/>
+      <c r="L213" t="n">
+        <v>159.25</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1</v>
+      </c>
+      <c r="O213" t="n">
+        <v>3</v>
+      </c>
+      <c r="P213" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>4</v>
+      </c>
+      <c r="R213" t="n">
+        <v>3</v>
+      </c>
+      <c r="S213" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>2866.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>105961</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>226799459</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>WSCR89</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
+      <c r="K214" s="2" t="n"/>
+      <c r="L214" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="M214" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" t="n">
+        <v>3</v>
+      </c>
+      <c r="P214" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>4</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2</v>
+      </c>
+      <c r="S214" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>2423.7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>226772885</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BBK071</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="n"/>
+      <c r="H215" s="2" t="n"/>
+      <c r="I215" s="2" t="n"/>
+      <c r="J215" s="2" t="n"/>
+      <c r="K215" s="2" t="n"/>
+      <c r="L215" t="n">
+        <v>153.38</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="n">
+        <v>2</v>
+      </c>
+      <c r="P215" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>4</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2</v>
+      </c>
+      <c r="S215" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>2300.7</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>226773843</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PAT119</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>PAT119CF</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>PAT119CF</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="n"/>
+      <c r="H216" s="2" t="n"/>
+      <c r="I216" s="2" t="n"/>
+      <c r="J216" s="2" t="n"/>
+      <c r="K216" s="2" t="n"/>
+      <c r="L216" t="n">
+        <v>131.29</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
+        <v>2</v>
+      </c>
+      <c r="O216" t="n">
+        <v>3</v>
+      </c>
+      <c r="P216" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>4</v>
+      </c>
+      <c r="R216" t="n">
+        <v>3</v>
+      </c>
+      <c r="S216" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>2363.22</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>222769922</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>PMD057FD</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>PMD057FD</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M217" t="n">
+        <v>1</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" t="n">
+        <v>2</v>
+      </c>
+      <c r="P217" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>4</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2</v>
+      </c>
+      <c r="S217" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>226773985</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PMD407</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="n"/>
+      <c r="H218" s="2" t="n"/>
+      <c r="I218" s="2" t="n"/>
+      <c r="J218" s="2" t="n"/>
+      <c r="K218" s="2" t="n"/>
+      <c r="L218" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M218" t="n">
+        <v>1</v>
+      </c>
+      <c r="N218" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" t="n">
+        <v>3</v>
+      </c>
+      <c r="P218" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>4</v>
+      </c>
+      <c r="R218" t="n">
+        <v>3</v>
+      </c>
+      <c r="S218" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>1983.24</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>226773986</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>PMD407</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>PMD407VO</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>PMD407VO</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="n"/>
+      <c r="H219" s="2" t="n"/>
+      <c r="I219" s="2" t="n"/>
+      <c r="J219" s="2" t="n"/>
+      <c r="K219" s="2" t="n"/>
+      <c r="L219" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>2</v>
+      </c>
+      <c r="O219" t="n">
+        <v>2</v>
+      </c>
+      <c r="P219" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>4</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2</v>
+      </c>
+      <c r="S219" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>1652.7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>226774180</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="n"/>
+      <c r="H220" s="2" t="n"/>
+      <c r="I220" s="2" t="n"/>
+      <c r="J220" s="2" t="n"/>
+      <c r="K220" s="2" t="n"/>
+      <c r="L220" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" t="n">
+        <v>3</v>
+      </c>
+      <c r="P220" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>4</v>
+      </c>
+      <c r="R220" t="n">
+        <v>3</v>
+      </c>
+      <c r="S220" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>1104.3</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>226774181</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="n"/>
+      <c r="H221" s="2" t="n"/>
+      <c r="I221" s="2" t="n"/>
+      <c r="J221" s="2" t="n"/>
+      <c r="K221" s="2" t="n"/>
+      <c r="L221" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>2</v>
+      </c>
+      <c r="O221" t="n">
+        <v>2</v>
+      </c>
+      <c r="P221" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>4</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2</v>
+      </c>
+      <c r="S221" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>920.25</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>105726</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>73909425</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>GBF529</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>GBF529TN</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>GBF529TN</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>460.8</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>105726</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>948266</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>HBV022</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>HBV022CF</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>HBV022CF</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>228</v>
+      </c>
+      <c r="M223" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>105726</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>941332</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>HBV022</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>HBV022PT</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>HBV022PT</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>228</v>
+      </c>
+      <c r="M224" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>105726</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>12078368</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>348</v>
+      </c>
+      <c r="M225" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>105962</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>13224</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M226" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>508.54</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>105962</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>13281</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>HMO101PT</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>HMO101PT</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>508.54</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>105720</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>99645682</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>WSC003</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>WSC003OW</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>WSC003OW</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="M228" t="n">
+        <v>1</v>
+      </c>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="n">
+        <v>3</v>
+      </c>
+      <c r="P228" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>4</v>
+      </c>
+      <c r="R228" t="n">
+        <v>3</v>
+      </c>
+      <c r="S228" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>2487.6</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>105720</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>226906303</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>WSC761</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>WSC761BC</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>WSC761BC</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="n"/>
+      <c r="H229" s="2" t="n"/>
+      <c r="I229" s="2" t="n"/>
+      <c r="J229" s="2" t="n"/>
+      <c r="K229" s="2" t="n"/>
+      <c r="L229" t="n">
+        <v>143.91</v>
+      </c>
+      <c r="M229" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" t="n">
+        <v>3</v>
+      </c>
+      <c r="P229" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>4</v>
+      </c>
+      <c r="R229" t="n">
+        <v>3</v>
+      </c>
+      <c r="S229" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>2590.38</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>105731</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>226772991</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DTR013</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>DTR013PT</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>DTR013PT</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="n"/>
+      <c r="H230" s="2" t="n"/>
+      <c r="I230" s="2" t="n"/>
+      <c r="J230" s="2" t="n"/>
+      <c r="K230" s="2" t="n"/>
+      <c r="L230" t="n">
+        <v>167.28</v>
+      </c>
+      <c r="M230" t="n">
+        <v>1</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1</v>
+      </c>
+      <c r="S230" t="n">
+        <v>2</v>
+      </c>
+      <c r="T230" t="n">
+        <v>2</v>
+      </c>
+      <c r="U230" t="n">
+        <v>3</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1</v>
+      </c>
+      <c r="X230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>2007.36</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>105731</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>226780323</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>SLG010MR</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>SLG010MR</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="n"/>
+      <c r="H231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+      <c r="J231" s="2" t="n"/>
+      <c r="K231" s="2" t="n"/>
+      <c r="L231" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M231" t="n">
+        <v>1</v>
+      </c>
+      <c r="R231" t="n">
+        <v>1</v>
+      </c>
+      <c r="S231" t="n">
+        <v>2</v>
+      </c>
+      <c r="T231" t="n">
+        <v>3</v>
+      </c>
+      <c r="U231" t="n">
+        <v>3</v>
+      </c>
+      <c r="V231" t="n">
+        <v>2</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>2907.72</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>105731</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>226780324</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="n"/>
+      <c r="H232" s="2" t="n"/>
+      <c r="I232" s="2" t="n"/>
+      <c r="J232" s="2" t="n"/>
+      <c r="K232" s="2" t="n"/>
+      <c r="L232" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M232" t="n">
+        <v>1</v>
+      </c>
+      <c r="R232" t="n">
+        <v>1</v>
+      </c>
+      <c r="S232" t="n">
+        <v>2</v>
+      </c>
+      <c r="T232" t="n">
+        <v>2</v>
+      </c>
+      <c r="U232" t="n">
+        <v>3</v>
+      </c>
+      <c r="V232" t="n">
+        <v>2</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1</v>
+      </c>
+      <c r="X232" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>2907.72</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>105963</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>939642</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M233" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>630.36</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>105963</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>939643</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M234" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>840.48</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>105963</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>4600</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>LMM009</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>LMM009MM</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>LMM009MM</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M235" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>562.6799999999999</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>105963</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>21174</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>LMM009</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>LMM009PT</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>LMM009PT</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>562.6799999999999</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>219741931</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>TBC193</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>TBC193PT</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>TBC193PT</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>SAPATILHA</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M237" t="n">
+        <v>1</v>
+      </c>
+      <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="n">
+        <v>2</v>
+      </c>
+      <c r="P237" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>2</v>
+      </c>
+      <c r="R237" t="n">
+        <v>1</v>
+      </c>
+      <c r="S237" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>804.87</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>219741932</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>TBC193</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>TBC193TN</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>TBC193TN</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>SAPATILHA</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M238" t="n">
+        <v>1</v>
+      </c>
+      <c r="N238" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" t="n">
+        <v>2</v>
+      </c>
+      <c r="P238" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>3</v>
+      </c>
+      <c r="R238" t="n">
+        <v>2</v>
+      </c>
+      <c r="S238" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>1073.16</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>219742032</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>TEC163</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>TEC163PT</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>TEC163PT</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>SCARPIN</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M239" t="n">
+        <v>1</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="n">
+        <v>2</v>
+      </c>
+      <c r="P239" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>2</v>
+      </c>
+      <c r="R239" t="n">
+        <v>1</v>
+      </c>
+      <c r="S239" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>926.1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>219742033</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>TEC163</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>TEC163TN</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>TEC163TN</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>SCARPIN</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M240" t="n">
+        <v>1</v>
+      </c>
+      <c r="N240" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" t="n">
+        <v>2</v>
+      </c>
+      <c r="P240" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>2</v>
+      </c>
+      <c r="R240" t="n">
+        <v>1</v>
+      </c>
+      <c r="S240" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>926.1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>226799195</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="n"/>
+      <c r="H241" s="2" t="n"/>
+      <c r="I241" s="2" t="n"/>
+      <c r="J241" s="2" t="n"/>
+      <c r="K241" s="2" t="n"/>
+      <c r="L241" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M241" t="n">
+        <v>1</v>
+      </c>
+      <c r="N241" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" t="n">
+        <v>2</v>
+      </c>
+      <c r="P241" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>3</v>
+      </c>
+      <c r="R241" t="n">
+        <v>2</v>
+      </c>
+      <c r="S241" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>226799196</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>TEC164FD</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>TEC164FD</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="n"/>
+      <c r="H242" s="2" t="n"/>
+      <c r="I242" s="2" t="n"/>
+      <c r="J242" s="2" t="n"/>
+      <c r="K242" s="2" t="n"/>
+      <c r="L242" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M242" t="n">
+        <v>1</v>
+      </c>
+      <c r="N242" t="n">
+        <v>1</v>
+      </c>
+      <c r="O242" t="n">
+        <v>2</v>
+      </c>
+      <c r="P242" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>3</v>
+      </c>
+      <c r="R242" t="n">
+        <v>2</v>
+      </c>
+      <c r="S242" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>226799197</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="n"/>
+      <c r="H243" s="2" t="n"/>
+      <c r="I243" s="2" t="n"/>
+      <c r="J243" s="2" t="n"/>
+      <c r="K243" s="2" t="n"/>
+      <c r="L243" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M243" t="n">
+        <v>1</v>
+      </c>
+      <c r="N243" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" t="n">
+        <v>3</v>
+      </c>
+      <c r="P243" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>4</v>
+      </c>
+      <c r="R243" t="n">
+        <v>2</v>
+      </c>
+      <c r="S243" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>1543.5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>105960</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>226772776</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="n"/>
+      <c r="H244" s="2" t="n"/>
+      <c r="I244" s="2" t="n"/>
+      <c r="J244" s="2" t="n"/>
+      <c r="K244" s="2" t="n"/>
+      <c r="L244" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M244" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>2</v>
+      </c>
+      <c r="S244" t="n">
+        <v>5</v>
+      </c>
+      <c r="U244" t="n">
+        <v>5</v>
+      </c>
+      <c r="W244" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>965.25</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>105960</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1213706</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M245" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>2</v>
+      </c>
+      <c r="S245" t="n">
+        <v>5</v>
+      </c>
+      <c r="U245" t="n">
+        <v>5</v>
+      </c>
+      <c r="W245" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>965.25</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>105723</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>170765818</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>WCL163</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>WCL163PT</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>WCL163PT</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>499.9</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>200.9</v>
+      </c>
+      <c r="M246" t="n">
+        <v>1</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" t="n">
+        <v>2</v>
+      </c>
+      <c r="P246" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>2</v>
+      </c>
+      <c r="R246" t="n">
+        <v>1</v>
+      </c>
+      <c r="S246" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>1808.1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>105964</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>23300</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>LMM016BG</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>LMM016BG</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M247" t="n">
+        <v>1</v>
+      </c>
+      <c r="P247" t="n">
+        <v>18</v>
+      </c>
+      <c r="T247" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>716.76</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>105964</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>4613</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>LMM016PT</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>LMM016PT</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M248" t="n">
+        <v>1</v>
+      </c>
+      <c r="P248" t="n">
+        <v>18</v>
+      </c>
+      <c r="T248" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>716.76</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>105964</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>105185079</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>LMW200</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>LMW200ND</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>LMW200ND</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M249" t="n">
+        <v>1</v>
+      </c>
+      <c r="O249" t="n">
+        <v>12</v>
+      </c>
+      <c r="S249" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>472.08</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>105964</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>105185080</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>LMW200</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>LMW200PT</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>LMW200PT</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="n">
+        <v>12</v>
+      </c>
+      <c r="S250" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>472.08</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>105711</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>156352242</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PABR56</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>PABR56MH</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>PABR56MH</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M251" t="n">
+        <v>1</v>
+      </c>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="n">
+        <v>3</v>
+      </c>
+      <c r="P251" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>4</v>
+      </c>
+      <c r="R251" t="n">
+        <v>2</v>
+      </c>
+      <c r="S251" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>1819.2</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>105711</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>156352243</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>PABR56</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>PABR56PT</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>PABR56PT</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M252" t="n">
+        <v>1</v>
+      </c>
+      <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="n">
+        <v>2</v>
+      </c>
+      <c r="P252" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>3</v>
+      </c>
+      <c r="R252" t="n">
+        <v>2</v>
+      </c>
+      <c r="S252" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>1455.36</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>105711</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>156352246</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PABR58</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>PABR58TN</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>PABR58TN</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>136.59</v>
+      </c>
+      <c r="M253" t="n">
+        <v>1</v>
+      </c>
+      <c r="N253" t="n">
+        <v>1</v>
+      </c>
+      <c r="O253" t="n">
+        <v>2</v>
+      </c>
+      <c r="P253" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>2</v>
+      </c>
+      <c r="R253" t="n">
+        <v>1</v>
+      </c>
+      <c r="S253" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>1229.31</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>105711</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>156352247</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PABR59</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>PABR59NT</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>PABR59NT</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M254" t="n">
+        <v>1</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="n">
+        <v>3</v>
+      </c>
+      <c r="P254" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>4</v>
+      </c>
+      <c r="R254" t="n">
+        <v>2</v>
+      </c>
+      <c r="S254" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>1819.2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>105711</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>226773817</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>PABR80</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="n"/>
+      <c r="H255" s="2" t="n"/>
+      <c r="I255" s="2" t="n"/>
+      <c r="J255" s="2" t="n"/>
+      <c r="K255" s="2" t="n"/>
+      <c r="L255" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="M255" t="n">
+        <v>1</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="n">
+        <v>2</v>
+      </c>
+      <c r="P255" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>3</v>
+      </c>
+      <c r="R255" t="n">
+        <v>2</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>1705.2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>105712</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>227869440</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="n"/>
+      <c r="H256" s="2" t="n"/>
+      <c r="I256" s="2" t="n"/>
+      <c r="J256" s="2" t="n"/>
+      <c r="K256" s="2" t="n"/>
+      <c r="L256" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="M256" t="n">
+        <v>1</v>
+      </c>
+      <c r="N256" t="n">
+        <v>1</v>
+      </c>
+      <c r="O256" t="n">
+        <v>2</v>
+      </c>
+      <c r="P256" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>3</v>
+      </c>
+      <c r="R256" t="n">
+        <v>2</v>
+      </c>
+      <c r="S256" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>1791.72</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>105712</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>137503829</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>WCL018</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>WCL018TN</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>WCL018TN</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="M257" t="n">
+        <v>1</v>
+      </c>
+      <c r="N257" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" t="n">
+        <v>2</v>
+      </c>
+      <c r="P257" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>2</v>
+      </c>
+      <c r="R257" t="n">
+        <v>1</v>
+      </c>
+      <c r="S257" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>833.3099999999999</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>105712</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>164260186</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>WCL099</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="M258" t="n">
+        <v>1</v>
+      </c>
+      <c r="N258" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" t="n">
+        <v>3</v>
+      </c>
+      <c r="P258" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>4</v>
+      </c>
+      <c r="R258" t="n">
+        <v>2</v>
+      </c>
+      <c r="S258" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>1336.05</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>105712</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>226799260</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>WCL203</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>WCL203CF</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>WCL203CF</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="n"/>
+      <c r="H259" s="2" t="n"/>
+      <c r="I259" s="2" t="n"/>
+      <c r="J259" s="2" t="n"/>
+      <c r="K259" s="2" t="n"/>
+      <c r="L259" t="n">
+        <v>145.33</v>
+      </c>
+      <c r="M259" t="n">
+        <v>1</v>
+      </c>
+      <c r="N259" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" t="n">
+        <v>3</v>
+      </c>
+      <c r="P259" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>4</v>
+      </c>
+      <c r="R259" t="n">
+        <v>2</v>
+      </c>
+      <c r="S259" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>2179.95</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>226773022</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="n"/>
+      <c r="H260" s="2" t="n"/>
+      <c r="I260" s="2" t="n"/>
+      <c r="J260" s="2" t="n"/>
+      <c r="K260" s="2" t="n"/>
+      <c r="L260" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M260" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>485.98</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>226773023</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="n"/>
+      <c r="H261" s="2" t="n"/>
+      <c r="I261" s="2" t="n"/>
+      <c r="J261" s="2" t="n"/>
+      <c r="K261" s="2" t="n"/>
+      <c r="L261" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M261" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>485.98</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>226773071</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>GBF269</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="n"/>
+      <c r="H262" s="2" t="n"/>
+      <c r="I262" s="2" t="n"/>
+      <c r="J262" s="2" t="n"/>
+      <c r="K262" s="2" t="n"/>
+      <c r="L262" t="n">
+        <v>235</v>
+      </c>
+      <c r="M262" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>58912429</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>GBF325</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>GBF325AK</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>GBF325AK</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="M263" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>169.2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>161296295</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>GBF325</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>GBF325CF</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>GBF325CF</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="M264" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>338.4</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>218687255</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M265" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>122.67</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>58174815</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M266" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>245.34</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>226773215</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>GBF786</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="n"/>
+      <c r="H267" s="2" t="n"/>
+      <c r="I267" s="2" t="n"/>
+      <c r="J267" s="2" t="n"/>
+      <c r="K267" s="2" t="n"/>
+      <c r="L267" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="M267" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>401.38</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>226773217</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="n"/>
+      <c r="H268" s="2" t="n"/>
+      <c r="I268" s="2" t="n"/>
+      <c r="J268" s="2" t="n"/>
+      <c r="K268" s="2" t="n"/>
+      <c r="L268" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M268" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>226773218</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="n"/>
+      <c r="H269" s="2" t="n"/>
+      <c r="I269" s="2" t="n"/>
+      <c r="J269" s="2" t="n"/>
+      <c r="K269" s="2" t="n"/>
+      <c r="L269" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M269" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>276.12</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>177646295</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>GBF827</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="M270" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>514.6799999999999</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>147957944</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>GSN811</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>GSN811PT</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>GSN811PT</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="M271" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>370.14</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>105965</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>226799136</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="n"/>
+      <c r="H272" s="2" t="n"/>
+      <c r="I272" s="2" t="n"/>
+      <c r="J272" s="2" t="n"/>
+      <c r="K272" s="2" t="n"/>
+      <c r="L272" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1</v>
+      </c>
+      <c r="N272" t="n">
+        <v>2</v>
+      </c>
+      <c r="O272" t="n">
+        <v>3</v>
+      </c>
+      <c r="P272" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>4</v>
+      </c>
+      <c r="R272" t="n">
+        <v>3</v>
+      </c>
+      <c r="S272" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>105965</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>226799137</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="n"/>
+      <c r="H273" s="2" t="n"/>
+      <c r="I273" s="2" t="n"/>
+      <c r="J273" s="2" t="n"/>
+      <c r="K273" s="2" t="n"/>
+      <c r="L273" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M273" t="n">
+        <v>1</v>
+      </c>
+      <c r="N273" t="n">
+        <v>2</v>
+      </c>
+      <c r="O273" t="n">
+        <v>3</v>
+      </c>
+      <c r="P273" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>4</v>
+      </c>
+      <c r="R273" t="n">
+        <v>3</v>
+      </c>
+      <c r="S273" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>105965</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>226799138</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="n"/>
+      <c r="H274" s="2" t="n"/>
+      <c r="I274" s="2" t="n"/>
+      <c r="J274" s="2" t="n"/>
+      <c r="K274" s="2" t="n"/>
+      <c r="L274" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M274" t="n">
+        <v>1</v>
+      </c>
+      <c r="N274" t="n">
+        <v>2</v>
+      </c>
+      <c r="O274" t="n">
+        <v>3</v>
+      </c>
+      <c r="P274" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>4</v>
+      </c>
+      <c r="R274" t="n">
+        <v>3</v>
+      </c>
+      <c r="S274" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>1095.84</v>
       </c>
     </row>
   </sheetData>
@@ -14329,7 +19054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15563,6 +20288,661 @@
         <v>3368.7</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>105711</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-18h59.xlsx</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>63</v>
+      </c>
+      <c r="G34" t="n">
+        <v>63</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8028.27</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8028.27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>105712</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>85</v>
+      </c>
+      <c r="G35" t="n">
+        <v>51</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10472.17</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6141.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>105718</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>90</v>
+      </c>
+      <c r="G36" t="n">
+        <v>78</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6969.69</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6308.13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>105719</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WW EXPORT LTDA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>114</v>
+      </c>
+      <c r="G37" t="n">
+        <v>114</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11962.41</v>
+      </c>
+      <c r="I37" t="n">
+        <v>11962.41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>105720</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>76</v>
+      </c>
+      <c r="G38" t="n">
+        <v>36</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10980.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5077.98</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N C CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>78</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7743.33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>7743.33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MASSEY CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SEM ARQUIVO</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>114</v>
+      </c>
+      <c r="H40" t="n">
+        <v>10669.74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>105723</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CALCADOS KISSOL LTDA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1808.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1808.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>28</v>
+      </c>
+      <c r="G42" t="n">
+        <v>28</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4294.07</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4294.07</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>105725</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>11</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2557.06</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1162.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>105726</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2536.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2068.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>105731</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>78</v>
+      </c>
+      <c r="G45" t="n">
+        <v>36</v>
+      </c>
+      <c r="H45" t="n">
+        <v>18594.4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>7822.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>105960</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>30</v>
+      </c>
+      <c r="G46" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1930.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>105961</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>54</v>
+      </c>
+      <c r="G47" t="n">
+        <v>54</v>
+      </c>
+      <c r="H47" t="n">
+        <v>8954.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>8954.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>105962</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1017.08</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1017.08</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>105963</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PRIMAR IND TEXTIL LTDA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>156</v>
+      </c>
+      <c r="G49" t="n">
+        <v>156</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2596.2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2596.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>105964</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>L T BERTOLANI CONFECCAO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>6_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>120</v>
+      </c>
+      <c r="G50" t="n">
+        <v>120</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2377.68</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2377.68</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>105965</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>D MATTHES CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h03.xlsx</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>54</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3287.52</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3287.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA274"/>
+  <dimension ref="A1:AA280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19041,6 +19041,474 @@
       </c>
       <c r="AA274" t="n">
         <v>1095.84</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>134703902</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>WSC330BC</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>WSC330BC</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="M275" t="n">
+        <v>1</v>
+      </c>
+      <c r="N275" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" t="n">
+        <v>3</v>
+      </c>
+      <c r="P275" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>4</v>
+      </c>
+      <c r="R275" t="n">
+        <v>3</v>
+      </c>
+      <c r="S275" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>1383.48</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>226799278</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="n"/>
+      <c r="H276" s="2" t="n"/>
+      <c r="I276" s="2" t="n"/>
+      <c r="J276" s="2" t="n"/>
+      <c r="K276" s="2" t="n"/>
+      <c r="L276" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M276" t="n">
+        <v>1</v>
+      </c>
+      <c r="N276" t="n">
+        <v>2</v>
+      </c>
+      <c r="O276" t="n">
+        <v>4</v>
+      </c>
+      <c r="P276" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>6</v>
+      </c>
+      <c r="R276" t="n">
+        <v>4</v>
+      </c>
+      <c r="S276" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>1639.68</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>147983439</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>WSC432</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>WSC432AW</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>WSC432AW</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M277" t="n">
+        <v>1</v>
+      </c>
+      <c r="N277" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" t="n">
+        <v>3</v>
+      </c>
+      <c r="P277" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>4</v>
+      </c>
+      <c r="R277" t="n">
+        <v>3</v>
+      </c>
+      <c r="S277" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>1229.76</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>137619676</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M278" t="n">
+        <v>1</v>
+      </c>
+      <c r="N278" t="n">
+        <v>1</v>
+      </c>
+      <c r="O278" t="n">
+        <v>3</v>
+      </c>
+      <c r="P278" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>4</v>
+      </c>
+      <c r="R278" t="n">
+        <v>3</v>
+      </c>
+      <c r="S278" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>2138.94</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>170929723</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>WSCR61FD</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>WSCR61FD</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1</v>
+      </c>
+      <c r="N279" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" t="n">
+        <v>3</v>
+      </c>
+      <c r="P279" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>4</v>
+      </c>
+      <c r="R279" t="n">
+        <v>3</v>
+      </c>
+      <c r="S279" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>2138.94</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>137619678</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>WSCR61PT</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>WSCR61PT</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1</v>
+      </c>
+      <c r="N280" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" t="n">
+        <v>3</v>
+      </c>
+      <c r="P280" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>4</v>
+      </c>
+      <c r="R280" t="n">
+        <v>3</v>
+      </c>
+      <c r="S280" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>2138.94</v>
       </c>
     </row>
   </sheetData>
@@ -20524,15 +20992,26 @@
           <t>MASSEY CALCADOS LTDA</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5876a4d7-RelB2bCarrinhoExcel-19h04.xlsx</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SEM ARQUIVO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>114</v>
       </c>
+      <c r="G40" t="n">
+        <v>114</v>
+      </c>
       <c r="H40" t="n">
+        <v>10669.74</v>
+      </c>
+      <c r="I40" t="n">
         <v>10669.74</v>
       </c>
     </row>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA280"/>
+  <dimension ref="A1:AA294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19509,6 +19509,909 @@
       </c>
       <c r="AA280" t="n">
         <v>2138.94</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>105839</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>12078368</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
+        <v>348</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>105839</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>12078369</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
+        <v>348</v>
+      </c>
+      <c r="M282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>105840</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>13224</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M283" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>227869440</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="n"/>
+      <c r="H284" s="2" t="n"/>
+      <c r="I284" s="2" t="n"/>
+      <c r="J284" s="2" t="n"/>
+      <c r="K284" s="2" t="n"/>
+      <c r="L284" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" t="n">
+        <v>2</v>
+      </c>
+      <c r="P284" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>2</v>
+      </c>
+      <c r="R284" t="n">
+        <v>1</v>
+      </c>
+      <c r="S284" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>1343.79</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>164260186</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>WCL099</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="M285" t="n">
+        <v>1</v>
+      </c>
+      <c r="N285" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" t="n">
+        <v>2</v>
+      </c>
+      <c r="P285" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>2</v>
+      </c>
+      <c r="R285" t="n">
+        <v>1</v>
+      </c>
+      <c r="S285" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>801.63</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>226799259</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>WCL202</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>WCL202CA</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>WCL202CA</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="n"/>
+      <c r="H286" s="2" t="n"/>
+      <c r="I286" s="2" t="n"/>
+      <c r="J286" s="2" t="n"/>
+      <c r="K286" s="2" t="n"/>
+      <c r="L286" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="M286" t="n">
+        <v>1</v>
+      </c>
+      <c r="N286" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" t="n">
+        <v>2</v>
+      </c>
+      <c r="P286" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>2</v>
+      </c>
+      <c r="R286" t="n">
+        <v>1</v>
+      </c>
+      <c r="S286" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>1122.3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>226773985</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>PMD407</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="n"/>
+      <c r="H287" s="2" t="n"/>
+      <c r="I287" s="2" t="n"/>
+      <c r="J287" s="2" t="n"/>
+      <c r="K287" s="2" t="n"/>
+      <c r="L287" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1</v>
+      </c>
+      <c r="N287" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" t="n">
+        <v>2</v>
+      </c>
+      <c r="P287" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>2</v>
+      </c>
+      <c r="R287" t="n">
+        <v>1</v>
+      </c>
+      <c r="S287" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>991.62</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>226774180</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="n"/>
+      <c r="H288" s="2" t="n"/>
+      <c r="I288" s="2" t="n"/>
+      <c r="J288" s="2" t="n"/>
+      <c r="K288" s="2" t="n"/>
+      <c r="L288" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1</v>
+      </c>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>2</v>
+      </c>
+      <c r="P288" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>2</v>
+      </c>
+      <c r="R288" t="n">
+        <v>1</v>
+      </c>
+      <c r="S288" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>552.15</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>226774181</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="n"/>
+      <c r="H289" s="2" t="n"/>
+      <c r="I289" s="2" t="n"/>
+      <c r="J289" s="2" t="n"/>
+      <c r="K289" s="2" t="n"/>
+      <c r="L289" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M289" t="n">
+        <v>1</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="n">
+        <v>2</v>
+      </c>
+      <c r="P289" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>2</v>
+      </c>
+      <c r="R289" t="n">
+        <v>1</v>
+      </c>
+      <c r="S289" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>552.15</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>161296295</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>GBF325</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>GBF325CF</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>GBF325CF</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="M290" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>169.2</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>58174815</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M291" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>122.67</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>226773215</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>GBF786</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="n"/>
+      <c r="H292" s="2" t="n"/>
+      <c r="I292" s="2" t="n"/>
+      <c r="J292" s="2" t="n"/>
+      <c r="K292" s="2" t="n"/>
+      <c r="L292" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="M292" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>401.38</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>177646295</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>GBF827</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>171.56</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>105843</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>226780324</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="n"/>
+      <c r="H294" s="2" t="n"/>
+      <c r="I294" s="2" t="n"/>
+      <c r="J294" s="2" t="n"/>
+      <c r="K294" s="2" t="n"/>
+      <c r="L294" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1</v>
+      </c>
+      <c r="R294" t="n">
+        <v>1</v>
+      </c>
+      <c r="S294" t="n">
+        <v>1</v>
+      </c>
+      <c r="T294" t="n">
+        <v>2</v>
+      </c>
+      <c r="U294" t="n">
+        <v>2</v>
+      </c>
+      <c r="V294" t="n">
+        <v>2</v>
+      </c>
+      <c r="W294" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>2180.79</v>
       </c>
     </row>
   </sheetData>
@@ -19522,7 +20425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21422,6 +22325,228 @@
         <v>3287.52</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>864.8099999999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>864.8099999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>105839</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>105840</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="I54" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>27</v>
+      </c>
+      <c r="G55" t="n">
+        <v>27</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3267.72</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3267.72</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>WW EXPORT LTDA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>27</v>
+      </c>
+      <c r="G56" t="n">
+        <v>27</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2095.92</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2095.92</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>105843</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h08.xlsx</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>9</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2180.79</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2180.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA294"/>
+  <dimension ref="A1:AA369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20412,6 +20412,5049 @@
       </c>
       <c r="AA294" t="n">
         <v>2180.79</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>105967</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>226772776</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="n"/>
+      <c r="H295" s="2" t="n"/>
+      <c r="I295" s="2" t="n"/>
+      <c r="J295" s="2" t="n"/>
+      <c r="K295" s="2" t="n"/>
+      <c r="L295" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M295" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>4</v>
+      </c>
+      <c r="S295" t="n">
+        <v>8</v>
+      </c>
+      <c r="U295" t="n">
+        <v>8</v>
+      </c>
+      <c r="W295" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>1544.4</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>105967</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>1213706</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M296" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>2</v>
+      </c>
+      <c r="S296" t="n">
+        <v>4</v>
+      </c>
+      <c r="U296" t="n">
+        <v>6</v>
+      </c>
+      <c r="W296" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>965.25</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>105983</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>134703902</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>WSC330BC</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>WSC330BC</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="M297" t="n">
+        <v>1</v>
+      </c>
+      <c r="N297" t="n">
+        <v>3</v>
+      </c>
+      <c r="O297" t="n">
+        <v>6</v>
+      </c>
+      <c r="P297" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>10</v>
+      </c>
+      <c r="R297" t="n">
+        <v>6</v>
+      </c>
+      <c r="S297" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>2766.96</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>105983</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>226799278</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="n"/>
+      <c r="H298" s="2" t="n"/>
+      <c r="I298" s="2" t="n"/>
+      <c r="J298" s="2" t="n"/>
+      <c r="K298" s="2" t="n"/>
+      <c r="L298" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M298" t="n">
+        <v>1</v>
+      </c>
+      <c r="N298" t="n">
+        <v>2</v>
+      </c>
+      <c r="O298" t="n">
+        <v>6</v>
+      </c>
+      <c r="P298" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>9</v>
+      </c>
+      <c r="R298" t="n">
+        <v>6</v>
+      </c>
+      <c r="S298" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>2459.52</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>105983</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>147983439</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>WSC432</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>WSC432AW</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>WSC432AW</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M299" t="n">
+        <v>1</v>
+      </c>
+      <c r="N299" t="n">
+        <v>3</v>
+      </c>
+      <c r="O299" t="n">
+        <v>4</v>
+      </c>
+      <c r="P299" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>9</v>
+      </c>
+      <c r="R299" t="n">
+        <v>8</v>
+      </c>
+      <c r="S299" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>2459.52</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>105983</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>137619676</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M300" t="n">
+        <v>1</v>
+      </c>
+      <c r="N300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="n">
+        <v>6</v>
+      </c>
+      <c r="P300" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>7</v>
+      </c>
+      <c r="R300" t="n">
+        <v>3</v>
+      </c>
+      <c r="S300" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>2851.92</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>105983</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>137619678</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>WSCR61PT</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>WSCR61PT</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L301" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M301" t="n">
+        <v>1</v>
+      </c>
+      <c r="N301" t="n">
+        <v>2</v>
+      </c>
+      <c r="O301" t="n">
+        <v>3</v>
+      </c>
+      <c r="P301" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>6</v>
+      </c>
+      <c r="R301" t="n">
+        <v>4</v>
+      </c>
+      <c r="S301" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>2851.92</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>105976</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>227869440</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="n"/>
+      <c r="H302" s="2" t="n"/>
+      <c r="I302" s="2" t="n"/>
+      <c r="J302" s="2" t="n"/>
+      <c r="K302" s="2" t="n"/>
+      <c r="L302" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="M302" t="n">
+        <v>1</v>
+      </c>
+      <c r="N302" t="n">
+        <v>1</v>
+      </c>
+      <c r="O302" t="n">
+        <v>2</v>
+      </c>
+      <c r="P302" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>3</v>
+      </c>
+      <c r="R302" t="n">
+        <v>2</v>
+      </c>
+      <c r="S302" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>1791.72</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>226772885</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>BBK071</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="n"/>
+      <c r="H303" s="2" t="n"/>
+      <c r="I303" s="2" t="n"/>
+      <c r="J303" s="2" t="n"/>
+      <c r="K303" s="2" t="n"/>
+      <c r="L303" t="n">
+        <v>153.38</v>
+      </c>
+      <c r="M303" t="n">
+        <v>1</v>
+      </c>
+      <c r="N303" t="n">
+        <v>1</v>
+      </c>
+      <c r="O303" t="n">
+        <v>2</v>
+      </c>
+      <c r="P303" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>3</v>
+      </c>
+      <c r="R303" t="n">
+        <v>2</v>
+      </c>
+      <c r="S303" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>1840.56</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>226772886</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>BBK072</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>BBK072CF</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>BBK072CF</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="n"/>
+      <c r="H304" s="2" t="n"/>
+      <c r="I304" s="2" t="n"/>
+      <c r="J304" s="2" t="n"/>
+      <c r="K304" s="2" t="n"/>
+      <c r="L304" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="M304" t="n">
+        <v>1</v>
+      </c>
+      <c r="N304" t="n">
+        <v>1</v>
+      </c>
+      <c r="O304" t="n">
+        <v>3</v>
+      </c>
+      <c r="P304" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>4</v>
+      </c>
+      <c r="R304" t="n">
+        <v>2</v>
+      </c>
+      <c r="S304" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>1527.6</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>222769922</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>PMD057FD</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>PMD057FD</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L305" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1</v>
+      </c>
+      <c r="N305" t="n">
+        <v>1</v>
+      </c>
+      <c r="O305" t="n">
+        <v>2</v>
+      </c>
+      <c r="P305" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>3</v>
+      </c>
+      <c r="R305" t="n">
+        <v>2</v>
+      </c>
+      <c r="S305" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>1310.4</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>137502391</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>PMD057PT</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>PMD057PT</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L306" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M306" t="n">
+        <v>1</v>
+      </c>
+      <c r="N306" t="n">
+        <v>1</v>
+      </c>
+      <c r="O306" t="n">
+        <v>1</v>
+      </c>
+      <c r="P306" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>4</v>
+      </c>
+      <c r="R306" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>1310.4</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>226773985</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>PMD407</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="n"/>
+      <c r="H307" s="2" t="n"/>
+      <c r="I307" s="2" t="n"/>
+      <c r="J307" s="2" t="n"/>
+      <c r="K307" s="2" t="n"/>
+      <c r="L307" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M307" t="n">
+        <v>1</v>
+      </c>
+      <c r="N307" t="n">
+        <v>1</v>
+      </c>
+      <c r="O307" t="n">
+        <v>3</v>
+      </c>
+      <c r="P307" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>4</v>
+      </c>
+      <c r="R307" t="n">
+        <v>3</v>
+      </c>
+      <c r="S307" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>1983.24</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>226774180</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="n"/>
+      <c r="H308" s="2" t="n"/>
+      <c r="I308" s="2" t="n"/>
+      <c r="J308" s="2" t="n"/>
+      <c r="K308" s="2" t="n"/>
+      <c r="L308" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1</v>
+      </c>
+      <c r="N308" t="n">
+        <v>2</v>
+      </c>
+      <c r="O308" t="n">
+        <v>4</v>
+      </c>
+      <c r="P308" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>5</v>
+      </c>
+      <c r="R308" t="n">
+        <v>4</v>
+      </c>
+      <c r="S308" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>1288.35</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>105968</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>226774181</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="n"/>
+      <c r="H309" s="2" t="n"/>
+      <c r="I309" s="2" t="n"/>
+      <c r="J309" s="2" t="n"/>
+      <c r="K309" s="2" t="n"/>
+      <c r="L309" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M309" t="n">
+        <v>1</v>
+      </c>
+      <c r="N309" t="n">
+        <v>1</v>
+      </c>
+      <c r="O309" t="n">
+        <v>3</v>
+      </c>
+      <c r="P309" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>3</v>
+      </c>
+      <c r="R309" t="n">
+        <v>3</v>
+      </c>
+      <c r="S309" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>920.25</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>105982</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>226799195</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="n"/>
+      <c r="H310" s="2" t="n"/>
+      <c r="I310" s="2" t="n"/>
+      <c r="J310" s="2" t="n"/>
+      <c r="K310" s="2" t="n"/>
+      <c r="L310" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M310" t="n">
+        <v>1</v>
+      </c>
+      <c r="N310" t="n">
+        <v>1</v>
+      </c>
+      <c r="O310" t="n">
+        <v>2</v>
+      </c>
+      <c r="P310" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>3</v>
+      </c>
+      <c r="R310" t="n">
+        <v>2</v>
+      </c>
+      <c r="S310" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>105982</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>226799197</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="n"/>
+      <c r="H311" s="2" t="n"/>
+      <c r="I311" s="2" t="n"/>
+      <c r="J311" s="2" t="n"/>
+      <c r="K311" s="2" t="n"/>
+      <c r="L311" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M311" t="n">
+        <v>1</v>
+      </c>
+      <c r="N311" t="n">
+        <v>1</v>
+      </c>
+      <c r="O311" t="n">
+        <v>2</v>
+      </c>
+      <c r="P311" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>3</v>
+      </c>
+      <c r="R311" t="n">
+        <v>2</v>
+      </c>
+      <c r="S311" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>105974</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>939642</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L312" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M312" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>630.36</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>105974</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>939643</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L313" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M313" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>1050.6</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>105974</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>79775189</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>LMM619</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>LMM619BC</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>LMM619BC</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L314" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M314" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>367.92</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>105974</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>79775190</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LMM619</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>LMM619BG</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>LMM619BG</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M315" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>183.96</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>105974</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>79775193</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>LMM619</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>LMM619PT</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>LMM619PT</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L316" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M316" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>367.92</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>105969</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>226772891</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CAR112</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>CAR112PT</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>CAR112PT</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="n"/>
+      <c r="H317" s="2" t="n"/>
+      <c r="I317" s="2" t="n"/>
+      <c r="J317" s="2" t="n"/>
+      <c r="K317" s="2" t="n"/>
+      <c r="L317" t="n">
+        <v>268.14</v>
+      </c>
+      <c r="M317" t="n">
+        <v>1</v>
+      </c>
+      <c r="R317" t="n">
+        <v>2</v>
+      </c>
+      <c r="S317" t="n">
+        <v>3</v>
+      </c>
+      <c r="T317" t="n">
+        <v>4</v>
+      </c>
+      <c r="U317" t="n">
+        <v>3</v>
+      </c>
+      <c r="V317" t="n">
+        <v>3</v>
+      </c>
+      <c r="W317" t="n">
+        <v>2</v>
+      </c>
+      <c r="X317" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>4826.52</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>105969</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>226772892</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>CAR113</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>CAR113CF</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>CAR113CF</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="n"/>
+      <c r="H318" s="2" t="n"/>
+      <c r="I318" s="2" t="n"/>
+      <c r="J318" s="2" t="n"/>
+      <c r="K318" s="2" t="n"/>
+      <c r="L318" t="n">
+        <v>268.14</v>
+      </c>
+      <c r="M318" t="n">
+        <v>1</v>
+      </c>
+      <c r="R318" t="n">
+        <v>2</v>
+      </c>
+      <c r="S318" t="n">
+        <v>3</v>
+      </c>
+      <c r="T318" t="n">
+        <v>4</v>
+      </c>
+      <c r="U318" t="n">
+        <v>3</v>
+      </c>
+      <c r="V318" t="n">
+        <v>3</v>
+      </c>
+      <c r="W318" t="n">
+        <v>2</v>
+      </c>
+      <c r="X318" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>4826.52</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>105969</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>226780323</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>SLG010MR</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>SLG010MR</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="n"/>
+      <c r="H319" s="2" t="n"/>
+      <c r="I319" s="2" t="n"/>
+      <c r="J319" s="2" t="n"/>
+      <c r="K319" s="2" t="n"/>
+      <c r="L319" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M319" t="n">
+        <v>1</v>
+      </c>
+      <c r="R319" t="n">
+        <v>1</v>
+      </c>
+      <c r="S319" t="n">
+        <v>2</v>
+      </c>
+      <c r="T319" t="n">
+        <v>3</v>
+      </c>
+      <c r="U319" t="n">
+        <v>3</v>
+      </c>
+      <c r="V319" t="n">
+        <v>2</v>
+      </c>
+      <c r="W319" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>2907.72</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>105969</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>226780324</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="n"/>
+      <c r="H320" s="2" t="n"/>
+      <c r="I320" s="2" t="n"/>
+      <c r="J320" s="2" t="n"/>
+      <c r="K320" s="2" t="n"/>
+      <c r="L320" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M320" t="n">
+        <v>1</v>
+      </c>
+      <c r="R320" t="n">
+        <v>1</v>
+      </c>
+      <c r="S320" t="n">
+        <v>2</v>
+      </c>
+      <c r="T320" t="n">
+        <v>3</v>
+      </c>
+      <c r="U320" t="n">
+        <v>3</v>
+      </c>
+      <c r="V320" t="n">
+        <v>2</v>
+      </c>
+      <c r="W320" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>2907.72</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>105981</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>226799135</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>TBE004BI</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>TBE004BI</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="n"/>
+      <c r="H321" s="2" t="n"/>
+      <c r="I321" s="2" t="n"/>
+      <c r="J321" s="2" t="n"/>
+      <c r="K321" s="2" t="n"/>
+      <c r="L321" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M321" t="n">
+        <v>1</v>
+      </c>
+      <c r="N321" t="n">
+        <v>1</v>
+      </c>
+      <c r="O321" t="n">
+        <v>3</v>
+      </c>
+      <c r="P321" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>4</v>
+      </c>
+      <c r="R321" t="n">
+        <v>3</v>
+      </c>
+      <c r="S321" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>105981</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>226799136</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="n"/>
+      <c r="H322" s="2" t="n"/>
+      <c r="I322" s="2" t="n"/>
+      <c r="J322" s="2" t="n"/>
+      <c r="K322" s="2" t="n"/>
+      <c r="L322" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M322" t="n">
+        <v>1</v>
+      </c>
+      <c r="N322" t="n">
+        <v>1</v>
+      </c>
+      <c r="O322" t="n">
+        <v>3</v>
+      </c>
+      <c r="P322" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>4</v>
+      </c>
+      <c r="R322" t="n">
+        <v>3</v>
+      </c>
+      <c r="S322" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>105981</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>226799137</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="n"/>
+      <c r="H323" s="2" t="n"/>
+      <c r="I323" s="2" t="n"/>
+      <c r="J323" s="2" t="n"/>
+      <c r="K323" s="2" t="n"/>
+      <c r="L323" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M323" t="n">
+        <v>1</v>
+      </c>
+      <c r="N323" t="n">
+        <v>1</v>
+      </c>
+      <c r="O323" t="n">
+        <v>3</v>
+      </c>
+      <c r="P323" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>4</v>
+      </c>
+      <c r="R323" t="n">
+        <v>3</v>
+      </c>
+      <c r="S323" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>105981</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>226799138</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="n"/>
+      <c r="H324" s="2" t="n"/>
+      <c r="I324" s="2" t="n"/>
+      <c r="J324" s="2" t="n"/>
+      <c r="K324" s="2" t="n"/>
+      <c r="L324" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M324" t="n">
+        <v>1</v>
+      </c>
+      <c r="N324" t="n">
+        <v>1</v>
+      </c>
+      <c r="O324" t="n">
+        <v>3</v>
+      </c>
+      <c r="P324" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>4</v>
+      </c>
+      <c r="R324" t="n">
+        <v>3</v>
+      </c>
+      <c r="S324" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>105970</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>188221170</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>GBE969</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>GBE969CF</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>GBE969CF</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L325" t="n">
+        <v>232.46</v>
+      </c>
+      <c r="M325" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>697.38</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>105970</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>20992</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>GBE969</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>GBE969PT</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>GBE969PT</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L326" t="n">
+        <v>232.46</v>
+      </c>
+      <c r="M326" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>697.38</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>105980</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>212925759</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SSU029</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>SSU029BC</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SSU029BC</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L327" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="M327" t="n">
+        <v>1</v>
+      </c>
+      <c r="R327" t="n">
+        <v>1</v>
+      </c>
+      <c r="S327" t="n">
+        <v>3</v>
+      </c>
+      <c r="T327" t="n">
+        <v>4</v>
+      </c>
+      <c r="U327" t="n">
+        <v>4</v>
+      </c>
+      <c r="V327" t="n">
+        <v>3</v>
+      </c>
+      <c r="W327" t="n">
+        <v>2</v>
+      </c>
+      <c r="X327" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>1798.56</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>105980</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>212925785</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SSU119</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>SSU119TN</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>SSU119TN</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L328" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="M328" t="n">
+        <v>1</v>
+      </c>
+      <c r="R328" t="n">
+        <v>1</v>
+      </c>
+      <c r="S328" t="n">
+        <v>3</v>
+      </c>
+      <c r="T328" t="n">
+        <v>4</v>
+      </c>
+      <c r="U328" t="n">
+        <v>4</v>
+      </c>
+      <c r="V328" t="n">
+        <v>3</v>
+      </c>
+      <c r="W328" t="n">
+        <v>2</v>
+      </c>
+      <c r="X328" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>1798.56</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>105971</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>114226724</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>GBF065</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>GBF065OW</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>GBF065OW</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J329" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L329" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="M329" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>691.2</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>105971</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>147957731</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>GMO404</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>GMO404PT</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>GMO404PT</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J330" t="n">
+        <v>699.9</v>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L330" t="n">
+        <v>240</v>
+      </c>
+      <c r="M330" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>105971</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>12078368</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J331" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L331" t="n">
+        <v>348</v>
+      </c>
+      <c r="M331" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>105971</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>12078369</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J332" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L332" t="n">
+        <v>348</v>
+      </c>
+      <c r="M332" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>105979</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>69427205</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>SAF125</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>SAF125PT</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>SAF125PT</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J333" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L333" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="M333" t="n">
+        <v>1</v>
+      </c>
+      <c r="R333" t="n">
+        <v>1</v>
+      </c>
+      <c r="S333" t="n">
+        <v>3</v>
+      </c>
+      <c r="T333" t="n">
+        <v>4</v>
+      </c>
+      <c r="U333" t="n">
+        <v>4</v>
+      </c>
+      <c r="V333" t="n">
+        <v>3</v>
+      </c>
+      <c r="W333" t="n">
+        <v>2</v>
+      </c>
+      <c r="X333" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>2435.4</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>105979</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>227068437</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SAF126</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>SAF126BK</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>SAF126BK</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="n"/>
+      <c r="H334" s="2" t="n"/>
+      <c r="I334" s="2" t="n"/>
+      <c r="J334" s="2" t="n"/>
+      <c r="K334" s="2" t="n"/>
+      <c r="L334" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="M334" t="n">
+        <v>1</v>
+      </c>
+      <c r="R334" t="n">
+        <v>2</v>
+      </c>
+      <c r="S334" t="n">
+        <v>4</v>
+      </c>
+      <c r="T334" t="n">
+        <v>5</v>
+      </c>
+      <c r="U334" t="n">
+        <v>5</v>
+      </c>
+      <c r="V334" t="n">
+        <v>4</v>
+      </c>
+      <c r="W334" t="n">
+        <v>3</v>
+      </c>
+      <c r="X334" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>3247.2</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>105979</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>226787944</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>SRT028</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>SRT028BK</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>SRT028BK</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="n"/>
+      <c r="H335" s="2" t="n"/>
+      <c r="I335" s="2" t="n"/>
+      <c r="J335" s="2" t="n"/>
+      <c r="K335" s="2" t="n"/>
+      <c r="L335" t="n">
+        <v>159.78</v>
+      </c>
+      <c r="M335" t="n">
+        <v>1</v>
+      </c>
+      <c r="R335" t="n">
+        <v>1</v>
+      </c>
+      <c r="S335" t="n">
+        <v>3</v>
+      </c>
+      <c r="T335" t="n">
+        <v>4</v>
+      </c>
+      <c r="U335" t="n">
+        <v>4</v>
+      </c>
+      <c r="V335" t="n">
+        <v>3</v>
+      </c>
+      <c r="W335" t="n">
+        <v>2</v>
+      </c>
+      <c r="X335" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>2876.04</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>105979</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>99645682</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>WSC003</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>WSC003OW</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>WSC003OW</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L336" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="M336" t="n">
+        <v>1</v>
+      </c>
+      <c r="O336" t="n">
+        <v>2</v>
+      </c>
+      <c r="P336" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>2</v>
+      </c>
+      <c r="R336" t="n">
+        <v>2</v>
+      </c>
+      <c r="S336" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>1243.8</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>105979</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>223147116</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>WSC767</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>WSC767TP</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>WSC767TP</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L337" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="M337" t="n">
+        <v>1</v>
+      </c>
+      <c r="N337" t="n">
+        <v>2</v>
+      </c>
+      <c r="O337" t="n">
+        <v>4</v>
+      </c>
+      <c r="P337" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>6</v>
+      </c>
+      <c r="R337" t="n">
+        <v>4</v>
+      </c>
+      <c r="S337" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>3542.4</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>226773022</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="n"/>
+      <c r="H338" s="2" t="n"/>
+      <c r="I338" s="2" t="n"/>
+      <c r="J338" s="2" t="n"/>
+      <c r="K338" s="2" t="n"/>
+      <c r="L338" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M338" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>485.98</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>226773023</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="n"/>
+      <c r="H339" s="2" t="n"/>
+      <c r="I339" s="2" t="n"/>
+      <c r="J339" s="2" t="n"/>
+      <c r="K339" s="2" t="n"/>
+      <c r="L339" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M339" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>485.98</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>226773071</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>GBF269</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="n"/>
+      <c r="H340" s="2" t="n"/>
+      <c r="I340" s="2" t="n"/>
+      <c r="J340" s="2" t="n"/>
+      <c r="K340" s="2" t="n"/>
+      <c r="L340" t="n">
+        <v>235</v>
+      </c>
+      <c r="M340" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>218687255</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L341" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M341" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>736.02</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>58174815</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L342" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M342" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>736.02</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>226773215</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>GBF786</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="n"/>
+      <c r="H343" s="2" t="n"/>
+      <c r="I343" s="2" t="n"/>
+      <c r="J343" s="2" t="n"/>
+      <c r="K343" s="2" t="n"/>
+      <c r="L343" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="M343" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>602.0700000000001</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>226773217</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="n"/>
+      <c r="H344" s="2" t="n"/>
+      <c r="I344" s="2" t="n"/>
+      <c r="J344" s="2" t="n"/>
+      <c r="K344" s="2" t="n"/>
+      <c r="L344" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M344" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>828.36</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>226773218</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="n"/>
+      <c r="H345" s="2" t="n"/>
+      <c r="I345" s="2" t="n"/>
+      <c r="J345" s="2" t="n"/>
+      <c r="K345" s="2" t="n"/>
+      <c r="L345" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M345" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>828.36</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>177646295</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>GBF827</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J346" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L346" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="M346" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>514.6799999999999</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>137476322</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>GSN810</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>GSN810PT</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>GSN810PT</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J347" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L347" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="M347" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>733.2</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>147957944</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>GSN811</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>GSN811PT</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>GSN811PT</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J348" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L348" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="M348" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>370.14</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>147957945</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>GSN811</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>GSN811TN</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>GSN811TN</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J349" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L349" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="M349" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>370.14</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>12714422</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>HNM234</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>HNM234PT</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>HNM234PT</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J350" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L350" t="n">
+        <v>91.61</v>
+      </c>
+      <c r="M350" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>183.22</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>105972</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>12714423</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>HNM234</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>HNM234WK</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>HNM234WK</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J351" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L351" t="n">
+        <v>91.61</v>
+      </c>
+      <c r="M351" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>183.22</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>105978</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>226773909</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>PAX634</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="n"/>
+      <c r="H352" s="2" t="n"/>
+      <c r="I352" s="2" t="n"/>
+      <c r="J352" s="2" t="n"/>
+      <c r="K352" s="2" t="n"/>
+      <c r="L352" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="M352" t="n">
+        <v>1</v>
+      </c>
+      <c r="N352" t="n">
+        <v>1</v>
+      </c>
+      <c r="O352" t="n">
+        <v>3</v>
+      </c>
+      <c r="P352" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>4</v>
+      </c>
+      <c r="R352" t="n">
+        <v>2</v>
+      </c>
+      <c r="S352" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>1521.45</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>105978</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>178969123</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>PRA127</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>PRA127CF</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>PRA127CF</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>SANDALIA RASTEIRA</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J353" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L353" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="M353" t="n">
+        <v>1</v>
+      </c>
+      <c r="N353" t="n">
+        <v>2</v>
+      </c>
+      <c r="O353" t="n">
+        <v>3</v>
+      </c>
+      <c r="P353" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>4</v>
+      </c>
+      <c r="R353" t="n">
+        <v>2</v>
+      </c>
+      <c r="S353" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>1100.34</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>105978</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>226774175</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="n"/>
+      <c r="H354" s="2" t="n"/>
+      <c r="I354" s="2" t="n"/>
+      <c r="J354" s="2" t="n"/>
+      <c r="K354" s="2" t="n"/>
+      <c r="L354" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M354" t="n">
+        <v>1</v>
+      </c>
+      <c r="N354" t="n">
+        <v>1</v>
+      </c>
+      <c r="O354" t="n">
+        <v>3</v>
+      </c>
+      <c r="P354" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>4</v>
+      </c>
+      <c r="R354" t="n">
+        <v>3</v>
+      </c>
+      <c r="S354" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>1276.74</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>105978</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>226774176</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="n"/>
+      <c r="H355" s="2" t="n"/>
+      <c r="I355" s="2" t="n"/>
+      <c r="J355" s="2" t="n"/>
+      <c r="K355" s="2" t="n"/>
+      <c r="L355" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M355" t="n">
+        <v>1</v>
+      </c>
+      <c r="N355" t="n">
+        <v>1</v>
+      </c>
+      <c r="O355" t="n">
+        <v>2</v>
+      </c>
+      <c r="P355" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>3</v>
+      </c>
+      <c r="R355" t="n">
+        <v>2</v>
+      </c>
+      <c r="S355" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>851.16</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>105978</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>226799120</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>TBC207</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="n"/>
+      <c r="H356" s="2" t="n"/>
+      <c r="I356" s="2" t="n"/>
+      <c r="J356" s="2" t="n"/>
+      <c r="K356" s="2" t="n"/>
+      <c r="L356" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="M356" t="n">
+        <v>1</v>
+      </c>
+      <c r="N356" t="n">
+        <v>1</v>
+      </c>
+      <c r="O356" t="n">
+        <v>3</v>
+      </c>
+      <c r="P356" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>4</v>
+      </c>
+      <c r="R356" t="n">
+        <v>3</v>
+      </c>
+      <c r="S356" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>1025.28</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>105966</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>99069557</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>AFB130</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>AFB130TC</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>AFB130TC</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J357" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L357" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="M357" t="n">
+        <v>1</v>
+      </c>
+      <c r="S357" t="n">
+        <v>4</v>
+      </c>
+      <c r="T357" t="n">
+        <v>2</v>
+      </c>
+      <c r="U357" t="n">
+        <v>2</v>
+      </c>
+      <c r="V357" t="n">
+        <v>6</v>
+      </c>
+      <c r="W357" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>2053.8</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>105966</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>21043</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ASF711</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ASF711CF</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>ASF711CF</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J358" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L358" t="n">
+        <v>74.66</v>
+      </c>
+      <c r="M358" t="n">
+        <v>1</v>
+      </c>
+      <c r="R358" t="n">
+        <v>1</v>
+      </c>
+      <c r="S358" t="n">
+        <v>3</v>
+      </c>
+      <c r="T358" t="n">
+        <v>4</v>
+      </c>
+      <c r="U358" t="n">
+        <v>4</v>
+      </c>
+      <c r="V358" t="n">
+        <v>3</v>
+      </c>
+      <c r="W358" t="n">
+        <v>2</v>
+      </c>
+      <c r="X358" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>1343.88</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>105966</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>63032743</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>PRAD44</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>PRAD44TP</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>PRAD44TP</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>SANDALIA BIRKEN</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J359" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L359" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="M359" t="n">
+        <v>1</v>
+      </c>
+      <c r="N359" t="n">
+        <v>1</v>
+      </c>
+      <c r="O359" t="n">
+        <v>5</v>
+      </c>
+      <c r="P359" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>4</v>
+      </c>
+      <c r="R359" t="n">
+        <v>2</v>
+      </c>
+      <c r="S359" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>2150.28</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>105966</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>226799440</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>WSCR54</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="n"/>
+      <c r="H360" s="2" t="n"/>
+      <c r="I360" s="2" t="n"/>
+      <c r="J360" s="2" t="n"/>
+      <c r="K360" s="2" t="n"/>
+      <c r="L360" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="M360" t="n">
+        <v>1</v>
+      </c>
+      <c r="N360" t="n">
+        <v>1</v>
+      </c>
+      <c r="O360" t="n">
+        <v>2</v>
+      </c>
+      <c r="P360" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>2</v>
+      </c>
+      <c r="R360" t="n">
+        <v>1</v>
+      </c>
+      <c r="S360" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>1905.12</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>105966</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>226799445</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>WSCR57</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="n"/>
+      <c r="H361" s="2" t="n"/>
+      <c r="I361" s="2" t="n"/>
+      <c r="J361" s="2" t="n"/>
+      <c r="K361" s="2" t="n"/>
+      <c r="L361" t="n">
+        <v>159.25</v>
+      </c>
+      <c r="M361" t="n">
+        <v>1</v>
+      </c>
+      <c r="N361" t="n">
+        <v>1</v>
+      </c>
+      <c r="O361" t="n">
+        <v>3</v>
+      </c>
+      <c r="P361" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>5</v>
+      </c>
+      <c r="R361" t="n">
+        <v>3</v>
+      </c>
+      <c r="S361" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>2866.5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>105966</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>226799459</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>WSCR89</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="n"/>
+      <c r="H362" s="2" t="n"/>
+      <c r="I362" s="2" t="n"/>
+      <c r="J362" s="2" t="n"/>
+      <c r="K362" s="2" t="n"/>
+      <c r="L362" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="M362" t="n">
+        <v>1</v>
+      </c>
+      <c r="N362" t="n">
+        <v>1</v>
+      </c>
+      <c r="O362" t="n">
+        <v>3</v>
+      </c>
+      <c r="P362" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>5</v>
+      </c>
+      <c r="R362" t="n">
+        <v>3</v>
+      </c>
+      <c r="S362" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>2908.44</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>105973</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>13224</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J363" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L363" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M363" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>508.54</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>105973</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>138654476</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>MCC008</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>MCC008PT</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>MCC008PT</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J364" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L364" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="M364" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>468.48</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>105973</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>138654477</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>MCC008</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>MCC008TN</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>MCC008TN</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J365" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L365" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="M365" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>468.48</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>105977</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>156352241</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>PABR56</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>PABR56CM</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>PABR56CM</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J366" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L366" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M366" t="n">
+        <v>1</v>
+      </c>
+      <c r="N366" t="n">
+        <v>1</v>
+      </c>
+      <c r="O366" t="n">
+        <v>3</v>
+      </c>
+      <c r="P366" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>3</v>
+      </c>
+      <c r="R366" t="n">
+        <v>3</v>
+      </c>
+      <c r="S366" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>1819.2</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>105977</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>156352245</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>PABR58</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>PABR58PT</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>PABR58PT</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J367" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L367" t="n">
+        <v>136.59</v>
+      </c>
+      <c r="M367" t="n">
+        <v>1</v>
+      </c>
+      <c r="O367" t="n">
+        <v>2</v>
+      </c>
+      <c r="P367" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>2</v>
+      </c>
+      <c r="R367" t="n">
+        <v>2</v>
+      </c>
+      <c r="S367" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>1639.08</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>105977</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>156352246</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>PABR58</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>PABR58TN</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>PABR58TN</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J368" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L368" t="n">
+        <v>136.59</v>
+      </c>
+      <c r="M368" t="n">
+        <v>1</v>
+      </c>
+      <c r="N368" t="n">
+        <v>1</v>
+      </c>
+      <c r="O368" t="n">
+        <v>1</v>
+      </c>
+      <c r="P368" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>2</v>
+      </c>
+      <c r="R368" t="n">
+        <v>2</v>
+      </c>
+      <c r="S368" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>1639.08</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>105977</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>226773817</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>PABR80</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="n"/>
+      <c r="H369" s="2" t="n"/>
+      <c r="I369" s="2" t="n"/>
+      <c r="J369" s="2" t="n"/>
+      <c r="K369" s="2" t="n"/>
+      <c r="L369" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="M369" t="n">
+        <v>1</v>
+      </c>
+      <c r="N369" t="n">
+        <v>1</v>
+      </c>
+      <c r="O369" t="n">
+        <v>3</v>
+      </c>
+      <c r="P369" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>5</v>
+      </c>
+      <c r="R369" t="n">
+        <v>3</v>
+      </c>
+      <c r="S369" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA369" t="n">
+        <v>2557.8</v>
       </c>
     </row>
   </sheetData>
@@ -20425,7 +25468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21180,11 +26223,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105844</v>
+        <v>105966</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -21194,7 +26237,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-18h37.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -21203,35 +26246,35 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G21" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>16482.63</v>
+        <v>13228.02</v>
       </c>
       <c r="I21" t="n">
-        <v>16482.63</v>
+        <v>13228.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105845</v>
+        <v>105967</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
+          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-18h38.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -21240,35 +26283,35 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="H22" t="n">
-        <v>11429.01</v>
+        <v>2509.65</v>
       </c>
       <c r="I22" t="n">
-        <v>11429.01</v>
+        <v>2509.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105846</v>
+        <v>105968</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+          <t>WW EXPORT LTDA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-18h38.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -21277,35 +26320,35 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="H23" t="n">
-        <v>10793.25</v>
+        <v>10180.8</v>
       </c>
       <c r="I23" t="n">
-        <v>10793.25</v>
+        <v>10180.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105848</v>
+        <v>105969</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-18h38.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -21314,35 +26357,35 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="H24" t="n">
-        <v>1642.8</v>
+        <v>15468.48</v>
       </c>
       <c r="I24" t="n">
-        <v>1642.8</v>
+        <v>15468.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105849</v>
+        <v>105970</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N3_RelB2bCarrinhoExcel-18h47.xlsx</t>
+          <t>5_RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -21351,35 +26394,35 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>6516.57</v>
+        <v>1394.76</v>
       </c>
       <c r="I25" t="n">
-        <v>6516.57</v>
+        <v>1394.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105851</v>
+        <v>105971</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-18h39.xlsx</t>
+          <t>6_RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -21388,35 +26431,35 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>1496.07</v>
+        <v>2563.2</v>
       </c>
       <c r="I26" t="n">
-        <v>1496.07</v>
+        <v>2563.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105852</v>
+        <v>105972</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PRIMAR IND TEXTIL LTDA</t>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N2_RelB2bCarrinhoExcel-18h46.xlsx</t>
+          <t>7_RelB2bCarrinhoExcel-19h10.xlsx</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -21425,35 +26468,35 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>276</v>
+        <v>56</v>
       </c>
       <c r="G27" t="n">
-        <v>276</v>
+        <v>56</v>
       </c>
       <c r="H27" t="n">
-        <v>4425</v>
+        <v>7762.39</v>
       </c>
       <c r="I27" t="n">
-        <v>4425</v>
+        <v>7762.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105853</v>
+        <v>105973</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L T BERTOLANI CONFECCAO</t>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-18h40.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -21462,35 +26505,35 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>1433.52</v>
+        <v>1445.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1433.52</v>
+        <v>1445.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105854</v>
+        <v>105974</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>PRIMAR IND TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-18h40.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h12.xlsx</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -21499,72 +26542,61 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="G29" t="n">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="H29" t="n">
-        <v>5385.12</v>
+        <v>2600.76</v>
       </c>
       <c r="I29" t="n">
-        <v>5385.12</v>
+        <v>2600.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105855</v>
+        <v>105975</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WW EXPORT LTDA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>4_RelB2bCarrinhoExcel-18h40.xlsx</t>
+          <t>COURO &amp; ARTE LTDA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>SEM ARQUIVO</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
-      </c>
-      <c r="G30" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H30" t="n">
-        <v>4210.95</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4210.95</v>
+        <v>470.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105856</v>
+        <v>105976</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+          <t>CALCADOS KARYBY LTDA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-18h41.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h12.xlsx</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -21573,35 +26605,35 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>3857.34</v>
+        <v>1791.72</v>
       </c>
       <c r="I31" t="n">
-        <v>3857.34</v>
+        <v>1791.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105857</v>
+        <v>105977</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D MATTHES CALCADOS LTDA</t>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-18h41.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h12.xlsx</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -21610,35 +26642,35 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G32" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="H32" t="n">
-        <v>4311.6</v>
+        <v>7655.16</v>
       </c>
       <c r="I32" t="n">
-        <v>4311.6</v>
+        <v>7655.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105858</v>
+        <v>105978</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SH. NOVA AMERICA</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MASSEY CALCADOS LTDA</t>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-18h41.xlsx</t>
+          <t>7_RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -21647,35 +26679,35 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="G33" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="H33" t="n">
-        <v>3368.7</v>
+        <v>5774.97</v>
       </c>
       <c r="I33" t="n">
-        <v>3368.7</v>
+        <v>5774.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105711</v>
+        <v>105979</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
+          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-18h59.xlsx</t>
+          <t>6_RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -21684,109 +26716,109 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="G34" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="H34" t="n">
-        <v>8028.27</v>
+        <v>13344.84</v>
       </c>
       <c r="I34" t="n">
-        <v>8028.27</v>
+        <v>13344.84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105712</v>
+        <v>105980</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>ZOTTO CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>5_RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="G35" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="H35" t="n">
-        <v>10472.17</v>
+        <v>3597.12</v>
       </c>
       <c r="I35" t="n">
-        <v>6141.03</v>
+        <v>3597.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105718</v>
+        <v>105981</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+          <t>D MATTHES CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G36" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H36" t="n">
-        <v>6969.69</v>
+        <v>4383.36</v>
       </c>
       <c r="I36" t="n">
-        <v>6308.13</v>
+        <v>4383.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105719</v>
+        <v>105982</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WW EXPORT LTDA</t>
+          <t>N C CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -21795,72 +26827,72 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="G37" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="H37" t="n">
-        <v>11962.41</v>
+        <v>2469.6</v>
       </c>
       <c r="I37" t="n">
-        <v>11962.41</v>
+        <v>2469.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105720</v>
+        <v>105983</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. PLAZA NITEROI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
+          <t>MASSEY CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h11.xlsx</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="G38" t="n">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="H38" t="n">
-        <v>10980.3</v>
+        <v>13389.84</v>
       </c>
       <c r="I38" t="n">
-        <v>5077.98</v>
+        <v>13389.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105721</v>
+        <v>105844</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>N C CALCADOS LTDA</t>
+          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>RelB2bCarrinhoExcel-18h37.xlsx</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -21869,35 +26901,35 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G39" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="H39" t="n">
-        <v>7743.33</v>
+        <v>16482.63</v>
       </c>
       <c r="I39" t="n">
-        <v>7743.33</v>
+        <v>16482.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105722</v>
+        <v>105845</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MASSEY CALCADOS LTDA</t>
+          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5876a4d7-RelB2bCarrinhoExcel-19h04.xlsx</t>
+          <t>RelB2bCarrinhoExcel-18h38.xlsx</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -21906,35 +26938,35 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="G40" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="H40" t="n">
-        <v>10669.74</v>
+        <v>11429.01</v>
       </c>
       <c r="I40" t="n">
-        <v>10669.74</v>
+        <v>11429.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105723</v>
+        <v>105846</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CALCADOS KISSOL LTDA</t>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-18h38.xlsx</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -21943,35 +26975,35 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H41" t="n">
-        <v>1808.1</v>
+        <v>10793.25</v>
       </c>
       <c r="I41" t="n">
-        <v>1808.1</v>
+        <v>10793.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105724</v>
+        <v>105848</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-18h38.xlsx</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -21980,146 +27012,146 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>4294.07</v>
+        <v>1642.8</v>
       </c>
       <c r="I42" t="n">
-        <v>4294.07</v>
+        <v>1642.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105725</v>
+        <v>105849</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>N3_RelB2bCarrinhoExcel-18h47.xlsx</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="H43" t="n">
-        <v>2557.06</v>
+        <v>6516.57</v>
       </c>
       <c r="I43" t="n">
-        <v>1162.3</v>
+        <v>6516.57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105726</v>
+        <v>105851</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>RelB2bCarrinhoExcel-18h39.xlsx</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G44" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H44" t="n">
-        <v>2536.8</v>
+        <v>1496.07</v>
       </c>
       <c r="I44" t="n">
-        <v>2068.8</v>
+        <v>1496.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105731</v>
+        <v>105852</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+          <t>PRIMAR IND TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>N2_RelB2bCarrinhoExcel-18h46.xlsx</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>78</v>
+        <v>276</v>
       </c>
       <c r="G45" t="n">
-        <v>36</v>
+        <v>276</v>
       </c>
       <c r="H45" t="n">
-        <v>18594.4</v>
+        <v>4425</v>
       </c>
       <c r="I45" t="n">
-        <v>7822.8</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>105960</v>
+        <v>105853</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
+          <t>L T BERTOLANI CONFECCAO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-18h40.xlsx</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -22128,35 +27160,35 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="G46" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H46" t="n">
-        <v>1930.5</v>
+        <v>1433.52</v>
       </c>
       <c r="I46" t="n">
-        <v>1930.5</v>
+        <v>1433.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>105961</v>
+        <v>105854</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
+          <t>CALCADOS KARYBY LTDA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-18h40.xlsx</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -22165,35 +27197,35 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G47" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H47" t="n">
-        <v>8954.1</v>
+        <v>5385.12</v>
       </c>
       <c r="I47" t="n">
-        <v>8954.1</v>
+        <v>5385.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>105962</v>
+        <v>105855</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+          <t>WW EXPORT LTDA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-18h40.xlsx</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -22202,35 +27234,35 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H48" t="n">
-        <v>1017.08</v>
+        <v>4210.95</v>
       </c>
       <c r="I48" t="n">
-        <v>1017.08</v>
+        <v>4210.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>105963</v>
+        <v>105856</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PRIMAR IND TEXTIL LTDA</t>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>RelB2bCarrinhoExcel-18h41.xlsx</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -22239,35 +27271,35 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="G49" t="n">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="H49" t="n">
-        <v>2596.2</v>
+        <v>3857.34</v>
       </c>
       <c r="I49" t="n">
-        <v>2596.2</v>
+        <v>3857.34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>105964</v>
+        <v>105857</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L T BERTOLANI CONFECCAO</t>
+          <t>D MATTHES CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-18h41.xlsx</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -22276,35 +27308,35 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="G50" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="H50" t="n">
-        <v>2377.68</v>
+        <v>4311.6</v>
       </c>
       <c r="I50" t="n">
-        <v>2377.68</v>
+        <v>4311.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>105965</v>
+        <v>105858</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. NOVA AMERICA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D MATTHES CALCADOS LTDA</t>
+          <t>MASSEY CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h03.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-18h41.xlsx</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -22313,35 +27345,35 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G51" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H51" t="n">
-        <v>3287.52</v>
+        <v>3368.7</v>
       </c>
       <c r="I51" t="n">
-        <v>3287.52</v>
+        <v>3368.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>105838</v>
+        <v>105711</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>RelB2bCarrinhoExcel-18h59.xlsx</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -22350,109 +27382,109 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="H52" t="n">
-        <v>864.8099999999999</v>
+        <v>8028.27</v>
       </c>
       <c r="I52" t="n">
-        <v>864.8099999999999</v>
+        <v>8028.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>105839</v>
+        <v>105712</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>CALCADOS KARYBY LTDA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H53" t="n">
-        <v>1044</v>
+        <v>10472.17</v>
       </c>
       <c r="I53" t="n">
-        <v>1044</v>
+        <v>6141.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>105840</v>
+        <v>105718</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="H54" t="n">
-        <v>254.27</v>
+        <v>6969.69</v>
       </c>
       <c r="I54" t="n">
-        <v>254.27</v>
+        <v>6308.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>105841</v>
+        <v>105719</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>WW EXPORT LTDA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -22461,89 +27493,755 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="G55" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="H55" t="n">
-        <v>3267.72</v>
+        <v>11962.41</v>
       </c>
       <c r="I55" t="n">
-        <v>3267.72</v>
+        <v>11962.41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>105842</v>
+        <v>105720</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WW EXPORT LTDA</t>
+          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G56" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H56" t="n">
-        <v>2095.92</v>
+        <v>10980.3</v>
       </c>
       <c r="I56" t="n">
-        <v>2095.92</v>
+        <v>5077.98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>105721</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>N C CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>78</v>
+      </c>
+      <c r="G57" t="n">
+        <v>78</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7743.33</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7743.33</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>105722</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MASSEY CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5876a4d7-RelB2bCarrinhoExcel-19h04.xlsx</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>114</v>
+      </c>
+      <c r="G58" t="n">
+        <v>114</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10669.74</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10669.74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>105723</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CALCADOS KISSOL LTDA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6_RelB2bCarrinhoExcel-19h00.xlsx</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1808.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1808.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>105724</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>28</v>
+      </c>
+      <c r="G60" t="n">
+        <v>28</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4294.07</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4294.07</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>105725</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>11</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2557.06</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1162.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>105726</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>10</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2536.8</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2068.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>105731</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>78</v>
+      </c>
+      <c r="G63" t="n">
+        <v>36</v>
+      </c>
+      <c r="H63" t="n">
+        <v>18594.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7822.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>105960</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h01.xlsx</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>30</v>
+      </c>
+      <c r="G64" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1930.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>105961</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>54</v>
+      </c>
+      <c r="G65" t="n">
+        <v>54</v>
+      </c>
+      <c r="H65" t="n">
+        <v>8954.1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>8954.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>105962</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1017.08</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1017.08</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>105963</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PRIMAR IND TEXTIL LTDA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>156</v>
+      </c>
+      <c r="G67" t="n">
+        <v>156</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2596.2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2596.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>105964</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>L T BERTOLANI CONFECCAO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6_RelB2bCarrinhoExcel-19h02.xlsx</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>120</v>
+      </c>
+      <c r="G68" t="n">
+        <v>120</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2377.68</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2377.68</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>105965</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SH. ELDORADO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>D MATTHES CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h03.xlsx</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>54</v>
+      </c>
+      <c r="G69" t="n">
+        <v>54</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3287.52</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3287.52</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>864.8099999999999</v>
+      </c>
+      <c r="I70" t="n">
+        <v>864.8099999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>105839</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>105840</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="I72" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>27</v>
+      </c>
+      <c r="G73" t="n">
+        <v>27</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3267.72</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3267.72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>WW EXPORT LTDA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>27</v>
+      </c>
+      <c r="G74" t="n">
+        <v>27</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2095.92</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2095.92</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
         <v>105843</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>SH. PARK SUL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>RelB2bCarrinhoExcel-19h08.xlsx</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="F75" t="n">
         <v>9</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G75" t="n">
         <v>9</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H75" t="n">
         <v>2180.79</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I75" t="n">
         <v>2180.79</v>
       </c>
     </row>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA369"/>
+  <dimension ref="A1:AA435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25455,6 +25455,4227 @@
       </c>
       <c r="AA369" t="n">
         <v>2557.8</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>114226724</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>GBF065</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>GBF065OW</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>GBF065OW</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J370" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L370" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="M370" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>460.8</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>73909424</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>GBF529</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>GBF529PT</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>GBF529PT</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J371" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L371" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="M371" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>230.4</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>73909425</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>GBF529</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>GBF529TN</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>GBF529TN</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J372" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L372" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="M372" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y372" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>460.8</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>948266</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>HBV022</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>HBV022CF</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>HBV022CF</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J373" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L373" t="n">
+        <v>228</v>
+      </c>
+      <c r="M373" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y373" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z373" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>941332</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>HBV022</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>HBV022PT</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>HBV022PT</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J374" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L374" t="n">
+        <v>228</v>
+      </c>
+      <c r="M374" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y374" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z374" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>12078368</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J375" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L375" t="n">
+        <v>348</v>
+      </c>
+      <c r="M375" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>12078369</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J376" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L376" t="n">
+        <v>348</v>
+      </c>
+      <c r="M376" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y376" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>105913</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>227869440</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="n"/>
+      <c r="H377" s="2" t="n"/>
+      <c r="I377" s="2" t="n"/>
+      <c r="J377" s="2" t="n"/>
+      <c r="K377" s="2" t="n"/>
+      <c r="L377" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="M377" t="n">
+        <v>1</v>
+      </c>
+      <c r="N377" t="n">
+        <v>1</v>
+      </c>
+      <c r="O377" t="n">
+        <v>3</v>
+      </c>
+      <c r="P377" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>3</v>
+      </c>
+      <c r="R377" t="n">
+        <v>3</v>
+      </c>
+      <c r="S377" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z377" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA377" t="n">
+        <v>2239.65</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>105913</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>164260186</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>WCL099</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J378" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L378" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="M378" t="n">
+        <v>1</v>
+      </c>
+      <c r="N378" t="n">
+        <v>1</v>
+      </c>
+      <c r="O378" t="n">
+        <v>3</v>
+      </c>
+      <c r="P378" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>3</v>
+      </c>
+      <c r="R378" t="n">
+        <v>3</v>
+      </c>
+      <c r="S378" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z378" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA378" t="n">
+        <v>1336.05</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>105913</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>226799259</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>WCL202</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>WCL202CA</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>WCL202CA</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="n"/>
+      <c r="H379" s="2" t="n"/>
+      <c r="I379" s="2" t="n"/>
+      <c r="J379" s="2" t="n"/>
+      <c r="K379" s="2" t="n"/>
+      <c r="L379" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="M379" t="n">
+        <v>1</v>
+      </c>
+      <c r="N379" t="n">
+        <v>1</v>
+      </c>
+      <c r="O379" t="n">
+        <v>3</v>
+      </c>
+      <c r="P379" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>4</v>
+      </c>
+      <c r="R379" t="n">
+        <v>2</v>
+      </c>
+      <c r="S379" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z379" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA379" t="n">
+        <v>1870.5</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>105913</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>226799260</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>WCL203</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>WCL203CF</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>WCL203CF</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="n"/>
+      <c r="H380" s="2" t="n"/>
+      <c r="I380" s="2" t="n"/>
+      <c r="J380" s="2" t="n"/>
+      <c r="K380" s="2" t="n"/>
+      <c r="L380" t="n">
+        <v>145.33</v>
+      </c>
+      <c r="M380" t="n">
+        <v>1</v>
+      </c>
+      <c r="N380" t="n">
+        <v>1</v>
+      </c>
+      <c r="O380" t="n">
+        <v>3</v>
+      </c>
+      <c r="P380" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>4</v>
+      </c>
+      <c r="R380" t="n">
+        <v>2</v>
+      </c>
+      <c r="S380" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z380" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA380" t="n">
+        <v>2179.95</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>105919</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>226799278</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="n"/>
+      <c r="H381" s="2" t="n"/>
+      <c r="I381" s="2" t="n"/>
+      <c r="J381" s="2" t="n"/>
+      <c r="K381" s="2" t="n"/>
+      <c r="L381" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M381" t="n">
+        <v>1</v>
+      </c>
+      <c r="N381" t="n">
+        <v>2</v>
+      </c>
+      <c r="O381" t="n">
+        <v>4</v>
+      </c>
+      <c r="P381" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>6</v>
+      </c>
+      <c r="R381" t="n">
+        <v>4</v>
+      </c>
+      <c r="S381" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z381" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA381" t="n">
+        <v>1639.68</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>105919</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>137619676</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J382" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L382" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M382" t="n">
+        <v>1</v>
+      </c>
+      <c r="N382" t="n">
+        <v>1</v>
+      </c>
+      <c r="O382" t="n">
+        <v>1</v>
+      </c>
+      <c r="P382" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>6</v>
+      </c>
+      <c r="R382" t="n">
+        <v>2</v>
+      </c>
+      <c r="S382" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z382" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA382" t="n">
+        <v>1782.45</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>105919</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>170929723</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>WSCR61FD</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>WSCR61FD</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J383" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L383" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M383" t="n">
+        <v>1</v>
+      </c>
+      <c r="N383" t="n">
+        <v>1</v>
+      </c>
+      <c r="O383" t="n">
+        <v>3</v>
+      </c>
+      <c r="P383" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>4</v>
+      </c>
+      <c r="R383" t="n">
+        <v>2</v>
+      </c>
+      <c r="S383" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>1782.45</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>226773022</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="n"/>
+      <c r="H384" s="2" t="n"/>
+      <c r="I384" s="2" t="n"/>
+      <c r="J384" s="2" t="n"/>
+      <c r="K384" s="2" t="n"/>
+      <c r="L384" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M384" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y384" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z384" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA384" t="n">
+        <v>485.98</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>226773023</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="n"/>
+      <c r="H385" s="2" t="n"/>
+      <c r="I385" s="2" t="n"/>
+      <c r="J385" s="2" t="n"/>
+      <c r="K385" s="2" t="n"/>
+      <c r="L385" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M385" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>485.98</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>226773053</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>GBF253</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>GBF253PT</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>GBF253PT</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="n"/>
+      <c r="H386" s="2" t="n"/>
+      <c r="I386" s="2" t="n"/>
+      <c r="J386" s="2" t="n"/>
+      <c r="K386" s="2" t="n"/>
+      <c r="L386" t="n">
+        <v>191.29</v>
+      </c>
+      <c r="M386" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>191.29</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>226773054</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>GBF253</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>GBF253TN</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>GBF253TN</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="n"/>
+      <c r="H387" s="2" t="n"/>
+      <c r="I387" s="2" t="n"/>
+      <c r="J387" s="2" t="n"/>
+      <c r="K387" s="2" t="n"/>
+      <c r="L387" t="n">
+        <v>191.29</v>
+      </c>
+      <c r="M387" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y387" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z387" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA387" t="n">
+        <v>191.29</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>226773071</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>GBF269</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="n"/>
+      <c r="H388" s="2" t="n"/>
+      <c r="I388" s="2" t="n"/>
+      <c r="J388" s="2" t="n"/>
+      <c r="K388" s="2" t="n"/>
+      <c r="L388" t="n">
+        <v>235</v>
+      </c>
+      <c r="M388" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y388" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z388" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA388" t="n">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>218687255</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J389" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L389" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M389" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA389" t="n">
+        <v>245.34</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>58174815</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J390" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L390" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M390" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y390" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z390" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA390" t="n">
+        <v>245.34</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>226773215</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>GBF786</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="n"/>
+      <c r="H391" s="2" t="n"/>
+      <c r="I391" s="2" t="n"/>
+      <c r="J391" s="2" t="n"/>
+      <c r="K391" s="2" t="n"/>
+      <c r="L391" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="M391" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y391" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z391" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA391" t="n">
+        <v>602.0700000000001</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>226773217</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="n"/>
+      <c r="H392" s="2" t="n"/>
+      <c r="I392" s="2" t="n"/>
+      <c r="J392" s="2" t="n"/>
+      <c r="K392" s="2" t="n"/>
+      <c r="L392" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M392" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA392" t="n">
+        <v>552.24</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>226773218</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="n"/>
+      <c r="H393" s="2" t="n"/>
+      <c r="I393" s="2" t="n"/>
+      <c r="J393" s="2" t="n"/>
+      <c r="K393" s="2" t="n"/>
+      <c r="L393" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M393" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA393" t="n">
+        <v>552.24</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>177646295</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>GBF827</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>GBF827PT</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J394" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L394" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="M394" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA394" t="n">
+        <v>343.12</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>105914</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>156352241</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>PABR56</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>PABR56CM</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>PABR56CM</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J395" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L395" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="M395" t="n">
+        <v>1</v>
+      </c>
+      <c r="N395" t="n">
+        <v>3</v>
+      </c>
+      <c r="O395" t="n">
+        <v>4</v>
+      </c>
+      <c r="P395" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>3</v>
+      </c>
+      <c r="R395" t="n">
+        <v>5</v>
+      </c>
+      <c r="S395" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>2546.88</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>105914</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>226773817</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>PABR80</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="n"/>
+      <c r="H396" s="2" t="n"/>
+      <c r="I396" s="2" t="n"/>
+      <c r="J396" s="2" t="n"/>
+      <c r="K396" s="2" t="n"/>
+      <c r="L396" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="M396" t="n">
+        <v>1</v>
+      </c>
+      <c r="N396" t="n">
+        <v>1</v>
+      </c>
+      <c r="O396" t="n">
+        <v>3</v>
+      </c>
+      <c r="P396" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>3</v>
+      </c>
+      <c r="R396" t="n">
+        <v>3</v>
+      </c>
+      <c r="S396" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA396" t="n">
+        <v>2131.5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>105920</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>226799440</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>WSCR54</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="n"/>
+      <c r="H397" s="2" t="n"/>
+      <c r="I397" s="2" t="n"/>
+      <c r="J397" s="2" t="n"/>
+      <c r="K397" s="2" t="n"/>
+      <c r="L397" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="M397" t="n">
+        <v>1</v>
+      </c>
+      <c r="N397" t="n">
+        <v>1</v>
+      </c>
+      <c r="O397" t="n">
+        <v>2</v>
+      </c>
+      <c r="P397" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>3</v>
+      </c>
+      <c r="R397" t="n">
+        <v>2</v>
+      </c>
+      <c r="S397" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>2540.16</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>105920</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>226799445</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>WSCR57</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="n"/>
+      <c r="H398" s="2" t="n"/>
+      <c r="I398" s="2" t="n"/>
+      <c r="J398" s="2" t="n"/>
+      <c r="K398" s="2" t="n"/>
+      <c r="L398" t="n">
+        <v>159.25</v>
+      </c>
+      <c r="M398" t="n">
+        <v>1</v>
+      </c>
+      <c r="N398" t="n">
+        <v>1</v>
+      </c>
+      <c r="O398" t="n">
+        <v>3</v>
+      </c>
+      <c r="P398" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>4</v>
+      </c>
+      <c r="R398" t="n">
+        <v>2</v>
+      </c>
+      <c r="S398" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z398" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>2388.75</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>105920</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>226799459</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>WSCR89</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="n"/>
+      <c r="H399" s="2" t="n"/>
+      <c r="I399" s="2" t="n"/>
+      <c r="J399" s="2" t="n"/>
+      <c r="K399" s="2" t="n"/>
+      <c r="L399" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="M399" t="n">
+        <v>1</v>
+      </c>
+      <c r="N399" t="n">
+        <v>1</v>
+      </c>
+      <c r="O399" t="n">
+        <v>3</v>
+      </c>
+      <c r="P399" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>4</v>
+      </c>
+      <c r="R399" t="n">
+        <v>2</v>
+      </c>
+      <c r="S399" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>2423.7</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>105910</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>13224</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J400" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L400" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M400" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y400" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z400" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA400" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>105910</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>13281</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>HMO101PT</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>HMO101PT</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J401" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L401" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M401" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA401" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>226773909</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>PAX634</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="n"/>
+      <c r="H402" s="2" t="n"/>
+      <c r="I402" s="2" t="n"/>
+      <c r="J402" s="2" t="n"/>
+      <c r="K402" s="2" t="n"/>
+      <c r="L402" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="M402" t="n">
+        <v>1</v>
+      </c>
+      <c r="N402" t="n">
+        <v>1</v>
+      </c>
+      <c r="O402" t="n">
+        <v>3</v>
+      </c>
+      <c r="P402" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>4</v>
+      </c>
+      <c r="R402" t="n">
+        <v>2</v>
+      </c>
+      <c r="S402" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z402" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA402" t="n">
+        <v>1521.45</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>226774175</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="n"/>
+      <c r="H403" s="2" t="n"/>
+      <c r="I403" s="2" t="n"/>
+      <c r="J403" s="2" t="n"/>
+      <c r="K403" s="2" t="n"/>
+      <c r="L403" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M403" t="n">
+        <v>1</v>
+      </c>
+      <c r="N403" t="n">
+        <v>1</v>
+      </c>
+      <c r="O403" t="n">
+        <v>3</v>
+      </c>
+      <c r="P403" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>4</v>
+      </c>
+      <c r="R403" t="n">
+        <v>3</v>
+      </c>
+      <c r="S403" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA403" t="n">
+        <v>1276.74</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>226774176</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="n"/>
+      <c r="H404" s="2" t="n"/>
+      <c r="I404" s="2" t="n"/>
+      <c r="J404" s="2" t="n"/>
+      <c r="K404" s="2" t="n"/>
+      <c r="L404" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M404" t="n">
+        <v>1</v>
+      </c>
+      <c r="N404" t="n">
+        <v>1</v>
+      </c>
+      <c r="O404" t="n">
+        <v>3</v>
+      </c>
+      <c r="P404" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>3</v>
+      </c>
+      <c r="R404" t="n">
+        <v>3</v>
+      </c>
+      <c r="S404" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA404" t="n">
+        <v>1063.95</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>226774179</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>PRA730</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>PRA730CA</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>PRA730CA</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="n"/>
+      <c r="H405" s="2" t="n"/>
+      <c r="I405" s="2" t="n"/>
+      <c r="J405" s="2" t="n"/>
+      <c r="K405" s="2" t="n"/>
+      <c r="L405" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="M405" t="n">
+        <v>1</v>
+      </c>
+      <c r="N405" t="n">
+        <v>1</v>
+      </c>
+      <c r="O405" t="n">
+        <v>3</v>
+      </c>
+      <c r="P405" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>3</v>
+      </c>
+      <c r="R405" t="n">
+        <v>3</v>
+      </c>
+      <c r="S405" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA405" t="n">
+        <v>1633.5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>226799120</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TBC207</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="n"/>
+      <c r="H406" s="2" t="n"/>
+      <c r="I406" s="2" t="n"/>
+      <c r="J406" s="2" t="n"/>
+      <c r="K406" s="2" t="n"/>
+      <c r="L406" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="M406" t="n">
+        <v>1</v>
+      </c>
+      <c r="N406" t="n">
+        <v>1</v>
+      </c>
+      <c r="O406" t="n">
+        <v>3</v>
+      </c>
+      <c r="P406" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>4</v>
+      </c>
+      <c r="R406" t="n">
+        <v>2</v>
+      </c>
+      <c r="S406" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA406" t="n">
+        <v>854.4</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>947706</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>LMM004BG</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>LMM004BG</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J407" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L407" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M407" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA407" t="n">
+        <v>420.24</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>939641</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>LMM004MH</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>LMM004MH</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J408" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L408" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M408" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA408" t="n">
+        <v>630.36</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>939642</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J409" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L409" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M409" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y409" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA409" t="n">
+        <v>420.24</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>939643</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J410" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L410" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M410" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y410" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA410" t="n">
+        <v>840.48</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>4600</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>LMM009</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>LMM009MM</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>LMM009MM</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J411" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L411" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M411" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y411" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA411" t="n">
+        <v>187.56</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>21174</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>LMM009</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>LMM009PT</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>LMM009PT</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J412" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L412" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M412" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y412" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA412" t="n">
+        <v>562.6799999999999</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>226774182</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>PRA747</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>PRA747CF</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>PRA747CF</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="n"/>
+      <c r="H413" s="2" t="n"/>
+      <c r="I413" s="2" t="n"/>
+      <c r="J413" s="2" t="n"/>
+      <c r="K413" s="2" t="n"/>
+      <c r="L413" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>1</v>
+      </c>
+      <c r="N413" t="n">
+        <v>1</v>
+      </c>
+      <c r="O413" t="n">
+        <v>2</v>
+      </c>
+      <c r="P413" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>3</v>
+      </c>
+      <c r="R413" t="n">
+        <v>2</v>
+      </c>
+      <c r="S413" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z413" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA413" t="n">
+        <v>658.8</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>226799135</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>TBE004BI</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>TBE004BI</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="n"/>
+      <c r="H414" s="2" t="n"/>
+      <c r="I414" s="2" t="n"/>
+      <c r="J414" s="2" t="n"/>
+      <c r="K414" s="2" t="n"/>
+      <c r="L414" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M414" t="n">
+        <v>1</v>
+      </c>
+      <c r="N414" t="n">
+        <v>1</v>
+      </c>
+      <c r="O414" t="n">
+        <v>3</v>
+      </c>
+      <c r="P414" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>4</v>
+      </c>
+      <c r="R414" t="n">
+        <v>2</v>
+      </c>
+      <c r="S414" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z414" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA414" t="n">
+        <v>913.2</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>226799136</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="n"/>
+      <c r="H415" s="2" t="n"/>
+      <c r="I415" s="2" t="n"/>
+      <c r="J415" s="2" t="n"/>
+      <c r="K415" s="2" t="n"/>
+      <c r="L415" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M415" t="n">
+        <v>1</v>
+      </c>
+      <c r="N415" t="n">
+        <v>1</v>
+      </c>
+      <c r="O415" t="n">
+        <v>3</v>
+      </c>
+      <c r="P415" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>4</v>
+      </c>
+      <c r="R415" t="n">
+        <v>3</v>
+      </c>
+      <c r="S415" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z415" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA415" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>226799137</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="n"/>
+      <c r="H416" s="2" t="n"/>
+      <c r="I416" s="2" t="n"/>
+      <c r="J416" s="2" t="n"/>
+      <c r="K416" s="2" t="n"/>
+      <c r="L416" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M416" t="n">
+        <v>1</v>
+      </c>
+      <c r="N416" t="n">
+        <v>1</v>
+      </c>
+      <c r="O416" t="n">
+        <v>3</v>
+      </c>
+      <c r="P416" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>4</v>
+      </c>
+      <c r="R416" t="n">
+        <v>3</v>
+      </c>
+      <c r="S416" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z416" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA416" t="n">
+        <v>1095.84</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>226799138</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="n"/>
+      <c r="H417" s="2" t="n"/>
+      <c r="I417" s="2" t="n"/>
+      <c r="J417" s="2" t="n"/>
+      <c r="K417" s="2" t="n"/>
+      <c r="L417" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M417" t="n">
+        <v>1</v>
+      </c>
+      <c r="N417" t="n">
+        <v>1</v>
+      </c>
+      <c r="O417" t="n">
+        <v>3</v>
+      </c>
+      <c r="P417" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>4</v>
+      </c>
+      <c r="R417" t="n">
+        <v>2</v>
+      </c>
+      <c r="S417" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z417" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA417" t="n">
+        <v>913.2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>105917</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>226780324</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="n"/>
+      <c r="H418" s="2" t="n"/>
+      <c r="I418" s="2" t="n"/>
+      <c r="J418" s="2" t="n"/>
+      <c r="K418" s="2" t="n"/>
+      <c r="L418" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M418" t="n">
+        <v>1</v>
+      </c>
+      <c r="R418" t="n">
+        <v>1</v>
+      </c>
+      <c r="S418" t="n">
+        <v>3</v>
+      </c>
+      <c r="T418" t="n">
+        <v>4</v>
+      </c>
+      <c r="U418" t="n">
+        <v>4</v>
+      </c>
+      <c r="V418" t="n">
+        <v>3</v>
+      </c>
+      <c r="W418" t="n">
+        <v>2</v>
+      </c>
+      <c r="X418" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z418" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA418" t="n">
+        <v>4361.58</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>105912</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>13274</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>LMM016BC</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>LMM016BC</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J419" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L419" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M419" t="n">
+        <v>1</v>
+      </c>
+      <c r="P419" t="n">
+        <v>6</v>
+      </c>
+      <c r="T419" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA419" t="n">
+        <v>238.92</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>105912</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>23300</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>LMM016BG</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>LMM016BG</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J420" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L420" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M420" t="n">
+        <v>1</v>
+      </c>
+      <c r="P420" t="n">
+        <v>18</v>
+      </c>
+      <c r="T420" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>716.76</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>105912</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>105185079</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>LMW200</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>LMW200ND</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>LMW200ND</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J421" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L421" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M421" t="n">
+        <v>1</v>
+      </c>
+      <c r="O421" t="n">
+        <v>18</v>
+      </c>
+      <c r="S421" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA421" t="n">
+        <v>708.12</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>105912</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>105185080</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>LMW200</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>LMW200PT</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>LMW200PT</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J422" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L422" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M422" t="n">
+        <v>1</v>
+      </c>
+      <c r="O422" t="n">
+        <v>6</v>
+      </c>
+      <c r="S422" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA422" t="n">
+        <v>236.04</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>105975</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>8619996</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>MCC190</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>MCC190PT</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>MCC190PT</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J423" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L423" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="M423" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA423" t="n">
+        <v>208.62</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>105975</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SH. PLAZA NITEROI</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>60897674</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>MCC980</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>MCC980PT</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>MCC980PT</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J424" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L424" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="M424" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA424" t="n">
+        <v>262.17</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>105906</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>226772885</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>BBK071</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="n"/>
+      <c r="H425" s="2" t="n"/>
+      <c r="I425" s="2" t="n"/>
+      <c r="J425" s="2" t="n"/>
+      <c r="K425" s="2" t="n"/>
+      <c r="L425" t="n">
+        <v>153.38</v>
+      </c>
+      <c r="M425" t="n">
+        <v>1</v>
+      </c>
+      <c r="N425" t="n">
+        <v>1</v>
+      </c>
+      <c r="O425" t="n">
+        <v>3</v>
+      </c>
+      <c r="P425" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>4</v>
+      </c>
+      <c r="R425" t="n">
+        <v>2</v>
+      </c>
+      <c r="S425" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA425" t="n">
+        <v>2300.7</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>105906</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>226772886</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>BBK072</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>BBK072CF</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>BBK072CF</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="n"/>
+      <c r="H426" s="2" t="n"/>
+      <c r="I426" s="2" t="n"/>
+      <c r="J426" s="2" t="n"/>
+      <c r="K426" s="2" t="n"/>
+      <c r="L426" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="M426" t="n">
+        <v>1</v>
+      </c>
+      <c r="N426" t="n">
+        <v>1</v>
+      </c>
+      <c r="O426" t="n">
+        <v>4</v>
+      </c>
+      <c r="P426" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>5</v>
+      </c>
+      <c r="R426" t="n">
+        <v>2</v>
+      </c>
+      <c r="S426" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA426" t="n">
+        <v>1833.12</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>105906</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>226773843</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>PAT119</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>PAT119CF</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>PAT119CF</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="n"/>
+      <c r="H427" s="2" t="n"/>
+      <c r="I427" s="2" t="n"/>
+      <c r="J427" s="2" t="n"/>
+      <c r="K427" s="2" t="n"/>
+      <c r="L427" t="n">
+        <v>131.29</v>
+      </c>
+      <c r="M427" t="n">
+        <v>1</v>
+      </c>
+      <c r="N427" t="n">
+        <v>1</v>
+      </c>
+      <c r="O427" t="n">
+        <v>3</v>
+      </c>
+      <c r="P427" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>4</v>
+      </c>
+      <c r="R427" t="n">
+        <v>2</v>
+      </c>
+      <c r="S427" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z427" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA427" t="n">
+        <v>1969.35</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>105906</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>226773985</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>PMD407</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="n"/>
+      <c r="H428" s="2" t="n"/>
+      <c r="I428" s="2" t="n"/>
+      <c r="J428" s="2" t="n"/>
+      <c r="K428" s="2" t="n"/>
+      <c r="L428" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M428" t="n">
+        <v>1</v>
+      </c>
+      <c r="N428" t="n">
+        <v>1</v>
+      </c>
+      <c r="O428" t="n">
+        <v>3</v>
+      </c>
+      <c r="P428" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>4</v>
+      </c>
+      <c r="R428" t="n">
+        <v>2</v>
+      </c>
+      <c r="S428" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z428" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA428" t="n">
+        <v>1652.7</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>105906</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>226774180</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="n"/>
+      <c r="H429" s="2" t="n"/>
+      <c r="I429" s="2" t="n"/>
+      <c r="J429" s="2" t="n"/>
+      <c r="K429" s="2" t="n"/>
+      <c r="L429" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M429" t="n">
+        <v>1</v>
+      </c>
+      <c r="N429" t="n">
+        <v>1</v>
+      </c>
+      <c r="O429" t="n">
+        <v>3</v>
+      </c>
+      <c r="P429" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>4</v>
+      </c>
+      <c r="R429" t="n">
+        <v>3</v>
+      </c>
+      <c r="S429" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z429" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA429" t="n">
+        <v>1104.3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>105906</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>226774181</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="n"/>
+      <c r="H430" s="2" t="n"/>
+      <c r="I430" s="2" t="n"/>
+      <c r="J430" s="2" t="n"/>
+      <c r="K430" s="2" t="n"/>
+      <c r="L430" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M430" t="n">
+        <v>1</v>
+      </c>
+      <c r="N430" t="n">
+        <v>1</v>
+      </c>
+      <c r="O430" t="n">
+        <v>3</v>
+      </c>
+      <c r="P430" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>4</v>
+      </c>
+      <c r="R430" t="n">
+        <v>3</v>
+      </c>
+      <c r="S430" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z430" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA430" t="n">
+        <v>1104.3</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>105907</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>42444814</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>GBE969</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>GBE969CN</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>GBE969CN</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J431" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L431" t="n">
+        <v>232.46</v>
+      </c>
+      <c r="M431" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y431" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z431" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA431" t="n">
+        <v>464.92</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>105907</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>98674755</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>HMO921</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>HMO921MR</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>HMO921MR</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J432" t="n">
+        <v>1399.9</v>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L432" t="n">
+        <v>401.08</v>
+      </c>
+      <c r="M432" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y432" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z432" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA432" t="n">
+        <v>802.16</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>105918</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>219741931</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TBC193</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>TBC193PT</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>TBC193PT</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>SAPATILHA</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J433" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L433" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M433" t="n">
+        <v>1</v>
+      </c>
+      <c r="N433" t="n">
+        <v>1</v>
+      </c>
+      <c r="O433" t="n">
+        <v>2</v>
+      </c>
+      <c r="P433" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>3</v>
+      </c>
+      <c r="R433" t="n">
+        <v>2</v>
+      </c>
+      <c r="S433" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA433" t="n">
+        <v>1073.16</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>105918</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>226799195</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="n"/>
+      <c r="H434" s="2" t="n"/>
+      <c r="I434" s="2" t="n"/>
+      <c r="J434" s="2" t="n"/>
+      <c r="K434" s="2" t="n"/>
+      <c r="L434" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M434" t="n">
+        <v>1</v>
+      </c>
+      <c r="N434" t="n">
+        <v>1</v>
+      </c>
+      <c r="O434" t="n">
+        <v>2</v>
+      </c>
+      <c r="P434" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>3</v>
+      </c>
+      <c r="R434" t="n">
+        <v>2</v>
+      </c>
+      <c r="S434" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>105918</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>226799197</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="n"/>
+      <c r="H435" s="2" t="n"/>
+      <c r="I435" s="2" t="n"/>
+      <c r="J435" s="2" t="n"/>
+      <c r="K435" s="2" t="n"/>
+      <c r="L435" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M435" t="n">
+        <v>1</v>
+      </c>
+      <c r="N435" t="n">
+        <v>1</v>
+      </c>
+      <c r="O435" t="n">
+        <v>2</v>
+      </c>
+      <c r="P435" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>3</v>
+      </c>
+      <c r="R435" t="n">
+        <v>2</v>
+      </c>
+      <c r="S435" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>1234.8</v>
       </c>
     </row>
   </sheetData>
@@ -25468,7 +29689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26568,15 +30789,26 @@
           <t>COURO &amp; ARTE LTDA</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>N_RelB2bCarrinhoExcel-19h17.xlsx</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SEM ARQUIVO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
+      <c r="G30" t="n">
+        <v>18</v>
+      </c>
       <c r="H30" t="n">
+        <v>470.79</v>
+      </c>
+      <c r="I30" t="n">
         <v>470.79</v>
       </c>
     </row>
@@ -28025,21 +32257,21 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>105838</v>
+        <v>105906</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. RIO SUL 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>WW EXPORT LTDA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h13.xlsx</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -28048,35 +32280,35 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="H70" t="n">
-        <v>864.8099999999999</v>
+        <v>9964.469999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>864.8099999999999</v>
+        <v>9964.469999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>105839</v>
+        <v>105907</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. RIO SUL 1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h14.xlsx</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -28085,35 +32317,35 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" t="n">
-        <v>1044</v>
+        <v>1267.08</v>
       </c>
       <c r="I71" t="n">
-        <v>1044</v>
+        <v>1267.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>105840</v>
+        <v>105908</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. RIO SUL 1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h14.xlsx</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -28122,35 +32354,35 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H72" t="n">
-        <v>254.27</v>
+        <v>3912</v>
       </c>
       <c r="I72" t="n">
-        <v>254.27</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>105841</v>
+        <v>105909</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. RIO SUL 1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h14.xlsx</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -28159,35 +32391,35 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H73" t="n">
-        <v>3267.72</v>
+        <v>4599.89</v>
       </c>
       <c r="I73" t="n">
-        <v>3267.72</v>
+        <v>4599.89</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>105842</v>
+        <v>105910</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. RIO SUL 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WW EXPORT LTDA</t>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h14.xlsx</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -28196,52 +32428,607 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>2095.92</v>
+        <v>508.54</v>
       </c>
       <c r="I74" t="n">
-        <v>2095.92</v>
+        <v>508.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PRIMAR IND TEXTIL LTDA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>180</v>
+      </c>
+      <c r="G75" t="n">
+        <v>180</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3061.56</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3061.56</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105912</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>L T BERTOLANI CONFECCAO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>96</v>
+      </c>
+      <c r="G76" t="n">
+        <v>96</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1899.84</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1899.84</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>105913</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>60</v>
+      </c>
+      <c r="G77" t="n">
+        <v>60</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7626.15</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7626.15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>105914</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>36</v>
+      </c>
+      <c r="G78" t="n">
+        <v>36</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4678.38</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4678.38</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>78</v>
+      </c>
+      <c r="G79" t="n">
+        <v>78</v>
+      </c>
+      <c r="H79" t="n">
+        <v>6350.04</v>
+      </c>
+      <c r="I79" t="n">
+        <v>6350.04</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>D MATTHES CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>78</v>
+      </c>
+      <c r="G80" t="n">
+        <v>78</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4676.88</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4676.88</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>105917</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>18</v>
+      </c>
+      <c r="G81" t="n">
+        <v>18</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4361.58</v>
+      </c>
+      <c r="I81" t="n">
+        <v>4361.58</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>105918</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>N C CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h16.xlsx</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>36</v>
+      </c>
+      <c r="G82" t="n">
+        <v>36</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3542.76</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3542.76</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>105919</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MASSEY CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h16.xlsx</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>54</v>
+      </c>
+      <c r="G83" t="n">
+        <v>54</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5204.58</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5204.58</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>105920</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h16.xlsx</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>42</v>
+      </c>
+      <c r="G84" t="n">
+        <v>42</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7352.61</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7352.61</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>6</v>
+      </c>
+      <c r="H85" t="n">
+        <v>864.8099999999999</v>
+      </c>
+      <c r="I85" t="n">
+        <v>864.8099999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>105839</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>105840</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="I87" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>27</v>
+      </c>
+      <c r="G88" t="n">
+        <v>27</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3267.72</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3267.72</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>WW EXPORT LTDA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>27</v>
+      </c>
+      <c r="G89" t="n">
+        <v>27</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2095.92</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2095.92</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
         <v>105843</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>SH. PARK SUL</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>RelB2bCarrinhoExcel-19h08.xlsx</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F90" t="n">
         <v>9</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G90" t="n">
         <v>9</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H90" t="n">
         <v>2180.79</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I90" t="n">
         <v>2180.79</v>
       </c>
     </row>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA435"/>
+  <dimension ref="A1:AA544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29676,6 +29676,7455 @@
       </c>
       <c r="AA435" t="n">
         <v>1234.8</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>105819</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>226772776</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>ASF182MM</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="n"/>
+      <c r="H436" s="2" t="n"/>
+      <c r="I436" s="2" t="n"/>
+      <c r="J436" s="2" t="n"/>
+      <c r="K436" s="2" t="n"/>
+      <c r="L436" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M436" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>6</v>
+      </c>
+      <c r="S436" t="n">
+        <v>10</v>
+      </c>
+      <c r="U436" t="n">
+        <v>12</v>
+      </c>
+      <c r="W436" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>2316.6</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>105819</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>1213706</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>ASF182</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>ASF182PT</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J437" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L437" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="M437" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>6</v>
+      </c>
+      <c r="S437" t="n">
+        <v>10</v>
+      </c>
+      <c r="U437" t="n">
+        <v>12</v>
+      </c>
+      <c r="W437" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>2316.6</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>105826</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>13222</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>HCT173</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>HCT173CF</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>HCT173CF</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J438" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L438" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="M438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>476.01</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>105826</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>13223</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>HCT173</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>HCT173PT</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>HCT173PT</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J439" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L439" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="M439" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>634.6799999999999</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>105826</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>13224</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>HMO101</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>HMO101CF</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J440" t="n">
+        <v>899.9</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L440" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="M440" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>508.54</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>105826</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>138654476</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>MCC008</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>MCC008PT</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>MCC008PT</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J441" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L441" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="M441" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>468.48</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>105826</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>138654477</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>MCC008</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>MCC008TN</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>MCC008TN</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J442" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L442" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="M442" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>468.48</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>105826</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>138654478</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>MCC008</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>MCC008VR</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>MCC008VR</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J443" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L443" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="M443" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>468.48</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>105831</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>162603452</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>PABR60</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>PABR60NT</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>PABR60NT</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>ANABELA</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J444" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L444" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="M444" t="n">
+        <v>1</v>
+      </c>
+      <c r="O444" t="n">
+        <v>1</v>
+      </c>
+      <c r="P444" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>3</v>
+      </c>
+      <c r="R444" t="n">
+        <v>1</v>
+      </c>
+      <c r="S444" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>1058.4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>105831</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>226773817</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>PABR80</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>PABR80FD</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="n"/>
+      <c r="H445" s="2" t="n"/>
+      <c r="I445" s="2" t="n"/>
+      <c r="J445" s="2" t="n"/>
+      <c r="K445" s="2" t="n"/>
+      <c r="L445" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="M445" t="n">
+        <v>1</v>
+      </c>
+      <c r="N445" t="n">
+        <v>2</v>
+      </c>
+      <c r="O445" t="n">
+        <v>4</v>
+      </c>
+      <c r="P445" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>4</v>
+      </c>
+      <c r="R445" t="n">
+        <v>4</v>
+      </c>
+      <c r="S445" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>2984.1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>105836</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>134703902</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>WSC330BC</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>WSC330BC</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J446" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L446" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="M446" t="n">
+        <v>1</v>
+      </c>
+      <c r="N446" t="n">
+        <v>3</v>
+      </c>
+      <c r="O446" t="n">
+        <v>3</v>
+      </c>
+      <c r="P446" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>14</v>
+      </c>
+      <c r="R446" t="n">
+        <v>6</v>
+      </c>
+      <c r="S446" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>2766.96</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>105836</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>226799278</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>WSC330</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>WSC330OU</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="n"/>
+      <c r="H447" s="2" t="n"/>
+      <c r="I447" s="2" t="n"/>
+      <c r="J447" s="2" t="n"/>
+      <c r="K447" s="2" t="n"/>
+      <c r="L447" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M447" t="n">
+        <v>1</v>
+      </c>
+      <c r="N447" t="n">
+        <v>2</v>
+      </c>
+      <c r="O447" t="n">
+        <v>6</v>
+      </c>
+      <c r="P447" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>9</v>
+      </c>
+      <c r="R447" t="n">
+        <v>6</v>
+      </c>
+      <c r="S447" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>2459.52</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>105836</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>147983439</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>WSC432</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>WSC432AW</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>WSC432AW</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J448" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L448" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="M448" t="n">
+        <v>1</v>
+      </c>
+      <c r="N448" t="n">
+        <v>1</v>
+      </c>
+      <c r="O448" t="n">
+        <v>3</v>
+      </c>
+      <c r="P448" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>10</v>
+      </c>
+      <c r="R448" t="n">
+        <v>8</v>
+      </c>
+      <c r="S448" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>2459.52</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>105836</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>137619676</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>WSCR61AR</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J449" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L449" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M449" t="n">
+        <v>1</v>
+      </c>
+      <c r="N449" t="n">
+        <v>1</v>
+      </c>
+      <c r="O449" t="n">
+        <v>2</v>
+      </c>
+      <c r="P449" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>10</v>
+      </c>
+      <c r="R449" t="n">
+        <v>4</v>
+      </c>
+      <c r="S449" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>2851.92</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>105836</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>170929723</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>WSCR61FD</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>WSCR61FD</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J450" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L450" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M450" t="n">
+        <v>1</v>
+      </c>
+      <c r="N450" t="n">
+        <v>1</v>
+      </c>
+      <c r="O450" t="n">
+        <v>2</v>
+      </c>
+      <c r="P450" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>3</v>
+      </c>
+      <c r="R450" t="n">
+        <v>2</v>
+      </c>
+      <c r="S450" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>1425.96</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>105836</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>137619678</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>WSCR61</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>WSCR61PT</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>WSCR61PT</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J451" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L451" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="M451" t="n">
+        <v>1</v>
+      </c>
+      <c r="N451" t="n">
+        <v>1</v>
+      </c>
+      <c r="O451" t="n">
+        <v>3</v>
+      </c>
+      <c r="P451" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>6</v>
+      </c>
+      <c r="R451" t="n">
+        <v>5</v>
+      </c>
+      <c r="S451" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>2851.92</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>162601593</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>ASN011</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>ASN011MR</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>ASN011MR</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J452" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L452" t="n">
+        <v>137.81</v>
+      </c>
+      <c r="M452" t="n">
+        <v>1</v>
+      </c>
+      <c r="R452" t="n">
+        <v>1</v>
+      </c>
+      <c r="S452" t="n">
+        <v>2</v>
+      </c>
+      <c r="T452" t="n">
+        <v>3</v>
+      </c>
+      <c r="U452" t="n">
+        <v>4</v>
+      </c>
+      <c r="V452" t="n">
+        <v>1</v>
+      </c>
+      <c r="W452" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>1653.72</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>69427205</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SAF125</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>SAF125PT</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>SAF125PT</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J453" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L453" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="M453" t="n">
+        <v>1</v>
+      </c>
+      <c r="R453" t="n">
+        <v>2</v>
+      </c>
+      <c r="S453" t="n">
+        <v>4</v>
+      </c>
+      <c r="T453" t="n">
+        <v>5</v>
+      </c>
+      <c r="U453" t="n">
+        <v>5</v>
+      </c>
+      <c r="V453" t="n">
+        <v>4</v>
+      </c>
+      <c r="W453" t="n">
+        <v>3</v>
+      </c>
+      <c r="X453" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>3247.2</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>227068437</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SAF126</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>SAF126BK</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>SAF126BK</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="n"/>
+      <c r="H454" s="2" t="n"/>
+      <c r="I454" s="2" t="n"/>
+      <c r="J454" s="2" t="n"/>
+      <c r="K454" s="2" t="n"/>
+      <c r="L454" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="M454" t="n">
+        <v>1</v>
+      </c>
+      <c r="R454" t="n">
+        <v>2</v>
+      </c>
+      <c r="S454" t="n">
+        <v>4</v>
+      </c>
+      <c r="T454" t="n">
+        <v>7</v>
+      </c>
+      <c r="U454" t="n">
+        <v>8</v>
+      </c>
+      <c r="V454" t="n">
+        <v>5</v>
+      </c>
+      <c r="W454" t="n">
+        <v>3</v>
+      </c>
+      <c r="X454" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>96929942</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>SAF132</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>SAF132TN</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>SAF132TN</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J455" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L455" t="n">
+        <v>152.02</v>
+      </c>
+      <c r="M455" t="n">
+        <v>1</v>
+      </c>
+      <c r="R455" t="n">
+        <v>1</v>
+      </c>
+      <c r="S455" t="n">
+        <v>2</v>
+      </c>
+      <c r="T455" t="n">
+        <v>2</v>
+      </c>
+      <c r="U455" t="n">
+        <v>8</v>
+      </c>
+      <c r="V455" t="n">
+        <v>4</v>
+      </c>
+      <c r="W455" t="n">
+        <v>6</v>
+      </c>
+      <c r="X455" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>3648.48</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>112125141</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>SAF134</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>SAF134PT</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>SAF134PT</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J456" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L456" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="M456" t="n">
+        <v>1</v>
+      </c>
+      <c r="R456" t="n">
+        <v>1</v>
+      </c>
+      <c r="S456" t="n">
+        <v>3</v>
+      </c>
+      <c r="T456" t="n">
+        <v>5</v>
+      </c>
+      <c r="U456" t="n">
+        <v>2</v>
+      </c>
+      <c r="V456" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>1517.52</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>194597523</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SRF025</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>SRF025MR</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>SRF025MR</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J457" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L457" t="n">
+        <v>153.55</v>
+      </c>
+      <c r="M457" t="n">
+        <v>1</v>
+      </c>
+      <c r="R457" t="n">
+        <v>2</v>
+      </c>
+      <c r="S457" t="n">
+        <v>2</v>
+      </c>
+      <c r="T457" t="n">
+        <v>3</v>
+      </c>
+      <c r="U457" t="n">
+        <v>9</v>
+      </c>
+      <c r="V457" t="n">
+        <v>5</v>
+      </c>
+      <c r="W457" t="n">
+        <v>2</v>
+      </c>
+      <c r="X457" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>3685.2</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>72489310</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>SRF025</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>SRF025PT</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>SRF025PT</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J458" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L458" t="n">
+        <v>153.55</v>
+      </c>
+      <c r="M458" t="n">
+        <v>1</v>
+      </c>
+      <c r="S458" t="n">
+        <v>1</v>
+      </c>
+      <c r="T458" t="n">
+        <v>1</v>
+      </c>
+      <c r="U458" t="n">
+        <v>2</v>
+      </c>
+      <c r="V458" t="n">
+        <v>3</v>
+      </c>
+      <c r="W458" t="n">
+        <v>1</v>
+      </c>
+      <c r="X458" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>1381.95</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>193547057</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>SRT027</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>SRT027BC</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>SRT027BC</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J459" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L459" t="n">
+        <v>147.98</v>
+      </c>
+      <c r="M459" t="n">
+        <v>1</v>
+      </c>
+      <c r="R459" t="n">
+        <v>1</v>
+      </c>
+      <c r="S459" t="n">
+        <v>2</v>
+      </c>
+      <c r="T459" t="n">
+        <v>4</v>
+      </c>
+      <c r="U459" t="n">
+        <v>3</v>
+      </c>
+      <c r="V459" t="n">
+        <v>2</v>
+      </c>
+      <c r="W459" t="n">
+        <v>2</v>
+      </c>
+      <c r="X459" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>2219.7</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>226787944</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>SRT028</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>SRT028BK</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>SRT028BK</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="n"/>
+      <c r="H460" s="2" t="n"/>
+      <c r="I460" s="2" t="n"/>
+      <c r="J460" s="2" t="n"/>
+      <c r="K460" s="2" t="n"/>
+      <c r="L460" t="n">
+        <v>159.78</v>
+      </c>
+      <c r="M460" t="n">
+        <v>1</v>
+      </c>
+      <c r="R460" t="n">
+        <v>2</v>
+      </c>
+      <c r="S460" t="n">
+        <v>4</v>
+      </c>
+      <c r="T460" t="n">
+        <v>7</v>
+      </c>
+      <c r="U460" t="n">
+        <v>8</v>
+      </c>
+      <c r="V460" t="n">
+        <v>5</v>
+      </c>
+      <c r="W460" t="n">
+        <v>3</v>
+      </c>
+      <c r="X460" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA460" t="n">
+        <v>4793.4</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>99645682</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>WSC003</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>WSC003OW</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>WSC003OW</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J461" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L461" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="M461" t="n">
+        <v>1</v>
+      </c>
+      <c r="O461" t="n">
+        <v>1</v>
+      </c>
+      <c r="P461" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>4</v>
+      </c>
+      <c r="R461" t="n">
+        <v>2</v>
+      </c>
+      <c r="S461" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>1658.4</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>226906303</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>WSC761</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>WSC761BC</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>WSC761BC</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="n"/>
+      <c r="H462" s="2" t="n"/>
+      <c r="I462" s="2" t="n"/>
+      <c r="J462" s="2" t="n"/>
+      <c r="K462" s="2" t="n"/>
+      <c r="L462" t="n">
+        <v>143.91</v>
+      </c>
+      <c r="M462" t="n">
+        <v>1</v>
+      </c>
+      <c r="N462" t="n">
+        <v>1</v>
+      </c>
+      <c r="O462" t="n">
+        <v>3</v>
+      </c>
+      <c r="P462" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>5</v>
+      </c>
+      <c r="R462" t="n">
+        <v>3</v>
+      </c>
+      <c r="S462" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>2590.38</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>105820</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>223147116</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>WSC767</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>WSC767TP</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>WSC767TP</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J463" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L463" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="M463" t="n">
+        <v>1</v>
+      </c>
+      <c r="N463" t="n">
+        <v>1</v>
+      </c>
+      <c r="O463" t="n">
+        <v>2</v>
+      </c>
+      <c r="P463" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>3</v>
+      </c>
+      <c r="R463" t="n">
+        <v>2</v>
+      </c>
+      <c r="S463" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>1771.2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>105827</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>41587477</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>HMO915</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>HMO915CF</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>HMO915CF</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J464" t="n">
+        <v>1699.9</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L464" t="n">
+        <v>624.22</v>
+      </c>
+      <c r="M464" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>624.22</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>105827</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>41587478</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>HMO915</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>HMO915PT</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>HMO915PT</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J465" t="n">
+        <v>1699.9</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L465" t="n">
+        <v>624.22</v>
+      </c>
+      <c r="M465" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>624.22</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>226772885</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>BBK071</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>BBK071CA</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="n"/>
+      <c r="H466" s="2" t="n"/>
+      <c r="I466" s="2" t="n"/>
+      <c r="J466" s="2" t="n"/>
+      <c r="K466" s="2" t="n"/>
+      <c r="L466" t="n">
+        <v>153.38</v>
+      </c>
+      <c r="M466" t="n">
+        <v>1</v>
+      </c>
+      <c r="N466" t="n">
+        <v>1</v>
+      </c>
+      <c r="O466" t="n">
+        <v>3</v>
+      </c>
+      <c r="P466" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>4</v>
+      </c>
+      <c r="R466" t="n">
+        <v>2</v>
+      </c>
+      <c r="S466" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>2300.7</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>226772886</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>BBK072</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>BBK072CF</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>BBK072CF</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="n"/>
+      <c r="H467" s="2" t="n"/>
+      <c r="I467" s="2" t="n"/>
+      <c r="J467" s="2" t="n"/>
+      <c r="K467" s="2" t="n"/>
+      <c r="L467" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="M467" t="n">
+        <v>1</v>
+      </c>
+      <c r="N467" t="n">
+        <v>1</v>
+      </c>
+      <c r="O467" t="n">
+        <v>4</v>
+      </c>
+      <c r="P467" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>5</v>
+      </c>
+      <c r="R467" t="n">
+        <v>2</v>
+      </c>
+      <c r="S467" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>1833.12</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>226773843</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>PAT119</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>PAT119CF</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>PAT119CF</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="n"/>
+      <c r="H468" s="2" t="n"/>
+      <c r="I468" s="2" t="n"/>
+      <c r="J468" s="2" t="n"/>
+      <c r="K468" s="2" t="n"/>
+      <c r="L468" t="n">
+        <v>131.29</v>
+      </c>
+      <c r="M468" t="n">
+        <v>1</v>
+      </c>
+      <c r="N468" t="n">
+        <v>1</v>
+      </c>
+      <c r="O468" t="n">
+        <v>3</v>
+      </c>
+      <c r="P468" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>4</v>
+      </c>
+      <c r="R468" t="n">
+        <v>3</v>
+      </c>
+      <c r="S468" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z468" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>2363.22</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>160809281</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>PMD057CF</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>PMD057CF</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J469" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L469" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M469" t="n">
+        <v>1</v>
+      </c>
+      <c r="N469" t="n">
+        <v>1</v>
+      </c>
+      <c r="O469" t="n">
+        <v>3</v>
+      </c>
+      <c r="P469" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>5</v>
+      </c>
+      <c r="R469" t="n">
+        <v>3</v>
+      </c>
+      <c r="S469" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z469" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>1965.6</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>222769922</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>PMD057FD</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>PMD057FD</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J470" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L470" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M470" t="n">
+        <v>1</v>
+      </c>
+      <c r="N470" t="n">
+        <v>1</v>
+      </c>
+      <c r="O470" t="n">
+        <v>2</v>
+      </c>
+      <c r="P470" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>3</v>
+      </c>
+      <c r="R470" t="n">
+        <v>2</v>
+      </c>
+      <c r="S470" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z470" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>1310.4</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>137502391</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>PMD057PT</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>PMD057PT</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J471" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L471" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M471" t="n">
+        <v>1</v>
+      </c>
+      <c r="O471" t="n">
+        <v>2</v>
+      </c>
+      <c r="P471" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>5</v>
+      </c>
+      <c r="R471" t="n">
+        <v>1</v>
+      </c>
+      <c r="S471" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z471" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>1310.4</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>137502392</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>PMD057</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>PMD057TN</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>PMD057TN</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>SANDALIA SALTO</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J472" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L472" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="M472" t="n">
+        <v>1</v>
+      </c>
+      <c r="N472" t="n">
+        <v>1</v>
+      </c>
+      <c r="O472" t="n">
+        <v>2</v>
+      </c>
+      <c r="P472" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>5</v>
+      </c>
+      <c r="R472" t="n">
+        <v>1</v>
+      </c>
+      <c r="S472" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>1310.4</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>226773985</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>PMD407</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>PMD407CF</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="n"/>
+      <c r="H473" s="2" t="n"/>
+      <c r="I473" s="2" t="n"/>
+      <c r="J473" s="2" t="n"/>
+      <c r="K473" s="2" t="n"/>
+      <c r="L473" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="M473" t="n">
+        <v>1</v>
+      </c>
+      <c r="N473" t="n">
+        <v>2</v>
+      </c>
+      <c r="O473" t="n">
+        <v>4</v>
+      </c>
+      <c r="P473" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>6</v>
+      </c>
+      <c r="R473" t="n">
+        <v>4</v>
+      </c>
+      <c r="S473" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z473" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA473" t="n">
+        <v>2644.32</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>226774180</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>PRA732CF</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="n"/>
+      <c r="H474" s="2" t="n"/>
+      <c r="I474" s="2" t="n"/>
+      <c r="J474" s="2" t="n"/>
+      <c r="K474" s="2" t="n"/>
+      <c r="L474" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M474" t="n">
+        <v>1</v>
+      </c>
+      <c r="N474" t="n">
+        <v>2</v>
+      </c>
+      <c r="O474" t="n">
+        <v>5</v>
+      </c>
+      <c r="P474" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>7</v>
+      </c>
+      <c r="R474" t="n">
+        <v>5</v>
+      </c>
+      <c r="S474" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>1840.5</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>105821</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>226774181</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>PRA732</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>PRA732VO</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="n"/>
+      <c r="H475" s="2" t="n"/>
+      <c r="I475" s="2" t="n"/>
+      <c r="J475" s="2" t="n"/>
+      <c r="K475" s="2" t="n"/>
+      <c r="L475" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="M475" t="n">
+        <v>1</v>
+      </c>
+      <c r="N475" t="n">
+        <v>1</v>
+      </c>
+      <c r="O475" t="n">
+        <v>3</v>
+      </c>
+      <c r="P475" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>4</v>
+      </c>
+      <c r="R475" t="n">
+        <v>3</v>
+      </c>
+      <c r="S475" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>1104.3</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>939642</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>LMM004MM</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J476" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L476" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M476" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y476" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z476" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>840.48</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>939643</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>LMM004</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>LMM004PT</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J477" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L477" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M477" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y477" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z477" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>1575.9</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>21174</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>LMM009</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>LMM009PT</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>LMM009PT</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J478" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L478" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M478" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y478" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z478" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>375.12</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>79775189</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>LMM619</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>LMM619BC</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>LMM619BC</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J479" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L479" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M479" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y479" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z479" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA479" t="n">
+        <v>919.8</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>79775190</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>LMM619</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>LMM619BG</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>LMM619BG</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J480" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L480" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M480" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y480" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z480" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>551.88</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>79775193</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>LMM619</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>LMM619PT</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>LMM619PT</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J481" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L481" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M481" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y481" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA481" t="n">
+        <v>1379.7</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>170577570</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>LMW005</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>LMW005BC</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>LMW005BC</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J482" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L482" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M482" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y482" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>133.92</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>105828</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>170577571</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>LMW005</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>LMW005PT</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>LMW005PT</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J483" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L483" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M483" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y483" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>267.84</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>105833</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>194876138</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>SSU030</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>SSU030CF</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>SSU030CF</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J484" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L484" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="M484" t="n">
+        <v>1</v>
+      </c>
+      <c r="S484" t="n">
+        <v>1</v>
+      </c>
+      <c r="T484" t="n">
+        <v>1</v>
+      </c>
+      <c r="U484" t="n">
+        <v>4</v>
+      </c>
+      <c r="V484" t="n">
+        <v>5</v>
+      </c>
+      <c r="W484" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z484" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>1199.04</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>105833</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>151143141</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SSU030</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>SSU030OW</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>SSU030OW</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J485" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L485" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="M485" t="n">
+        <v>1</v>
+      </c>
+      <c r="S485" t="n">
+        <v>2</v>
+      </c>
+      <c r="T485" t="n">
+        <v>3</v>
+      </c>
+      <c r="U485" t="n">
+        <v>7</v>
+      </c>
+      <c r="V485" t="n">
+        <v>5</v>
+      </c>
+      <c r="W485" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z485" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA485" t="n">
+        <v>1798.56</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>105833</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>151143142</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>SSU030</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>SSU030PT</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>SSU030PT</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J486" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L486" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="M486" t="n">
+        <v>1</v>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>2</v>
+      </c>
+      <c r="T486" t="n">
+        <v>2</v>
+      </c>
+      <c r="U486" t="n">
+        <v>3</v>
+      </c>
+      <c r="V486" t="n">
+        <v>6</v>
+      </c>
+      <c r="W486" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z486" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA486" t="n">
+        <v>1798.56</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>226773022</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>GBF191CF</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="n"/>
+      <c r="H487" s="2" t="n"/>
+      <c r="I487" s="2" t="n"/>
+      <c r="J487" s="2" t="n"/>
+      <c r="K487" s="2" t="n"/>
+      <c r="L487" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M487" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y487" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z487" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA487" t="n">
+        <v>971.96</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>226773023</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>GBF191</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>GBF191VO</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="n"/>
+      <c r="H488" s="2" t="n"/>
+      <c r="I488" s="2" t="n"/>
+      <c r="J488" s="2" t="n"/>
+      <c r="K488" s="2" t="n"/>
+      <c r="L488" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="M488" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y488" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z488" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA488" t="n">
+        <v>728.97</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>226773053</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>GBF253</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>GBF253PT</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>GBF253PT</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="n"/>
+      <c r="H489" s="2" t="n"/>
+      <c r="I489" s="2" t="n"/>
+      <c r="J489" s="2" t="n"/>
+      <c r="K489" s="2" t="n"/>
+      <c r="L489" t="n">
+        <v>191.29</v>
+      </c>
+      <c r="M489" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y489" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z489" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA489" t="n">
+        <v>382.58</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>226773054</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>GBF253</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>GBF253TN</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>GBF253TN</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="n"/>
+      <c r="H490" s="2" t="n"/>
+      <c r="I490" s="2" t="n"/>
+      <c r="J490" s="2" t="n"/>
+      <c r="K490" s="2" t="n"/>
+      <c r="L490" t="n">
+        <v>191.29</v>
+      </c>
+      <c r="M490" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y490" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z490" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA490" t="n">
+        <v>382.58</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>226773071</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>GBF269</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>GBF269FD</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="n"/>
+      <c r="H491" s="2" t="n"/>
+      <c r="I491" s="2" t="n"/>
+      <c r="J491" s="2" t="n"/>
+      <c r="K491" s="2" t="n"/>
+      <c r="L491" t="n">
+        <v>235</v>
+      </c>
+      <c r="M491" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y491" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z491" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA491" t="n">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>218687255</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>GBF445CF</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J492" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L492" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M492" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y492" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z492" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA492" t="n">
+        <v>490.68</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>58174815</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>GBF445</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>GBF445PT</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J493" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L493" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="M493" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y493" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z493" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA493" t="n">
+        <v>490.68</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>226773215</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>GBF786</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>GBF786CF</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="n"/>
+      <c r="H494" s="2" t="n"/>
+      <c r="I494" s="2" t="n"/>
+      <c r="J494" s="2" t="n"/>
+      <c r="K494" s="2" t="n"/>
+      <c r="L494" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="M494" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y494" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z494" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA494" t="n">
+        <v>802.76</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>226773217</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>GBF788PT</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="n"/>
+      <c r="H495" s="2" t="n"/>
+      <c r="I495" s="2" t="n"/>
+      <c r="J495" s="2" t="n"/>
+      <c r="K495" s="2" t="n"/>
+      <c r="L495" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M495" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y495" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z495" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA495" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>226773218</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>GBF788</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>GBF788TN</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="n"/>
+      <c r="H496" s="2" t="n"/>
+      <c r="I496" s="2" t="n"/>
+      <c r="J496" s="2" t="n"/>
+      <c r="K496" s="2" t="n"/>
+      <c r="L496" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="M496" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y496" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z496" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA496" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>62511719</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>GCA334</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>GCA334PT</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>GCA334PT</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J497" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L497" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="M497" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y497" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z497" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA497" t="n">
+        <v>913.6799999999999</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>65890198</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>GCA334</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>GCA334VR</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>GCA334VR</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J498" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L498" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="M498" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y498" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z498" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA498" t="n">
+        <v>913.6799999999999</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>205216493</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>GCA442</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>GCA442VR</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>GCA442VR</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J499" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L499" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="M499" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y499" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z499" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA499" t="n">
+        <v>563.28</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>205216494</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>GCA443</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>GCA443TN</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>GCA443TN</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J500" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L500" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="M500" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y500" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z500" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA500" t="n">
+        <v>433.62</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>16652</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>HCT054</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>HCT054CF</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>HCT054CF</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J501" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L501" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="M501" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y501" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z501" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA501" t="n">
+        <v>1098.48</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>16653</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>HCT054</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>HCT054PT</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>HCT054PT</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J502" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L502" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="M502" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y502" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z502" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA502" t="n">
+        <v>1098.48</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>10222948</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>HCT095</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>HCT095CF</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>HCT095CF</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J503" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L503" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="M503" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y503" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z503" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA503" t="n">
+        <v>444.15</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>10222949</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>HCT095</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>HCT095PT</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>HCT095PT</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J504" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L504" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="M504" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y504" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z504" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA504" t="n">
+        <v>444.15</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>10222950</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>HCT096</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>HCT096CF</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>HCT096CF</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J505" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L505" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="M505" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y505" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z505" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA505" t="n">
+        <v>549.36</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>12714422</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>HNM234</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>HNM234PT</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>HNM234PT</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J506" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L506" t="n">
+        <v>91.61</v>
+      </c>
+      <c r="M506" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y506" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z506" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA506" t="n">
+        <v>366.44</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>105823</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>12714423</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>HNM234</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>HNM234WK</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>HNM234WK</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J507" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L507" t="n">
+        <v>91.61</v>
+      </c>
+      <c r="M507" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y507" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z507" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA507" t="n">
+        <v>366.44</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>105829</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>13274</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>LMM016BC</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>LMM016BC</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J508" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L508" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M508" t="n">
+        <v>1</v>
+      </c>
+      <c r="P508" t="n">
+        <v>18</v>
+      </c>
+      <c r="T508" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z508" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA508" t="n">
+        <v>716.76</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>105829</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>23300</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>LMM016BG</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>LMM016BG</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J509" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L509" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M509" t="n">
+        <v>1</v>
+      </c>
+      <c r="P509" t="n">
+        <v>18</v>
+      </c>
+      <c r="T509" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z509" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA509" t="n">
+        <v>716.76</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>105829</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>4613</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>LMM016</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>LMM016PT</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>LMM016PT</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J510" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L510" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M510" t="n">
+        <v>1</v>
+      </c>
+      <c r="P510" t="n">
+        <v>24</v>
+      </c>
+      <c r="T510" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z510" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA510" t="n">
+        <v>955.6799999999999</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>105829</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>105185079</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>LMW200</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>LMW200ND</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>LMW200ND</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J511" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L511" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M511" t="n">
+        <v>1</v>
+      </c>
+      <c r="O511" t="n">
+        <v>12</v>
+      </c>
+      <c r="S511" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z511" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA511" t="n">
+        <v>472.08</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>105829</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>105185080</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>LMW200</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>LMW200PT</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>LMW200PT</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>VESTUARIO</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>MEIAS</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J512" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L512" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>18</v>
+      </c>
+      <c r="S512" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z512" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA512" t="n">
+        <v>708.12</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>105834</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>219741931</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>TBC193</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>TBC193PT</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>TBC193PT</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>SAPATILHA</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J513" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L513" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M513" t="n">
+        <v>1</v>
+      </c>
+      <c r="N513" t="n">
+        <v>1</v>
+      </c>
+      <c r="O513" t="n">
+        <v>2</v>
+      </c>
+      <c r="P513" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>3</v>
+      </c>
+      <c r="R513" t="n">
+        <v>2</v>
+      </c>
+      <c r="S513" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z513" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA513" t="n">
+        <v>1073.16</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>105834</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>219741932</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>TBC193</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>TBC193TN</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>TBC193TN</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>SAPATILHA</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J514" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L514" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M514" t="n">
+        <v>1</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>3</v>
+      </c>
+      <c r="P514" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>4</v>
+      </c>
+      <c r="R514" t="n">
+        <v>2</v>
+      </c>
+      <c r="S514" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z514" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA514" t="n">
+        <v>1341.45</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>105834</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>226799195</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>TEC164CF</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="n"/>
+      <c r="H515" s="2" t="n"/>
+      <c r="I515" s="2" t="n"/>
+      <c r="J515" s="2" t="n"/>
+      <c r="K515" s="2" t="n"/>
+      <c r="L515" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M515" t="n">
+        <v>1</v>
+      </c>
+      <c r="N515" t="n">
+        <v>2</v>
+      </c>
+      <c r="O515" t="n">
+        <v>3</v>
+      </c>
+      <c r="P515" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>4</v>
+      </c>
+      <c r="R515" t="n">
+        <v>2</v>
+      </c>
+      <c r="S515" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z515" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA515" t="n">
+        <v>1852.2</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>105834</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>226799196</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>TEC164FD</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>TEC164FD</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="n"/>
+      <c r="H516" s="2" t="n"/>
+      <c r="I516" s="2" t="n"/>
+      <c r="J516" s="2" t="n"/>
+      <c r="K516" s="2" t="n"/>
+      <c r="L516" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M516" t="n">
+        <v>1</v>
+      </c>
+      <c r="N516" t="n">
+        <v>1</v>
+      </c>
+      <c r="O516" t="n">
+        <v>3</v>
+      </c>
+      <c r="P516" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>4</v>
+      </c>
+      <c r="R516" t="n">
+        <v>2</v>
+      </c>
+      <c r="S516" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z516" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA516" t="n">
+        <v>1543.5</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>105834</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>226799197</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>TEC164</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>TEC164PT</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="n"/>
+      <c r="H517" s="2" t="n"/>
+      <c r="I517" s="2" t="n"/>
+      <c r="J517" s="2" t="n"/>
+      <c r="K517" s="2" t="n"/>
+      <c r="L517" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M517" t="n">
+        <v>1</v>
+      </c>
+      <c r="N517" t="n">
+        <v>2</v>
+      </c>
+      <c r="O517" t="n">
+        <v>3</v>
+      </c>
+      <c r="P517" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>4</v>
+      </c>
+      <c r="R517" t="n">
+        <v>2</v>
+      </c>
+      <c r="S517" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z517" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA517" t="n">
+        <v>1852.2</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>105824</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>73909424</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>GBF529</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>GBF529PT</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>GBF529PT</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J518" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L518" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="M518" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y518" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z518" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA518" t="n">
+        <v>460.8</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>105824</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>170739607</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>GBF801</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>GBF801CF</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>GBF801CF</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>BOLSA</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J519" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L519" t="n">
+        <v>234</v>
+      </c>
+      <c r="M519" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y519" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z519" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA519" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>105824</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>12078368</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>HMO032CF</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J520" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L520" t="n">
+        <v>348</v>
+      </c>
+      <c r="M520" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y520" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z520" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA520" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>105824</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>12078369</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>HMO032</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>HMO032PT</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>BOLSA MASCULINA</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J521" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L521" t="n">
+        <v>348</v>
+      </c>
+      <c r="M521" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y521" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z521" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA521" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>105835</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>226799135</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>TBE004BI</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>TBE004BI</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="n"/>
+      <c r="H522" s="2" t="n"/>
+      <c r="I522" s="2" t="n"/>
+      <c r="J522" s="2" t="n"/>
+      <c r="K522" s="2" t="n"/>
+      <c r="L522" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M522" t="n">
+        <v>1</v>
+      </c>
+      <c r="N522" t="n">
+        <v>2</v>
+      </c>
+      <c r="O522" t="n">
+        <v>4</v>
+      </c>
+      <c r="P522" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>6</v>
+      </c>
+      <c r="R522" t="n">
+        <v>4</v>
+      </c>
+      <c r="S522" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z522" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA522" t="n">
+        <v>1461.12</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>105835</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>226799136</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>TBE004OU</t>
+        </is>
+      </c>
+      <c r="G523" s="2" t="n"/>
+      <c r="H523" s="2" t="n"/>
+      <c r="I523" s="2" t="n"/>
+      <c r="J523" s="2" t="n"/>
+      <c r="K523" s="2" t="n"/>
+      <c r="L523" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M523" t="n">
+        <v>1</v>
+      </c>
+      <c r="N523" t="n">
+        <v>3</v>
+      </c>
+      <c r="O523" t="n">
+        <v>6</v>
+      </c>
+      <c r="P523" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>9</v>
+      </c>
+      <c r="R523" t="n">
+        <v>5</v>
+      </c>
+      <c r="S523" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z523" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA523" t="n">
+        <v>2191.68</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>105835</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>226799137</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>TBE004PT</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="n"/>
+      <c r="H524" s="2" t="n"/>
+      <c r="I524" s="2" t="n"/>
+      <c r="J524" s="2" t="n"/>
+      <c r="K524" s="2" t="n"/>
+      <c r="L524" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M524" t="n">
+        <v>1</v>
+      </c>
+      <c r="N524" t="n">
+        <v>3</v>
+      </c>
+      <c r="O524" t="n">
+        <v>6</v>
+      </c>
+      <c r="P524" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>9</v>
+      </c>
+      <c r="R524" t="n">
+        <v>5</v>
+      </c>
+      <c r="S524" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z524" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA524" t="n">
+        <v>2191.68</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>105835</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>226799138</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>TBE004</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>TBE004TN</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="n"/>
+      <c r="H525" s="2" t="n"/>
+      <c r="I525" s="2" t="n"/>
+      <c r="J525" s="2" t="n"/>
+      <c r="K525" s="2" t="n"/>
+      <c r="L525" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="M525" t="n">
+        <v>1</v>
+      </c>
+      <c r="N525" t="n">
+        <v>2</v>
+      </c>
+      <c r="O525" t="n">
+        <v>5</v>
+      </c>
+      <c r="P525" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>7</v>
+      </c>
+      <c r="R525" t="n">
+        <v>4</v>
+      </c>
+      <c r="S525" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z525" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA525" t="n">
+        <v>1826.4</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>99069512</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>ADP160</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>ADP160CF</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>ADP160CF</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J526" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L526" t="n">
+        <v>148.03</v>
+      </c>
+      <c r="M526" t="n">
+        <v>1</v>
+      </c>
+      <c r="S526" t="n">
+        <v>3</v>
+      </c>
+      <c r="T526" t="n">
+        <v>2</v>
+      </c>
+      <c r="U526" t="n">
+        <v>5</v>
+      </c>
+      <c r="V526" t="n">
+        <v>1</v>
+      </c>
+      <c r="W526" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z526" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA526" t="n">
+        <v>1776.36</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>99069557</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>AFB130</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>AFB130TC</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>AFB130TC</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J527" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L527" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="M527" t="n">
+        <v>1</v>
+      </c>
+      <c r="S527" t="n">
+        <v>3</v>
+      </c>
+      <c r="T527" t="n">
+        <v>3</v>
+      </c>
+      <c r="U527" t="n">
+        <v>4</v>
+      </c>
+      <c r="V527" t="n">
+        <v>3</v>
+      </c>
+      <c r="W527" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z527" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA527" t="n">
+        <v>1711.5</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>56456539</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>ASF950</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>ASF950TP</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>ASF950TP</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J528" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L528" t="n">
+        <v>124.86</v>
+      </c>
+      <c r="M528" t="n">
+        <v>1</v>
+      </c>
+      <c r="R528" t="n">
+        <v>1</v>
+      </c>
+      <c r="S528" t="n">
+        <v>2</v>
+      </c>
+      <c r="T528" t="n">
+        <v>2</v>
+      </c>
+      <c r="U528" t="n">
+        <v>3</v>
+      </c>
+      <c r="V528" t="n">
+        <v>2</v>
+      </c>
+      <c r="W528" t="n">
+        <v>1</v>
+      </c>
+      <c r="X528" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z528" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA528" t="n">
+        <v>1498.32</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>56045775</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>CAT001</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>CAT001TN</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>CAT001TN</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J529" t="n">
+        <v>639.9</v>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L529" t="n">
+        <v>227.11</v>
+      </c>
+      <c r="M529" t="n">
+        <v>1</v>
+      </c>
+      <c r="S529" t="n">
+        <v>3</v>
+      </c>
+      <c r="T529" t="n">
+        <v>4</v>
+      </c>
+      <c r="U529" t="n">
+        <v>2</v>
+      </c>
+      <c r="V529" t="n">
+        <v>2</v>
+      </c>
+      <c r="W529" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z529" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA529" t="n">
+        <v>2725.32</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>63032743</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>PRAD44</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>PRAD44TP</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>PRAD44TP</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>SANDALIA BIRKEN</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J530" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L530" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="M530" t="n">
+        <v>1</v>
+      </c>
+      <c r="N530" t="n">
+        <v>1</v>
+      </c>
+      <c r="O530" t="n">
+        <v>3</v>
+      </c>
+      <c r="P530" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>7</v>
+      </c>
+      <c r="R530" t="n">
+        <v>2</v>
+      </c>
+      <c r="S530" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z530" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA530" t="n">
+        <v>2150.28</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>62522833</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>SLB034</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>SLB034PT</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>SLB034PT</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J531" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L531" t="n">
+        <v>200.54</v>
+      </c>
+      <c r="M531" t="n">
+        <v>1</v>
+      </c>
+      <c r="R531" t="n">
+        <v>2</v>
+      </c>
+      <c r="S531" t="n">
+        <v>2</v>
+      </c>
+      <c r="T531" t="n">
+        <v>4</v>
+      </c>
+      <c r="U531" t="n">
+        <v>4</v>
+      </c>
+      <c r="V531" t="n">
+        <v>3</v>
+      </c>
+      <c r="W531" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z531" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA531" t="n">
+        <v>3609.72</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>226799440</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>WSCR54</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>WSCR54BC</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="n"/>
+      <c r="H532" s="2" t="n"/>
+      <c r="I532" s="2" t="n"/>
+      <c r="J532" s="2" t="n"/>
+      <c r="K532" s="2" t="n"/>
+      <c r="L532" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="M532" t="n">
+        <v>1</v>
+      </c>
+      <c r="N532" t="n">
+        <v>1</v>
+      </c>
+      <c r="O532" t="n">
+        <v>1</v>
+      </c>
+      <c r="P532" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>3</v>
+      </c>
+      <c r="R532" t="n">
+        <v>2</v>
+      </c>
+      <c r="S532" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z532" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA532" t="n">
+        <v>2540.16</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>226799445</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>WSCR57</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>WSCR57BI</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="n"/>
+      <c r="H533" s="2" t="n"/>
+      <c r="I533" s="2" t="n"/>
+      <c r="J533" s="2" t="n"/>
+      <c r="K533" s="2" t="n"/>
+      <c r="L533" t="n">
+        <v>159.25</v>
+      </c>
+      <c r="M533" t="n">
+        <v>1</v>
+      </c>
+      <c r="N533" t="n">
+        <v>1</v>
+      </c>
+      <c r="O533" t="n">
+        <v>3</v>
+      </c>
+      <c r="P533" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>5</v>
+      </c>
+      <c r="R533" t="n">
+        <v>3</v>
+      </c>
+      <c r="S533" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z533" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA533" t="n">
+        <v>2866.5</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>105818</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>226799459</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>WSCR89</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>WSCR89TN</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="n"/>
+      <c r="H534" s="2" t="n"/>
+      <c r="I534" s="2" t="n"/>
+      <c r="J534" s="2" t="n"/>
+      <c r="K534" s="2" t="n"/>
+      <c r="L534" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="M534" t="n">
+        <v>1</v>
+      </c>
+      <c r="N534" t="n">
+        <v>1</v>
+      </c>
+      <c r="O534" t="n">
+        <v>3</v>
+      </c>
+      <c r="P534" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>5</v>
+      </c>
+      <c r="R534" t="n">
+        <v>3</v>
+      </c>
+      <c r="S534" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z534" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA534" t="n">
+        <v>2908.44</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>105825</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>13035</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>HCT018</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>HCT018CF</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>HCT018CF</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J535" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L535" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="M535" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y535" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z535" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA535" t="n">
+        <v>858.48</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>105825</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>16143</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>HCT018</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>HCT018PT</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>HCT018PT</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>CARTEIRA</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J536" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L536" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="M536" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y536" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z536" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA536" t="n">
+        <v>1073.1</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>105825</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>8607946</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>MCC190</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>MCC190CF</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>MCC190CF</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J537" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L537" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="M537" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y537" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z537" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA537" t="n">
+        <v>278.16</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>105825</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>8619996</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>MCC190</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>MCC190PT</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>MCC190PT</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J538" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L538" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="M538" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y538" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z538" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA538" t="n">
+        <v>417.24</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>105825</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>60897674</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>MCC980</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>MCC980PT</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>MCC980PT</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>ACESSORIOS</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>COMPLEMENTOS</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>CLASSICO</t>
+        </is>
+      </c>
+      <c r="J539" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L539" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="M539" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y539" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z539" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA539" t="n">
+        <v>524.34</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>105830</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>227869440</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>PAB078</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>PAB078VO</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="n"/>
+      <c r="H540" s="2" t="n"/>
+      <c r="I540" s="2" t="n"/>
+      <c r="J540" s="2" t="n"/>
+      <c r="K540" s="2" t="n"/>
+      <c r="L540" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="M540" t="n">
+        <v>1</v>
+      </c>
+      <c r="N540" t="n">
+        <v>1</v>
+      </c>
+      <c r="O540" t="n">
+        <v>3</v>
+      </c>
+      <c r="P540" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>3</v>
+      </c>
+      <c r="R540" t="n">
+        <v>3</v>
+      </c>
+      <c r="S540" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z540" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA540" t="n">
+        <v>2239.65</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>105830</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>164260186</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>WCL099</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>WCL099CF</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>MOCASSIM</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J541" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L541" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="M541" t="n">
+        <v>1</v>
+      </c>
+      <c r="N541" t="n">
+        <v>1</v>
+      </c>
+      <c r="O541" t="n">
+        <v>3</v>
+      </c>
+      <c r="P541" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>1</v>
+      </c>
+      <c r="R541" t="n">
+        <v>1</v>
+      </c>
+      <c r="S541" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z541" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA541" t="n">
+        <v>1068.84</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>105830</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>226799259</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>WCL202</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>WCL202CA</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>WCL202CA</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="n"/>
+      <c r="H542" s="2" t="n"/>
+      <c r="I542" s="2" t="n"/>
+      <c r="J542" s="2" t="n"/>
+      <c r="K542" s="2" t="n"/>
+      <c r="L542" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="M542" t="n">
+        <v>1</v>
+      </c>
+      <c r="N542" t="n">
+        <v>1</v>
+      </c>
+      <c r="O542" t="n">
+        <v>2</v>
+      </c>
+      <c r="P542" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>3</v>
+      </c>
+      <c r="R542" t="n">
+        <v>2</v>
+      </c>
+      <c r="S542" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z542" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA542" t="n">
+        <v>1496.4</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>105830</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>226799260</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>WCL203</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>WCL203CF</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>WCL203CF</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="n"/>
+      <c r="H543" s="2" t="n"/>
+      <c r="I543" s="2" t="n"/>
+      <c r="J543" s="2" t="n"/>
+      <c r="K543" s="2" t="n"/>
+      <c r="L543" t="n">
+        <v>145.33</v>
+      </c>
+      <c r="M543" t="n">
+        <v>1</v>
+      </c>
+      <c r="N543" t="n">
+        <v>1</v>
+      </c>
+      <c r="O543" t="n">
+        <v>3</v>
+      </c>
+      <c r="P543" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>4</v>
+      </c>
+      <c r="R543" t="n">
+        <v>2</v>
+      </c>
+      <c r="S543" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z543" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA543" t="n">
+        <v>2179.95</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>105830</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>226799261</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>WCL204</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>WCL204CA</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>WCL204CA</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="n"/>
+      <c r="H544" s="2" t="n"/>
+      <c r="I544" s="2" t="n"/>
+      <c r="J544" s="2" t="n"/>
+      <c r="K544" s="2" t="n"/>
+      <c r="L544" t="n">
+        <v>154.12</v>
+      </c>
+      <c r="M544" t="n">
+        <v>1</v>
+      </c>
+      <c r="N544" t="n">
+        <v>1</v>
+      </c>
+      <c r="O544" t="n">
+        <v>3</v>
+      </c>
+      <c r="P544" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>4</v>
+      </c>
+      <c r="R544" t="n">
+        <v>2</v>
+      </c>
+      <c r="S544" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z544" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA544" t="n">
+        <v>2311.8</v>
       </c>
     </row>
   </sheetData>
@@ -29689,7 +37138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31591,21 +39040,21 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>105711</v>
+        <v>105818</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
+          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-18h59.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h18.xlsx</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -31614,99 +39063,99 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="G52" t="n">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="H52" t="n">
-        <v>8028.27</v>
+        <v>21786.6</v>
       </c>
       <c r="I52" t="n">
-        <v>8028.27</v>
+        <v>21786.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>105712</v>
+        <v>105819</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h18.xlsx</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G53" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H53" t="n">
-        <v>10472.17</v>
+        <v>4633.2</v>
       </c>
       <c r="I53" t="n">
-        <v>6141.03</v>
+        <v>4633.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>105718</v>
+        <v>105820</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h18.xlsx</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="G54" t="n">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="H54" t="n">
-        <v>6969.69</v>
+        <v>32226.15</v>
       </c>
       <c r="I54" t="n">
-        <v>6308.13</v>
+        <v>32226.15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>105719</v>
+        <v>105821</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -31716,7 +39165,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h18.xlsx</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -31725,72 +39174,61 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="G55" t="n">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="H55" t="n">
-        <v>11962.41</v>
+        <v>17982.96</v>
       </c>
       <c r="I55" t="n">
-        <v>11962.41</v>
+        <v>17982.96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>105720</v>
+        <v>105822</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>4_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>SEM ARQUIVO</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>76</v>
-      </c>
-      <c r="G56" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="H56" t="n">
-        <v>10980.3</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5077.98</v>
+        <v>20479.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>105721</v>
+        <v>105823</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>N C CALCADOS LTDA</t>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>5_RelB2bCarrinhoExcel-19h18.xlsx</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -31799,35 +39237,35 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="G57" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H57" t="n">
-        <v>7743.33</v>
+        <v>13527.57</v>
       </c>
       <c r="I57" t="n">
-        <v>7743.33</v>
+        <v>13527.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>105722</v>
+        <v>105824</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MASSEY CALCADOS LTDA</t>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5876a4d7-RelB2bCarrinhoExcel-19h04.xlsx</t>
+          <t>7_RelB2bCarrinhoExcel-19h18.xlsx</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -31836,35 +39274,35 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>10669.74</v>
+        <v>2440.8</v>
       </c>
       <c r="I58" t="n">
-        <v>10669.74</v>
+        <v>2440.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>105723</v>
+        <v>105825</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CALCADOS KISSOL LTDA</t>
+          <t>COURO &amp; ARTE LTDA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6_RelB2bCarrinhoExcel-19h00.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h19.xlsx</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -31873,35 +39311,35 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="H59" t="n">
-        <v>1808.1</v>
+        <v>3151.32</v>
       </c>
       <c r="I59" t="n">
-        <v>1808.1</v>
+        <v>3151.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>105724</v>
+        <v>105826</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h19.xlsx</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -31910,25 +39348,25 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="G60" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>4294.07</v>
+        <v>3024.67</v>
       </c>
       <c r="I60" t="n">
-        <v>4294.07</v>
+        <v>3024.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>105725</v>
+        <v>105827</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -31938,118 +39376,118 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h19.xlsx</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>2557.06</v>
+        <v>1248.44</v>
       </c>
       <c r="I61" t="n">
-        <v>1162.3</v>
+        <v>1248.44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>105726</v>
+        <v>105828</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>PRIMAR IND TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h19.xlsx</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>384</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>384</v>
       </c>
       <c r="H62" t="n">
-        <v>2536.8</v>
+        <v>6044.64</v>
       </c>
       <c r="I62" t="n">
-        <v>2068.8</v>
+        <v>6044.64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>105731</v>
+        <v>105829</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+          <t>L T BERTOLANI CONFECCAO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>5_RelB2bCarrinhoExcel-19h19.xlsx</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIVERGENTE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="G63" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="H63" t="n">
-        <v>18594.4</v>
+        <v>3569.4</v>
       </c>
       <c r="I63" t="n">
-        <v>7822.8</v>
+        <v>3569.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>105960</v>
+        <v>105830</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
+          <t>CALCADOS KARYBY LTDA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h01.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h20.xlsx</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -32058,35 +39496,35 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G64" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="H64" t="n">
-        <v>1930.5</v>
+        <v>9296.639999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>1930.5</v>
+        <v>9296.639999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>105961</v>
+        <v>105831</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h20.xlsx</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -32095,72 +39533,61 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G65" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="H65" t="n">
-        <v>8954.1</v>
+        <v>4042.5</v>
       </c>
       <c r="I65" t="n">
-        <v>8954.1</v>
+        <v>4042.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>105962</v>
+        <v>105832</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>3_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>SEM ARQUIVO</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
-      </c>
-      <c r="G66" t="n">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="H66" t="n">
-        <v>1017.08</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1017.08</v>
+        <v>8692.889999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>105963</v>
+        <v>105833</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PRIMAR IND TEXTIL LTDA</t>
+          <t>ZOTTO CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h20.xlsx</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -32169,35 +39596,35 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="G67" t="n">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="H67" t="n">
-        <v>2596.2</v>
+        <v>4796.16</v>
       </c>
       <c r="I67" t="n">
-        <v>2596.2</v>
+        <v>4796.16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>105964</v>
+        <v>105834</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>L T BERTOLANI CONFECCAO</t>
+          <t>N C CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6_RelB2bCarrinhoExcel-19h02.xlsx</t>
+          <t>6_RelB2bCarrinhoExcel-19h20.xlsx</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -32206,25 +39633,25 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="G68" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="H68" t="n">
-        <v>2377.68</v>
+        <v>7662.51</v>
       </c>
       <c r="I68" t="n">
-        <v>2377.68</v>
+        <v>7662.51</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>105965</v>
+        <v>105835</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SH. ELDORADO</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -32234,7 +39661,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h03.xlsx</t>
+          <t>7_RelB2bCarrinhoExcel-19h20.xlsx</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -32243,35 +39670,35 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="G69" t="n">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="H69" t="n">
-        <v>3287.52</v>
+        <v>7670.88</v>
       </c>
       <c r="I69" t="n">
-        <v>3287.52</v>
+        <v>7670.88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>105906</v>
+        <v>105836</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. TIJUCA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WW EXPORT LTDA</t>
+          <t>MASSEY CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h13.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h21.xlsx</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -32280,35 +39707,35 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="G70" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="H70" t="n">
-        <v>9964.469999999999</v>
+        <v>14815.8</v>
       </c>
       <c r="I70" t="n">
-        <v>9964.469999999999</v>
+        <v>14815.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>105907</v>
+        <v>105711</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h14.xlsx</t>
+          <t>RelB2bCarrinhoExcel-18h59.xlsx</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -32317,109 +39744,109 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="H71" t="n">
-        <v>1267.08</v>
+        <v>8028.27</v>
       </c>
       <c r="I71" t="n">
-        <v>1267.08</v>
+        <v>8028.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>105908</v>
+        <v>105712</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>CALCADOS KARYBY LTDA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h14.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G72" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="H72" t="n">
-        <v>3912</v>
+        <v>10472.17</v>
       </c>
       <c r="I72" t="n">
-        <v>3912</v>
+        <v>6141.03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>105909</v>
+        <v>105718</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h14.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="G73" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="H73" t="n">
-        <v>4599.89</v>
+        <v>6969.69</v>
       </c>
       <c r="I73" t="n">
-        <v>4599.89</v>
+        <v>6308.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>105910</v>
+        <v>105719</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+          <t>WW EXPORT LTDA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h14.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -32428,72 +39855,72 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="H74" t="n">
-        <v>508.54</v>
+        <v>11962.41</v>
       </c>
       <c r="I74" t="n">
-        <v>508.54</v>
+        <v>11962.41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>105911</v>
+        <v>105720</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PRIMAR IND TEXTIL LTDA</t>
+          <t>SR. DOS PES INDUSTRIA DE CALCADOS LTDA.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h14.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="G75" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="H75" t="n">
-        <v>3061.56</v>
+        <v>10980.3</v>
       </c>
       <c r="I75" t="n">
-        <v>3061.56</v>
+        <v>5077.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>105912</v>
+        <v>105721</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>L T BERTOLANI CONFECCAO</t>
+          <t>N C CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7_RelB2bCarrinhoExcel-19h14.xlsx</t>
+          <t>5_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -32502,35 +39929,35 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G76" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H76" t="n">
-        <v>1899.84</v>
+        <v>7743.33</v>
       </c>
       <c r="I76" t="n">
-        <v>1899.84</v>
+        <v>7743.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>105913</v>
+        <v>105722</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>MASSEY CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h15.xlsx</t>
+          <t>5876a4d7-RelB2bCarrinhoExcel-19h04.xlsx</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -32539,35 +39966,35 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="G77" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="H77" t="n">
-        <v>7626.15</v>
+        <v>10669.74</v>
       </c>
       <c r="I77" t="n">
-        <v>7626.15</v>
+        <v>10669.74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>105914</v>
+        <v>105723</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
+          <t>INDUSTRIA DE CALCADOS KISSOL LTDA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h15.xlsx</t>
+          <t>6_RelB2bCarrinhoExcel-19h00.xlsx</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -32576,35 +40003,35 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H78" t="n">
-        <v>4678.38</v>
+        <v>1808.1</v>
       </c>
       <c r="I78" t="n">
-        <v>4678.38</v>
+        <v>1808.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>105915</v>
+        <v>105724</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h15.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h01.xlsx</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -32613,146 +40040,146 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="G79" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="H79" t="n">
-        <v>6350.04</v>
+        <v>4294.07</v>
       </c>
       <c r="I79" t="n">
-        <v>6350.04</v>
+        <v>4294.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>105916</v>
+        <v>105725</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>D MATTHES CALCADOS LTDA</t>
+          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h15.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h01.xlsx</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="H80" t="n">
-        <v>4676.88</v>
+        <v>2557.06</v>
       </c>
       <c r="I80" t="n">
-        <v>4676.88</v>
+        <v>1162.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>105917</v>
+        <v>105726</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6_RelB2bCarrinhoExcel-19h15.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h01.xlsx</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G81" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>4361.58</v>
+        <v>2536.8</v>
       </c>
       <c r="I81" t="n">
-        <v>4361.58</v>
+        <v>2068.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>105918</v>
+        <v>105731</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>N C CALCADOS LTDA</t>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h16.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h01.xlsx</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DIVERGENTE</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="G82" t="n">
         <v>36</v>
       </c>
       <c r="H82" t="n">
-        <v>3542.76</v>
+        <v>18594.4</v>
       </c>
       <c r="I82" t="n">
-        <v>3542.76</v>
+        <v>7822.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>105919</v>
+        <v>105960</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MASSEY CALCADOS LTDA</t>
+          <t>A. G. M. INDUSTRIA DE CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h16.xlsx</t>
+          <t>5_RelB2bCarrinhoExcel-19h01.xlsx</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -32761,25 +40188,25 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G83" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="H83" t="n">
-        <v>5204.58</v>
+        <v>1930.5</v>
       </c>
       <c r="I83" t="n">
-        <v>5204.58</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>105920</v>
+        <v>105961</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SH. RIO SUL 1</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -32789,7 +40216,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h16.xlsx</t>
+          <t>2_RelB2bCarrinhoExcel-19h02.xlsx</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -32798,35 +40225,35 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G84" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H84" t="n">
-        <v>7352.61</v>
+        <v>8954.1</v>
       </c>
       <c r="I84" t="n">
-        <v>7352.61</v>
+        <v>8954.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>105838</v>
+        <v>105962</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CLASSE COURO DISTRIBUIDORA</t>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>3_RelB2bCarrinhoExcel-19h02.xlsx</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -32835,35 +40262,35 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H85" t="n">
-        <v>864.8099999999999</v>
+        <v>1017.08</v>
       </c>
       <c r="I85" t="n">
-        <v>864.8099999999999</v>
+        <v>1017.08</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>105839</v>
+        <v>105963</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+          <t>PRIMAR IND TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>4_RelB2bCarrinhoExcel-19h02.xlsx</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -32872,35 +40299,35 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="H86" t="n">
-        <v>1044</v>
+        <v>2596.2</v>
       </c>
       <c r="I86" t="n">
-        <v>1044</v>
+        <v>2596.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>105840</v>
+        <v>105964</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+          <t>L T BERTOLANI CONFECCAO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>6_RelB2bCarrinhoExcel-19h02.xlsx</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -32909,35 +40336,35 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H87" t="n">
-        <v>254.27</v>
+        <v>2377.68</v>
       </c>
       <c r="I87" t="n">
-        <v>254.27</v>
+        <v>2377.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>105841</v>
+        <v>105965</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. ELDORADO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CALCADOS KARYBY LTDA</t>
+          <t>D MATTHES CALCADOS LTDA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h03.xlsx</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -32946,25 +40373,25 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G88" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="H88" t="n">
-        <v>3267.72</v>
+        <v>3287.52</v>
       </c>
       <c r="I88" t="n">
-        <v>3267.72</v>
+        <v>3287.52</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>105842</v>
+        <v>105906</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SH. PARK SUL</t>
+          <t>SH. RIO SUL 1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -32974,7 +40401,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+          <t>RelB2bCarrinhoExcel-19h13.xlsx</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -32983,52 +40410,755 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="G89" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="H89" t="n">
-        <v>2095.92</v>
+        <v>9964.469999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>2095.92</v>
+        <v>9964.469999999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
+        <v>105907</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>M &amp; R ARTEFATOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1267.08</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1267.08</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>105908</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>15</v>
+      </c>
+      <c r="G91" t="n">
+        <v>15</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3912</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>105909</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>28</v>
+      </c>
+      <c r="G92" t="n">
+        <v>28</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4599.89</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4599.89</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>105910</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>508.54</v>
+      </c>
+      <c r="I93" t="n">
+        <v>508.54</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>105911</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PRIMAR IND TEXTIL LTDA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>180</v>
+      </c>
+      <c r="G94" t="n">
+        <v>180</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3061.56</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3061.56</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>105912</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>L T BERTOLANI CONFECCAO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>7_RelB2bCarrinhoExcel-19h14.xlsx</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>96</v>
+      </c>
+      <c r="G95" t="n">
+        <v>96</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1899.84</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1899.84</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>105913</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>60</v>
+      </c>
+      <c r="G96" t="n">
+        <v>60</v>
+      </c>
+      <c r="H96" t="n">
+        <v>7626.15</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7626.15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>105914</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SEPHORA INDUSTRIA DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>36</v>
+      </c>
+      <c r="G97" t="n">
+        <v>36</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4678.38</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4678.38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>105915</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>78</v>
+      </c>
+      <c r="G98" t="n">
+        <v>78</v>
+      </c>
+      <c r="H98" t="n">
+        <v>6350.04</v>
+      </c>
+      <c r="I98" t="n">
+        <v>6350.04</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>105916</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>D MATTHES CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>78</v>
+      </c>
+      <c r="G99" t="n">
+        <v>78</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4676.88</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4676.88</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>105917</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6_RelB2bCarrinhoExcel-19h15.xlsx</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>18</v>
+      </c>
+      <c r="G100" t="n">
+        <v>18</v>
+      </c>
+      <c r="H100" t="n">
+        <v>4361.58</v>
+      </c>
+      <c r="I100" t="n">
+        <v>4361.58</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>105918</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>N C CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h16.xlsx</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>36</v>
+      </c>
+      <c r="G101" t="n">
+        <v>36</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3542.76</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3542.76</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>105919</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MASSEY CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h16.xlsx</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>54</v>
+      </c>
+      <c r="G102" t="n">
+        <v>54</v>
+      </c>
+      <c r="H102" t="n">
+        <v>5204.58</v>
+      </c>
+      <c r="I102" t="n">
+        <v>5204.58</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>105920</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SH. RIO SUL 1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CALCADOS PACIN LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h16.xlsx</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>42</v>
+      </c>
+      <c r="G103" t="n">
+        <v>42</v>
+      </c>
+      <c r="H103" t="n">
+        <v>7352.61</v>
+      </c>
+      <c r="I103" t="n">
+        <v>7352.61</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>105838</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CLASSE COURO DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>6</v>
+      </c>
+      <c r="G104" t="n">
+        <v>6</v>
+      </c>
+      <c r="H104" t="n">
+        <v>864.8099999999999</v>
+      </c>
+      <c r="I104" t="n">
+        <v>864.8099999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>105839</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RAZZAZ ACESSORIOS E ARTIGOS DE COURO LTDA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105840</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BMCG INDUSTRIA E COMERCIO DE COURO LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="I106" t="n">
+        <v>254.27</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105841</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CALCADOS KARYBY LTDA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>4_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>27</v>
+      </c>
+      <c r="G107" t="n">
+        <v>27</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3267.72</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3267.72</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>105842</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SH. PARK SUL</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>WW EXPORT LTDA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5_RelB2bCarrinhoExcel-19h07.xlsx</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>27</v>
+      </c>
+      <c r="G108" t="n">
+        <v>27</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2095.92</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2095.92</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
         <v>105843</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>SH. PARK SUL</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>RelB2bCarrinhoExcel-19h08.xlsx</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F90" t="n">
+      <c r="F109" t="n">
         <v>9</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G109" t="n">
         <v>9</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H109" t="n">
         <v>2180.79</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I109" t="n">
         <v>2180.79</v>
       </c>
     </row>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA550"/>
+  <dimension ref="A1:AA563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37391,6 +37391,876 @@
         <v>2311.8</v>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>198486332</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>CAB302</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>CAB302PT</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>CAB302PT</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="J551" t="n">
+        <v>699.9</v>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L551" t="n">
+        <v>250.92</v>
+      </c>
+      <c r="M551" t="n">
+        <v>1</v>
+      </c>
+      <c r="S551" t="n">
+        <v>1</v>
+      </c>
+      <c r="T551" t="n">
+        <v>2</v>
+      </c>
+      <c r="U551" t="n">
+        <v>2</v>
+      </c>
+      <c r="V551" t="n">
+        <v>2</v>
+      </c>
+      <c r="W551" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z551" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA551" t="n">
+        <v>2258.28</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>226772891</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>CAR112</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>CAR112PT</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>CAR112PT</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="n"/>
+      <c r="H552" s="2" t="n"/>
+      <c r="I552" s="2" t="n"/>
+      <c r="J552" s="2" t="n"/>
+      <c r="K552" s="2" t="n"/>
+      <c r="L552" t="n">
+        <v>268.14</v>
+      </c>
+      <c r="M552" t="n">
+        <v>1</v>
+      </c>
+      <c r="R552" t="n">
+        <v>1</v>
+      </c>
+      <c r="S552" t="n">
+        <v>2</v>
+      </c>
+      <c r="T552" t="n">
+        <v>3</v>
+      </c>
+      <c r="U552" t="n">
+        <v>2</v>
+      </c>
+      <c r="V552" t="n">
+        <v>2</v>
+      </c>
+      <c r="W552" t="n">
+        <v>1</v>
+      </c>
+      <c r="X552" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z552" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA552" t="n">
+        <v>3217.68</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>226772892</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>CAR113</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>CAR113CF</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>CAR113CF</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="n"/>
+      <c r="H553" s="2" t="n"/>
+      <c r="I553" s="2" t="n"/>
+      <c r="J553" s="2" t="n"/>
+      <c r="K553" s="2" t="n"/>
+      <c r="L553" t="n">
+        <v>268.14</v>
+      </c>
+      <c r="M553" t="n">
+        <v>1</v>
+      </c>
+      <c r="R553" t="n">
+        <v>1</v>
+      </c>
+      <c r="S553" t="n">
+        <v>2</v>
+      </c>
+      <c r="T553" t="n">
+        <v>3</v>
+      </c>
+      <c r="U553" t="n">
+        <v>2</v>
+      </c>
+      <c r="V553" t="n">
+        <v>2</v>
+      </c>
+      <c r="W553" t="n">
+        <v>1</v>
+      </c>
+      <c r="X553" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z553" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA553" t="n">
+        <v>3217.68</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>226772990</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>DTR013</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>DTR013MR</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>DTR013MR</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="n"/>
+      <c r="H554" s="2" t="n"/>
+      <c r="I554" s="2" t="n"/>
+      <c r="J554" s="2" t="n"/>
+      <c r="K554" s="2" t="n"/>
+      <c r="L554" t="n">
+        <v>167.28</v>
+      </c>
+      <c r="M554" t="n">
+        <v>1</v>
+      </c>
+      <c r="R554" t="n">
+        <v>1</v>
+      </c>
+      <c r="S554" t="n">
+        <v>2</v>
+      </c>
+      <c r="T554" t="n">
+        <v>3</v>
+      </c>
+      <c r="U554" t="n">
+        <v>4</v>
+      </c>
+      <c r="V554" t="n">
+        <v>3</v>
+      </c>
+      <c r="W554" t="n">
+        <v>1</v>
+      </c>
+      <c r="X554" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z554" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA554" t="n">
+        <v>2509.2</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>226772991</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>DTR013</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>DTR013PT</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>DTR013PT</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="n"/>
+      <c r="H555" s="2" t="n"/>
+      <c r="I555" s="2" t="n"/>
+      <c r="J555" s="2" t="n"/>
+      <c r="K555" s="2" t="n"/>
+      <c r="L555" t="n">
+        <v>167.28</v>
+      </c>
+      <c r="M555" t="n">
+        <v>1</v>
+      </c>
+      <c r="R555" t="n">
+        <v>1</v>
+      </c>
+      <c r="S555" t="n">
+        <v>2</v>
+      </c>
+      <c r="T555" t="n">
+        <v>3</v>
+      </c>
+      <c r="U555" t="n">
+        <v>2</v>
+      </c>
+      <c r="V555" t="n">
+        <v>2</v>
+      </c>
+      <c r="W555" t="n">
+        <v>1</v>
+      </c>
+      <c r="X555" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z555" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA555" t="n">
+        <v>2007.36</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>226780323</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>SLG010MR</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>SLG010MR</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="n"/>
+      <c r="H556" s="2" t="n"/>
+      <c r="I556" s="2" t="n"/>
+      <c r="J556" s="2" t="n"/>
+      <c r="K556" s="2" t="n"/>
+      <c r="L556" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M556" t="n">
+        <v>1</v>
+      </c>
+      <c r="R556" t="n">
+        <v>1</v>
+      </c>
+      <c r="S556" t="n">
+        <v>2</v>
+      </c>
+      <c r="T556" t="n">
+        <v>3</v>
+      </c>
+      <c r="U556" t="n">
+        <v>3</v>
+      </c>
+      <c r="V556" t="n">
+        <v>3</v>
+      </c>
+      <c r="W556" t="n">
+        <v>2</v>
+      </c>
+      <c r="X556" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z556" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA556" t="n">
+        <v>3634.65</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>105822</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>226780324</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>SLG010</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>SLG010PT</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="n"/>
+      <c r="H557" s="2" t="n"/>
+      <c r="I557" s="2" t="n"/>
+      <c r="J557" s="2" t="n"/>
+      <c r="K557" s="2" t="n"/>
+      <c r="L557" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="M557" t="n">
+        <v>1</v>
+      </c>
+      <c r="R557" t="n">
+        <v>1</v>
+      </c>
+      <c r="S557" t="n">
+        <v>2</v>
+      </c>
+      <c r="T557" t="n">
+        <v>3</v>
+      </c>
+      <c r="U557" t="n">
+        <v>3</v>
+      </c>
+      <c r="V557" t="n">
+        <v>3</v>
+      </c>
+      <c r="W557" t="n">
+        <v>2</v>
+      </c>
+      <c r="X557" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z557" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA557" t="n">
+        <v>3634.65</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>105832</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>226773909</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>PAX634</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>PAX634CA</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="n"/>
+      <c r="H558" s="2" t="n"/>
+      <c r="I558" s="2" t="n"/>
+      <c r="J558" s="2" t="n"/>
+      <c r="K558" s="2" t="n"/>
+      <c r="L558" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="M558" t="n">
+        <v>1</v>
+      </c>
+      <c r="N558" t="n">
+        <v>1</v>
+      </c>
+      <c r="O558" t="n">
+        <v>3</v>
+      </c>
+      <c r="P558" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>4</v>
+      </c>
+      <c r="R558" t="n">
+        <v>3</v>
+      </c>
+      <c r="S558" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z558" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA558" t="n">
+        <v>1825.74</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>105832</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>178969123</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>PRA127</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>PRA127CF</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>PRA127CF</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>SANDALIA RASTEIRA</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>INVERNO</t>
+        </is>
+      </c>
+      <c r="J559" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L559" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="M559" t="n">
+        <v>1</v>
+      </c>
+      <c r="N559" t="n">
+        <v>1</v>
+      </c>
+      <c r="O559" t="n">
+        <v>3</v>
+      </c>
+      <c r="P559" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q559" t="n">
+        <v>4</v>
+      </c>
+      <c r="R559" t="n">
+        <v>3</v>
+      </c>
+      <c r="S559" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z559" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA559" t="n">
+        <v>1100.34</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>105832</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>226774175</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>PRA728FD</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="n"/>
+      <c r="H560" s="2" t="n"/>
+      <c r="I560" s="2" t="n"/>
+      <c r="J560" s="2" t="n"/>
+      <c r="K560" s="2" t="n"/>
+      <c r="L560" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M560" t="n">
+        <v>1</v>
+      </c>
+      <c r="N560" t="n">
+        <v>2</v>
+      </c>
+      <c r="O560" t="n">
+        <v>4</v>
+      </c>
+      <c r="P560" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q560" t="n">
+        <v>5</v>
+      </c>
+      <c r="R560" t="n">
+        <v>4</v>
+      </c>
+      <c r="S560" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z560" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA560" t="n">
+        <v>1702.32</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>105832</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>226774176</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>PRA728</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>PRA728VO</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="n"/>
+      <c r="H561" s="2" t="n"/>
+      <c r="I561" s="2" t="n"/>
+      <c r="J561" s="2" t="n"/>
+      <c r="K561" s="2" t="n"/>
+      <c r="L561" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="M561" t="n">
+        <v>1</v>
+      </c>
+      <c r="N561" t="n">
+        <v>1</v>
+      </c>
+      <c r="O561" t="n">
+        <v>3</v>
+      </c>
+      <c r="P561" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>4</v>
+      </c>
+      <c r="R561" t="n">
+        <v>2</v>
+      </c>
+      <c r="S561" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z561" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA561" t="n">
+        <v>1063.95</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>105832</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>226774179</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>PRA730</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>PRA730CA</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>PRA730CA</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="n"/>
+      <c r="H562" s="2" t="n"/>
+      <c r="I562" s="2" t="n"/>
+      <c r="J562" s="2" t="n"/>
+      <c r="K562" s="2" t="n"/>
+      <c r="L562" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="M562" t="n">
+        <v>1</v>
+      </c>
+      <c r="N562" t="n">
+        <v>1</v>
+      </c>
+      <c r="O562" t="n">
+        <v>3</v>
+      </c>
+      <c r="P562" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q562" t="n">
+        <v>3</v>
+      </c>
+      <c r="R562" t="n">
+        <v>3</v>
+      </c>
+      <c r="S562" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z562" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA562" t="n">
+        <v>1633.5</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>105832</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>SH. TIJUCA</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>226799120</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>TBC207</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>TBC207CA</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="n"/>
+      <c r="H563" s="2" t="n"/>
+      <c r="I563" s="2" t="n"/>
+      <c r="J563" s="2" t="n"/>
+      <c r="K563" s="2" t="n"/>
+      <c r="L563" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="M563" t="n">
+        <v>1</v>
+      </c>
+      <c r="N563" t="n">
+        <v>2</v>
+      </c>
+      <c r="O563" t="n">
+        <v>4</v>
+      </c>
+      <c r="P563" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q563" t="n">
+        <v>6</v>
+      </c>
+      <c r="R563" t="n">
+        <v>4</v>
+      </c>
+      <c r="S563" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z563" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA563" t="n">
+        <v>1367.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39464,15 +40334,26 @@
           <t>J. B. SHOES INDUSTRIA E COMERCIO DE CALCADOS LTDA - ME</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1b67292a-RelB2bCarrinhoExcel-19h30.xlsx</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SEM ARQUIVO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>90</v>
       </c>
+      <c r="G56" t="n">
+        <v>90</v>
+      </c>
       <c r="H56" t="n">
+        <v>20479.5</v>
+      </c>
+      <c r="I56" t="n">
         <v>20479.5</v>
       </c>
     </row>
@@ -39823,15 +40704,26 @@
           <t>FABRICACAO DE CALCADOS PERTHO LTDA</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7ce5fc48-2_RelB2bCarrinhoExcel-19h30.xlsx</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SEM ARQUIVO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>114</v>
       </c>
+      <c r="G66" t="n">
+        <v>114</v>
+      </c>
       <c r="H66" t="n">
+        <v>8692.889999999999</v>
+      </c>
+      <c r="I66" t="n">
         <v>8692.889999999999</v>
       </c>
     </row>

--- a/pedidos/Pedidos_Fev27_Unificado.xlsx
+++ b/pedidos/Pedidos_Fev27_Unificado.xlsx
@@ -577,7 +577,11 @@
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" t="n">
@@ -727,7 +731,11 @@
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" t="n">
@@ -931,7 +939,11 @@
       </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" t="n">
@@ -994,7 +1006,11 @@
       </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" t="n">
@@ -1057,7 +1073,11 @@
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" t="n">
@@ -1120,7 +1140,11 @@
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" t="n">
@@ -1183,7 +1207,11 @@
       </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" t="n">
@@ -1510,7 +1538,11 @@
       </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" t="n">
@@ -1573,7 +1605,11 @@
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" t="n">
@@ -1636,7 +1672,11 @@
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" t="n">
@@ -1687,21 +1727,31 @@
           <t>WSC330</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L19" t="n">
         <v>68.31999999999999</v>
       </c>
@@ -1924,7 +1974,11 @@
       </c>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" t="n">
@@ -1987,7 +2041,11 @@
       </c>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" t="n">
@@ -2512,7 +2570,11 @@
       </c>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" t="n">
@@ -2560,7 +2622,11 @@
       </c>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" t="n">
@@ -2608,7 +2674,11 @@
       </c>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" t="n">
@@ -2788,7 +2858,11 @@
       </c>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" t="n">
@@ -2836,7 +2910,11 @@
       </c>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" t="n">
@@ -2884,7 +2962,11 @@
       </c>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" t="n">
@@ -3874,7 +3956,11 @@
       </c>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" t="n">
@@ -3937,7 +4023,11 @@
       </c>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" t="n">
@@ -3988,21 +4078,39 @@
           <t>SAF126</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="L54" t="n">
         <v>135.3</v>
       </c>
@@ -4150,7 +4258,11 @@
       </c>
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="2" t="n"/>
       <c r="L56" t="n">
@@ -4720,7 +4832,11 @@
       </c>
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
       <c r="L64" t="n">
@@ -4783,7 +4899,11 @@
       </c>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" t="n">
@@ -4846,7 +4966,11 @@
       </c>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" t="n">
@@ -5065,21 +5189,39 @@
           <t>SAF126</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="L69" t="n">
         <v>135.3</v>
       </c>
@@ -5815,7 +5957,11 @@
       </c>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" t="n">
@@ -6127,7 +6273,11 @@
       </c>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="n"/>
       <c r="K82" s="2" t="n"/>
       <c r="L82" t="n">
@@ -6190,7 +6340,11 @@
       </c>
       <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="n"/>
       <c r="K83" s="2" t="n"/>
       <c r="L83" t="n">
@@ -6253,7 +6407,11 @@
       </c>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n"/>
       <c r="L84" t="n">
@@ -6316,7 +6474,11 @@
       </c>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="n"/>
       <c r="K85" s="2" t="n"/>
       <c r="L85" t="n">
@@ -6379,7 +6541,11 @@
       </c>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="n"/>
       <c r="K86" s="2" t="n"/>
       <c r="L86" t="n">
@@ -6442,7 +6608,11 @@
       </c>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="n"/>
       <c r="K87" s="2" t="n"/>
       <c r="L87" t="n">
@@ -6505,7 +6675,11 @@
       </c>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="n"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="2" t="n"/>
       <c r="L88" t="n">
@@ -7165,21 +7339,31 @@
           <t>WSC330</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L98" t="n">
         <v>68.31999999999999</v>
       </c>
@@ -7840,7 +8024,11 @@
       </c>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="n"/>
       <c r="K107" s="2" t="n"/>
       <c r="L107" t="n">
@@ -7906,7 +8094,11 @@
       </c>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="n"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="n"/>
       <c r="K108" s="2" t="n"/>
       <c r="L108" t="n">
@@ -8557,7 +8749,11 @@
       </c>
       <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="n"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J116" s="2" t="n"/>
       <c r="K116" s="2" t="n"/>
       <c r="L116" t="n">
@@ -8623,7 +8819,11 @@
       </c>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
-      <c r="I117" s="2" t="n"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J117" s="2" t="n"/>
       <c r="K117" s="2" t="n"/>
       <c r="L117" t="n">
@@ -8689,7 +8889,11 @@
       </c>
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="n"/>
       <c r="K118" s="2" t="n"/>
       <c r="L118" t="n">
@@ -8755,7 +8959,11 @@
       </c>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J119" s="2" t="n"/>
       <c r="K119" s="2" t="n"/>
       <c r="L119" t="n">
@@ -9085,7 +9293,11 @@
       </c>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J124" s="2" t="n"/>
       <c r="K124" s="2" t="n"/>
       <c r="L124" t="n">
@@ -9148,7 +9360,11 @@
       </c>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
-      <c r="I125" s="2" t="n"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J125" s="2" t="n"/>
       <c r="K125" s="2" t="n"/>
       <c r="L125" t="n">
@@ -9211,7 +9427,11 @@
       </c>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J126" s="2" t="n"/>
       <c r="K126" s="2" t="n"/>
       <c r="L126" t="n">
@@ -10462,7 +10682,11 @@
       </c>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="n"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J145" s="2" t="n"/>
       <c r="K145" s="2" t="n"/>
       <c r="L145" t="n">
@@ -10525,7 +10749,11 @@
       </c>
       <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="n"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J146" s="2" t="n"/>
       <c r="K146" s="2" t="n"/>
       <c r="L146" t="n">
@@ -10588,7 +10816,11 @@
       </c>
       <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="n"/>
-      <c r="I147" s="2" t="n"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="n"/>
       <c r="K147" s="2" t="n"/>
       <c r="L147" t="n">
@@ -10651,7 +10883,11 @@
       </c>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="n"/>
       <c r="K148" s="2" t="n"/>
       <c r="L148" t="n">
@@ -10714,7 +10950,11 @@
       </c>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
-      <c r="I149" s="2" t="n"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J149" s="2" t="n"/>
       <c r="K149" s="2" t="n"/>
       <c r="L149" t="n">
@@ -10777,7 +11017,11 @@
       </c>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
-      <c r="I150" s="2" t="n"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="n"/>
       <c r="K150" s="2" t="n"/>
       <c r="L150" t="n">
@@ -10825,7 +11069,11 @@
       </c>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
-      <c r="I151" s="2" t="n"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J151" s="2" t="n"/>
       <c r="K151" s="2" t="n"/>
       <c r="L151" t="n">
@@ -10873,7 +11121,11 @@
       </c>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
-      <c r="I152" s="2" t="n"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="n"/>
       <c r="K152" s="2" t="n"/>
       <c r="L152" t="n">
@@ -10921,7 +11173,11 @@
       </c>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
-      <c r="I153" s="2" t="n"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J153" s="2" t="n"/>
       <c r="K153" s="2" t="n"/>
       <c r="L153" t="n">
@@ -10969,7 +11225,11 @@
       </c>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="n"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="n"/>
       <c r="K154" s="2" t="n"/>
       <c r="L154" t="n">
@@ -11281,7 +11541,11 @@
       </c>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
-      <c r="I159" s="2" t="n"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J159" s="2" t="n"/>
       <c r="K159" s="2" t="n"/>
       <c r="L159" t="n">
@@ -11329,7 +11593,11 @@
       </c>
       <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="n"/>
-      <c r="I160" s="2" t="n"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J160" s="2" t="n"/>
       <c r="K160" s="2" t="n"/>
       <c r="L160" t="n">
@@ -11377,7 +11645,11 @@
       </c>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J161" s="2" t="n"/>
       <c r="K161" s="2" t="n"/>
       <c r="L161" t="n">
@@ -12349,7 +12621,11 @@
       </c>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
-      <c r="I176" s="2" t="n"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="n"/>
       <c r="K176" s="2" t="n"/>
       <c r="L176" t="n">
@@ -12412,7 +12688,11 @@
       </c>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
-      <c r="I177" s="2" t="n"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J177" s="2" t="n"/>
       <c r="K177" s="2" t="n"/>
       <c r="L177" t="n">
@@ -12475,7 +12755,11 @@
       </c>
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
-      <c r="I178" s="2" t="n"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="n"/>
       <c r="K178" s="2" t="n"/>
       <c r="L178" t="n">
@@ -12538,7 +12822,11 @@
       </c>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="n"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="n"/>
       <c r="K179" s="2" t="n"/>
       <c r="L179" t="n">
@@ -12601,7 +12889,11 @@
       </c>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="n"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="n"/>
       <c r="K180" s="2" t="n"/>
       <c r="L180" t="n">
@@ -12991,7 +13283,11 @@
       </c>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
-      <c r="I185" s="2" t="n"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J185" s="2" t="n"/>
       <c r="K185" s="2" t="n"/>
       <c r="L185" t="n">
@@ -13054,7 +13350,11 @@
       </c>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
-      <c r="I186" s="2" t="n"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J186" s="2" t="n"/>
       <c r="K186" s="2" t="n"/>
       <c r="L186" t="n">
@@ -13117,7 +13417,11 @@
       </c>
       <c r="G187" s="2" t="n"/>
       <c r="H187" s="2" t="n"/>
-      <c r="I187" s="2" t="n"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="n"/>
       <c r="K187" s="2" t="n"/>
       <c r="L187" t="n">
@@ -13180,7 +13484,11 @@
       </c>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
-      <c r="I188" s="2" t="n"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="n"/>
       <c r="K188" s="2" t="n"/>
       <c r="L188" t="n">
@@ -13243,7 +13551,11 @@
       </c>
       <c r="G189" s="2" t="n"/>
       <c r="H189" s="2" t="n"/>
-      <c r="I189" s="2" t="n"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J189" s="2" t="n"/>
       <c r="K189" s="2" t="n"/>
       <c r="L189" t="n">
@@ -13807,7 +14119,11 @@
       </c>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
-      <c r="I196" s="2" t="n"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J196" s="2" t="n"/>
       <c r="K196" s="2" t="n"/>
       <c r="L196" t="n">
@@ -13870,7 +14186,11 @@
       </c>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
-      <c r="I197" s="2" t="n"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J197" s="2" t="n"/>
       <c r="K197" s="2" t="n"/>
       <c r="L197" t="n">
@@ -13933,7 +14253,11 @@
       </c>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
-      <c r="I198" s="2" t="n"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="n"/>
       <c r="K198" s="2" t="n"/>
       <c r="L198" t="n">
@@ -13984,21 +14308,31 @@
           <t>ASF182</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="G199" s="2" t="n"/>
-      <c r="H199" s="2" t="n"/>
-      <c r="I199" s="2" t="n"/>
-      <c r="J199" s="2" t="n"/>
-      <c r="K199" s="2" t="n"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L199" t="n">
         <v>64.34999999999999</v>
       </c>
@@ -14290,7 +14624,11 @@
       </c>
       <c r="G203" s="2" t="n"/>
       <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="n"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J203" s="2" t="n"/>
       <c r="K203" s="2" t="n"/>
       <c r="L203" t="n">
@@ -14353,7 +14691,11 @@
       </c>
       <c r="G204" s="2" t="n"/>
       <c r="H204" s="2" t="n"/>
-      <c r="I204" s="2" t="n"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J204" s="2" t="n"/>
       <c r="K204" s="2" t="n"/>
       <c r="L204" t="n">
@@ -14416,7 +14758,11 @@
       </c>
       <c r="G205" s="2" t="n"/>
       <c r="H205" s="2" t="n"/>
-      <c r="I205" s="2" t="n"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J205" s="2" t="n"/>
       <c r="K205" s="2" t="n"/>
       <c r="L205" t="n">
@@ -14479,7 +14825,11 @@
       </c>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
-      <c r="I206" s="2" t="n"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J206" s="2" t="n"/>
       <c r="K206" s="2" t="n"/>
       <c r="L206" t="n">
@@ -14542,7 +14892,11 @@
       </c>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
-      <c r="I207" s="2" t="n"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J207" s="2" t="n"/>
       <c r="K207" s="2" t="n"/>
       <c r="L207" t="n">
@@ -14605,7 +14959,11 @@
       </c>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
-      <c r="I208" s="2" t="n"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J208" s="2" t="n"/>
       <c r="K208" s="2" t="n"/>
       <c r="L208" t="n">
@@ -14967,7 +15325,11 @@
       </c>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="n"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J214" s="2" t="n"/>
       <c r="K214" s="2" t="n"/>
       <c r="L214" t="n">
@@ -15030,7 +15392,11 @@
       </c>
       <c r="G215" s="2" t="n"/>
       <c r="H215" s="2" t="n"/>
-      <c r="I215" s="2" t="n"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J215" s="2" t="n"/>
       <c r="K215" s="2" t="n"/>
       <c r="L215" t="n">
@@ -15093,7 +15459,11 @@
       </c>
       <c r="G216" s="2" t="n"/>
       <c r="H216" s="2" t="n"/>
-      <c r="I216" s="2" t="n"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J216" s="2" t="n"/>
       <c r="K216" s="2" t="n"/>
       <c r="L216" t="n">
@@ -15156,7 +15526,11 @@
       </c>
       <c r="G217" s="2" t="n"/>
       <c r="H217" s="2" t="n"/>
-      <c r="I217" s="2" t="n"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="n"/>
       <c r="K217" s="2" t="n"/>
       <c r="L217" t="n">
@@ -15219,7 +15593,11 @@
       </c>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
-      <c r="I218" s="2" t="n"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J218" s="2" t="n"/>
       <c r="K218" s="2" t="n"/>
       <c r="L218" t="n">
@@ -15363,7 +15741,11 @@
       </c>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
-      <c r="I220" s="2" t="n"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J220" s="2" t="n"/>
       <c r="K220" s="2" t="n"/>
       <c r="L220" t="n">
@@ -15426,7 +15808,11 @@
       </c>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
-      <c r="I221" s="2" t="n"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J221" s="2" t="n"/>
       <c r="K221" s="2" t="n"/>
       <c r="L221" t="n">
@@ -15489,7 +15875,11 @@
       </c>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
-      <c r="I222" s="2" t="n"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J222" s="2" t="n"/>
       <c r="K222" s="2" t="n"/>
       <c r="L222" t="n">
@@ -15552,7 +15942,11 @@
       </c>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
-      <c r="I223" s="2" t="n"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J223" s="2" t="n"/>
       <c r="K223" s="2" t="n"/>
       <c r="L223" t="n">
@@ -16135,7 +16529,11 @@
       </c>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
-      <c r="I232" s="2" t="n"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J232" s="2" t="n"/>
       <c r="K232" s="2" t="n"/>
       <c r="L232" t="n">
@@ -16241,7 +16639,11 @@
       </c>
       <c r="G234" s="2" t="n"/>
       <c r="H234" s="2" t="n"/>
-      <c r="I234" s="2" t="n"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J234" s="2" t="n"/>
       <c r="K234" s="2" t="n"/>
       <c r="L234" t="n">
@@ -16307,7 +16709,11 @@
       </c>
       <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
-      <c r="I235" s="2" t="n"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J235" s="2" t="n"/>
       <c r="K235" s="2" t="n"/>
       <c r="L235" t="n">
@@ -16370,7 +16776,11 @@
       </c>
       <c r="G236" s="2" t="n"/>
       <c r="H236" s="2" t="n"/>
-      <c r="I236" s="2" t="n"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J236" s="2" t="n"/>
       <c r="K236" s="2" t="n"/>
       <c r="L236" t="n">
@@ -17067,7 +17477,11 @@
       </c>
       <c r="G246" s="2" t="n"/>
       <c r="H246" s="2" t="n"/>
-      <c r="I246" s="2" t="n"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J246" s="2" t="n"/>
       <c r="K246" s="2" t="n"/>
       <c r="L246" t="n">
@@ -17130,7 +17544,11 @@
       </c>
       <c r="G247" s="2" t="n"/>
       <c r="H247" s="2" t="n"/>
-      <c r="I247" s="2" t="n"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J247" s="2" t="n"/>
       <c r="K247" s="2" t="n"/>
       <c r="L247" t="n">
@@ -17193,7 +17611,11 @@
       </c>
       <c r="G248" s="2" t="n"/>
       <c r="H248" s="2" t="n"/>
-      <c r="I248" s="2" t="n"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J248" s="2" t="n"/>
       <c r="K248" s="2" t="n"/>
       <c r="L248" t="n">
@@ -17244,21 +17666,31 @@
           <t>ASF182</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F249" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="G249" s="2" t="n"/>
-      <c r="H249" s="2" t="n"/>
-      <c r="I249" s="2" t="n"/>
-      <c r="J249" s="2" t="n"/>
-      <c r="K249" s="2" t="n"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L249" t="n">
         <v>64.34999999999999</v>
       </c>
@@ -18069,7 +18501,11 @@
       </c>
       <c r="G260" s="2" t="n"/>
       <c r="H260" s="2" t="n"/>
-      <c r="I260" s="2" t="n"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J260" s="2" t="n"/>
       <c r="K260" s="2" t="n"/>
       <c r="L260" t="n">
@@ -18132,7 +18568,11 @@
       </c>
       <c r="G261" s="2" t="n"/>
       <c r="H261" s="2" t="n"/>
-      <c r="I261" s="2" t="n"/>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J261" s="2" t="n"/>
       <c r="K261" s="2" t="n"/>
       <c r="L261" t="n">
@@ -18357,7 +18797,11 @@
       </c>
       <c r="G264" s="2" t="n"/>
       <c r="H264" s="2" t="n"/>
-      <c r="I264" s="2" t="n"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J264" s="2" t="n"/>
       <c r="K264" s="2" t="n"/>
       <c r="L264" t="n">
@@ -18463,7 +18907,11 @@
       </c>
       <c r="G266" s="2" t="n"/>
       <c r="H266" s="2" t="n"/>
-      <c r="I266" s="2" t="n"/>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J266" s="2" t="n"/>
       <c r="K266" s="2" t="n"/>
       <c r="L266" t="n">
@@ -18511,7 +18959,11 @@
       </c>
       <c r="G267" s="2" t="n"/>
       <c r="H267" s="2" t="n"/>
-      <c r="I267" s="2" t="n"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J267" s="2" t="n"/>
       <c r="K267" s="2" t="n"/>
       <c r="L267" t="n">
@@ -18559,7 +19011,11 @@
       </c>
       <c r="G268" s="2" t="n"/>
       <c r="H268" s="2" t="n"/>
-      <c r="I268" s="2" t="n"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J268" s="2" t="n"/>
       <c r="K268" s="2" t="n"/>
       <c r="L268" t="n">
@@ -18871,7 +19327,11 @@
       </c>
       <c r="G273" s="2" t="n"/>
       <c r="H273" s="2" t="n"/>
-      <c r="I273" s="2" t="n"/>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J273" s="2" t="n"/>
       <c r="K273" s="2" t="n"/>
       <c r="L273" t="n">
@@ -18919,7 +19379,11 @@
       </c>
       <c r="G274" s="2" t="n"/>
       <c r="H274" s="2" t="n"/>
-      <c r="I274" s="2" t="n"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J274" s="2" t="n"/>
       <c r="K274" s="2" t="n"/>
       <c r="L274" t="n">
@@ -18967,7 +19431,11 @@
       </c>
       <c r="G275" s="2" t="n"/>
       <c r="H275" s="2" t="n"/>
-      <c r="I275" s="2" t="n"/>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J275" s="2" t="n"/>
       <c r="K275" s="2" t="n"/>
       <c r="L275" t="n">
@@ -19147,7 +19615,11 @@
       </c>
       <c r="G278" s="2" t="n"/>
       <c r="H278" s="2" t="n"/>
-      <c r="I278" s="2" t="n"/>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J278" s="2" t="n"/>
       <c r="K278" s="2" t="n"/>
       <c r="L278" t="n">
@@ -19210,7 +19682,11 @@
       </c>
       <c r="G279" s="2" t="n"/>
       <c r="H279" s="2" t="n"/>
-      <c r="I279" s="2" t="n"/>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J279" s="2" t="n"/>
       <c r="K279" s="2" t="n"/>
       <c r="L279" t="n">
@@ -19273,7 +19749,11 @@
       </c>
       <c r="G280" s="2" t="n"/>
       <c r="H280" s="2" t="n"/>
-      <c r="I280" s="2" t="n"/>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J280" s="2" t="n"/>
       <c r="K280" s="2" t="n"/>
       <c r="L280" t="n">
@@ -19405,21 +19885,31 @@
           <t>WSC330</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E282" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="G282" s="2" t="n"/>
-      <c r="H282" s="2" t="n"/>
-      <c r="I282" s="2" t="n"/>
-      <c r="J282" s="2" t="n"/>
-      <c r="K282" s="2" t="n"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L282" t="n">
         <v>68.31999999999999</v>
       </c>
@@ -20002,7 +20492,11 @@
       </c>
       <c r="G290" s="2" t="n"/>
       <c r="H290" s="2" t="n"/>
-      <c r="I290" s="2" t="n"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J290" s="2" t="n"/>
       <c r="K290" s="2" t="n"/>
       <c r="L290" t="n">
@@ -20146,7 +20640,11 @@
       </c>
       <c r="G292" s="2" t="n"/>
       <c r="H292" s="2" t="n"/>
-      <c r="I292" s="2" t="n"/>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J292" s="2" t="n"/>
       <c r="K292" s="2" t="n"/>
       <c r="L292" t="n">
@@ -20209,7 +20707,11 @@
       </c>
       <c r="G293" s="2" t="n"/>
       <c r="H293" s="2" t="n"/>
-      <c r="I293" s="2" t="n"/>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J293" s="2" t="n"/>
       <c r="K293" s="2" t="n"/>
       <c r="L293" t="n">
@@ -20272,7 +20774,11 @@
       </c>
       <c r="G294" s="2" t="n"/>
       <c r="H294" s="2" t="n"/>
-      <c r="I294" s="2" t="n"/>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J294" s="2" t="n"/>
       <c r="K294" s="2" t="n"/>
       <c r="L294" t="n">
@@ -20335,7 +20841,11 @@
       </c>
       <c r="G295" s="2" t="n"/>
       <c r="H295" s="2" t="n"/>
-      <c r="I295" s="2" t="n"/>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J295" s="2" t="n"/>
       <c r="K295" s="2" t="n"/>
       <c r="L295" t="n">
@@ -20530,7 +21040,11 @@
       </c>
       <c r="G298" s="2" t="n"/>
       <c r="H298" s="2" t="n"/>
-      <c r="I298" s="2" t="n"/>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J298" s="2" t="n"/>
       <c r="K298" s="2" t="n"/>
       <c r="L298" t="n">
@@ -20644,7 +21158,11 @@
       </c>
       <c r="G300" s="2" t="n"/>
       <c r="H300" s="2" t="n"/>
-      <c r="I300" s="2" t="n"/>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J300" s="2" t="n"/>
       <c r="K300" s="2" t="n"/>
       <c r="L300" t="n">
@@ -20695,21 +21213,31 @@
           <t>ASF182</t>
         </is>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E301" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="F301" s="2" t="inlineStr">
+      <c r="F301" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="G301" s="2" t="n"/>
-      <c r="H301" s="2" t="n"/>
-      <c r="I301" s="2" t="n"/>
-      <c r="J301" s="2" t="n"/>
-      <c r="K301" s="2" t="n"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L301" t="n">
         <v>64.34999999999999</v>
       </c>
@@ -20908,21 +21436,31 @@
           <t>WSC330</t>
         </is>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="E304" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="F304" s="2" t="inlineStr">
+      <c r="F304" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="G304" s="2" t="n"/>
-      <c r="H304" s="2" t="n"/>
-      <c r="I304" s="2" t="n"/>
-      <c r="J304" s="2" t="n"/>
-      <c r="K304" s="2" t="n"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L304" t="n">
         <v>68.31999999999999</v>
       </c>
@@ -21226,7 +21764,11 @@
       </c>
       <c r="G308" s="2" t="n"/>
       <c r="H308" s="2" t="n"/>
-      <c r="I308" s="2" t="n"/>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J308" s="2" t="n"/>
       <c r="K308" s="2" t="n"/>
       <c r="L308" t="n">
@@ -21289,7 +21831,11 @@
       </c>
       <c r="G309" s="2" t="n"/>
       <c r="H309" s="2" t="n"/>
-      <c r="I309" s="2" t="n"/>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J309" s="2" t="n"/>
       <c r="K309" s="2" t="n"/>
       <c r="L309" t="n">
@@ -21352,7 +21898,11 @@
       </c>
       <c r="G310" s="2" t="n"/>
       <c r="H310" s="2" t="n"/>
-      <c r="I310" s="2" t="n"/>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J310" s="2" t="n"/>
       <c r="K310" s="2" t="n"/>
       <c r="L310" t="n">
@@ -21574,7 +22124,11 @@
       </c>
       <c r="G313" s="2" t="n"/>
       <c r="H313" s="2" t="n"/>
-      <c r="I313" s="2" t="n"/>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J313" s="2" t="n"/>
       <c r="K313" s="2" t="n"/>
       <c r="L313" t="n">
@@ -21637,7 +22191,11 @@
       </c>
       <c r="G314" s="2" t="n"/>
       <c r="H314" s="2" t="n"/>
-      <c r="I314" s="2" t="n"/>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J314" s="2" t="n"/>
       <c r="K314" s="2" t="n"/>
       <c r="L314" t="n">
@@ -21700,7 +22258,11 @@
       </c>
       <c r="G315" s="2" t="n"/>
       <c r="H315" s="2" t="n"/>
-      <c r="I315" s="2" t="n"/>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J315" s="2" t="n"/>
       <c r="K315" s="2" t="n"/>
       <c r="L315" t="n">
@@ -21763,7 +22325,11 @@
       </c>
       <c r="G316" s="2" t="n"/>
       <c r="H316" s="2" t="n"/>
-      <c r="I316" s="2" t="n"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J316" s="2" t="n"/>
       <c r="K316" s="2" t="n"/>
       <c r="L316" t="n">
@@ -21826,7 +22392,11 @@
       </c>
       <c r="G317" s="2" t="n"/>
       <c r="H317" s="2" t="n"/>
-      <c r="I317" s="2" t="n"/>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J317" s="2" t="n"/>
       <c r="K317" s="2" t="n"/>
       <c r="L317" t="n">
@@ -22219,7 +22789,11 @@
       </c>
       <c r="G323" s="2" t="n"/>
       <c r="H323" s="2" t="n"/>
-      <c r="I323" s="2" t="n"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J323" s="2" t="n"/>
       <c r="K323" s="2" t="n"/>
       <c r="L323" t="n">
@@ -22285,7 +22859,11 @@
       </c>
       <c r="G324" s="2" t="n"/>
       <c r="H324" s="2" t="n"/>
-      <c r="I324" s="2" t="n"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J324" s="2" t="n"/>
       <c r="K324" s="2" t="n"/>
       <c r="L324" t="n">
@@ -22351,7 +22929,11 @@
       </c>
       <c r="G325" s="2" t="n"/>
       <c r="H325" s="2" t="n"/>
-      <c r="I325" s="2" t="n"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J325" s="2" t="n"/>
       <c r="K325" s="2" t="n"/>
       <c r="L325" t="n">
@@ -22414,7 +22996,11 @@
       </c>
       <c r="G326" s="2" t="n"/>
       <c r="H326" s="2" t="n"/>
-      <c r="I326" s="2" t="n"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J326" s="2" t="n"/>
       <c r="K326" s="2" t="n"/>
       <c r="L326" t="n">
@@ -22477,7 +23063,11 @@
       </c>
       <c r="G327" s="2" t="n"/>
       <c r="H327" s="2" t="n"/>
-      <c r="I327" s="2" t="n"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J327" s="2" t="n"/>
       <c r="K327" s="2" t="n"/>
       <c r="L327" t="n">
@@ -22540,7 +23130,11 @@
       </c>
       <c r="G328" s="2" t="n"/>
       <c r="H328" s="2" t="n"/>
-      <c r="I328" s="2" t="n"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J328" s="2" t="n"/>
       <c r="K328" s="2" t="n"/>
       <c r="L328" t="n">
@@ -22603,7 +23197,11 @@
       </c>
       <c r="G329" s="2" t="n"/>
       <c r="H329" s="2" t="n"/>
-      <c r="I329" s="2" t="n"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J329" s="2" t="n"/>
       <c r="K329" s="2" t="n"/>
       <c r="L329" t="n">
@@ -22666,7 +23264,11 @@
       </c>
       <c r="G330" s="2" t="n"/>
       <c r="H330" s="2" t="n"/>
-      <c r="I330" s="2" t="n"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J330" s="2" t="n"/>
       <c r="K330" s="2" t="n"/>
       <c r="L330" t="n">
@@ -23365,21 +23967,39 @@
           <t>SAF126</t>
         </is>
       </c>
-      <c r="E340" s="2" t="inlineStr">
+      <c r="E340" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="F340" s="2" t="inlineStr">
+      <c r="F340" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="G340" s="2" t="n"/>
-      <c r="H340" s="2" t="n"/>
-      <c r="I340" s="2" t="n"/>
-      <c r="J340" s="2" t="n"/>
-      <c r="K340" s="2" t="n"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="L340" t="n">
         <v>135.3</v>
       </c>
@@ -23443,7 +24063,11 @@
       </c>
       <c r="G341" s="2" t="n"/>
       <c r="H341" s="2" t="n"/>
-      <c r="I341" s="2" t="n"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J341" s="2" t="n"/>
       <c r="K341" s="2" t="n"/>
       <c r="L341" t="n">
@@ -23668,7 +24292,11 @@
       </c>
       <c r="G344" s="2" t="n"/>
       <c r="H344" s="2" t="n"/>
-      <c r="I344" s="2" t="n"/>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J344" s="2" t="n"/>
       <c r="K344" s="2" t="n"/>
       <c r="L344" t="n">
@@ -23716,7 +24344,11 @@
       </c>
       <c r="G345" s="2" t="n"/>
       <c r="H345" s="2" t="n"/>
-      <c r="I345" s="2" t="n"/>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J345" s="2" t="n"/>
       <c r="K345" s="2" t="n"/>
       <c r="L345" t="n">
@@ -23764,7 +24396,11 @@
       </c>
       <c r="G346" s="2" t="n"/>
       <c r="H346" s="2" t="n"/>
-      <c r="I346" s="2" t="n"/>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J346" s="2" t="n"/>
       <c r="K346" s="2" t="n"/>
       <c r="L346" t="n">
@@ -23944,7 +24580,11 @@
       </c>
       <c r="G349" s="2" t="n"/>
       <c r="H349" s="2" t="n"/>
-      <c r="I349" s="2" t="n"/>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J349" s="2" t="n"/>
       <c r="K349" s="2" t="n"/>
       <c r="L349" t="n">
@@ -23992,7 +24632,11 @@
       </c>
       <c r="G350" s="2" t="n"/>
       <c r="H350" s="2" t="n"/>
-      <c r="I350" s="2" t="n"/>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J350" s="2" t="n"/>
       <c r="K350" s="2" t="n"/>
       <c r="L350" t="n">
@@ -24040,7 +24684,11 @@
       </c>
       <c r="G351" s="2" t="n"/>
       <c r="H351" s="2" t="n"/>
-      <c r="I351" s="2" t="n"/>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J351" s="2" t="n"/>
       <c r="K351" s="2" t="n"/>
       <c r="L351" t="n">
@@ -24484,7 +25132,11 @@
       </c>
       <c r="G358" s="2" t="n"/>
       <c r="H358" s="2" t="n"/>
-      <c r="I358" s="2" t="n"/>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J358" s="2" t="n"/>
       <c r="K358" s="2" t="n"/>
       <c r="L358" t="n">
@@ -24628,7 +25280,11 @@
       </c>
       <c r="G360" s="2" t="n"/>
       <c r="H360" s="2" t="n"/>
-      <c r="I360" s="2" t="n"/>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J360" s="2" t="n"/>
       <c r="K360" s="2" t="n"/>
       <c r="L360" t="n">
@@ -24691,7 +25347,11 @@
       </c>
       <c r="G361" s="2" t="n"/>
       <c r="H361" s="2" t="n"/>
-      <c r="I361" s="2" t="n"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J361" s="2" t="n"/>
       <c r="K361" s="2" t="n"/>
       <c r="L361" t="n">
@@ -24754,7 +25414,11 @@
       </c>
       <c r="G362" s="2" t="n"/>
       <c r="H362" s="2" t="n"/>
-      <c r="I362" s="2" t="n"/>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J362" s="2" t="n"/>
       <c r="K362" s="2" t="n"/>
       <c r="L362" t="n">
@@ -25060,7 +25724,11 @@
       </c>
       <c r="G366" s="2" t="n"/>
       <c r="H366" s="2" t="n"/>
-      <c r="I366" s="2" t="n"/>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J366" s="2" t="n"/>
       <c r="K366" s="2" t="n"/>
       <c r="L366" t="n">
@@ -25123,7 +25791,11 @@
       </c>
       <c r="G367" s="2" t="n"/>
       <c r="H367" s="2" t="n"/>
-      <c r="I367" s="2" t="n"/>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J367" s="2" t="n"/>
       <c r="K367" s="2" t="n"/>
       <c r="L367" t="n">
@@ -25186,7 +25858,11 @@
       </c>
       <c r="G368" s="2" t="n"/>
       <c r="H368" s="2" t="n"/>
-      <c r="I368" s="2" t="n"/>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J368" s="2" t="n"/>
       <c r="K368" s="2" t="n"/>
       <c r="L368" t="n">
@@ -25687,7 +26363,11 @@
       </c>
       <c r="G375" s="2" t="n"/>
       <c r="H375" s="2" t="n"/>
-      <c r="I375" s="2" t="n"/>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J375" s="2" t="n"/>
       <c r="K375" s="2" t="n"/>
       <c r="L375" t="n">
@@ -26212,7 +26892,11 @@
       </c>
       <c r="G383" s="2" t="n"/>
       <c r="H383" s="2" t="n"/>
-      <c r="I383" s="2" t="n"/>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J383" s="2" t="n"/>
       <c r="K383" s="2" t="n"/>
       <c r="L383" t="n">
@@ -26356,7 +27040,11 @@
       </c>
       <c r="G385" s="2" t="n"/>
       <c r="H385" s="2" t="n"/>
-      <c r="I385" s="2" t="n"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J385" s="2" t="n"/>
       <c r="K385" s="2" t="n"/>
       <c r="L385" t="n">
@@ -26419,7 +27107,11 @@
       </c>
       <c r="G386" s="2" t="n"/>
       <c r="H386" s="2" t="n"/>
-      <c r="I386" s="2" t="n"/>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J386" s="2" t="n"/>
       <c r="K386" s="2" t="n"/>
       <c r="L386" t="n">
@@ -26470,21 +27162,31 @@
           <t>WSC330</t>
         </is>
       </c>
-      <c r="E387" s="2" t="inlineStr">
+      <c r="E387" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="F387" s="2" t="inlineStr">
+      <c r="F387" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="G387" s="2" t="n"/>
-      <c r="H387" s="2" t="n"/>
-      <c r="I387" s="2" t="n"/>
-      <c r="J387" s="2" t="n"/>
-      <c r="K387" s="2" t="n"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L387" t="n">
         <v>68.31999999999999</v>
       </c>
@@ -26707,7 +27409,11 @@
       </c>
       <c r="G390" s="2" t="n"/>
       <c r="H390" s="2" t="n"/>
-      <c r="I390" s="2" t="n"/>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J390" s="2" t="n"/>
       <c r="K390" s="2" t="n"/>
       <c r="L390" t="n">
@@ -26755,7 +27461,11 @@
       </c>
       <c r="G391" s="2" t="n"/>
       <c r="H391" s="2" t="n"/>
-      <c r="I391" s="2" t="n"/>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J391" s="2" t="n"/>
       <c r="K391" s="2" t="n"/>
       <c r="L391" t="n">
@@ -26803,7 +27513,11 @@
       </c>
       <c r="G392" s="2" t="n"/>
       <c r="H392" s="2" t="n"/>
-      <c r="I392" s="2" t="n"/>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J392" s="2" t="n"/>
       <c r="K392" s="2" t="n"/>
       <c r="L392" t="n">
@@ -26851,7 +27565,11 @@
       </c>
       <c r="G393" s="2" t="n"/>
       <c r="H393" s="2" t="n"/>
-      <c r="I393" s="2" t="n"/>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J393" s="2" t="n"/>
       <c r="K393" s="2" t="n"/>
       <c r="L393" t="n">
@@ -26899,7 +27617,11 @@
       </c>
       <c r="G394" s="2" t="n"/>
       <c r="H394" s="2" t="n"/>
-      <c r="I394" s="2" t="n"/>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J394" s="2" t="n"/>
       <c r="K394" s="2" t="n"/>
       <c r="L394" t="n">
@@ -27079,7 +27801,11 @@
       </c>
       <c r="G397" s="2" t="n"/>
       <c r="H397" s="2" t="n"/>
-      <c r="I397" s="2" t="n"/>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J397" s="2" t="n"/>
       <c r="K397" s="2" t="n"/>
       <c r="L397" t="n">
@@ -27127,7 +27853,11 @@
       </c>
       <c r="G398" s="2" t="n"/>
       <c r="H398" s="2" t="n"/>
-      <c r="I398" s="2" t="n"/>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J398" s="2" t="n"/>
       <c r="K398" s="2" t="n"/>
       <c r="L398" t="n">
@@ -27175,7 +27905,11 @@
       </c>
       <c r="G399" s="2" t="n"/>
       <c r="H399" s="2" t="n"/>
-      <c r="I399" s="2" t="n"/>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J399" s="2" t="n"/>
       <c r="K399" s="2" t="n"/>
       <c r="L399" t="n">
@@ -27370,7 +28104,11 @@
       </c>
       <c r="G402" s="2" t="n"/>
       <c r="H402" s="2" t="n"/>
-      <c r="I402" s="2" t="n"/>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J402" s="2" t="n"/>
       <c r="K402" s="2" t="n"/>
       <c r="L402" t="n">
@@ -27433,7 +28171,11 @@
       </c>
       <c r="G403" s="2" t="n"/>
       <c r="H403" s="2" t="n"/>
-      <c r="I403" s="2" t="n"/>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J403" s="2" t="n"/>
       <c r="K403" s="2" t="n"/>
       <c r="L403" t="n">
@@ -27496,7 +28238,11 @@
       </c>
       <c r="G404" s="2" t="n"/>
       <c r="H404" s="2" t="n"/>
-      <c r="I404" s="2" t="n"/>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J404" s="2" t="n"/>
       <c r="K404" s="2" t="n"/>
       <c r="L404" t="n">
@@ -27559,7 +28305,11 @@
       </c>
       <c r="G405" s="2" t="n"/>
       <c r="H405" s="2" t="n"/>
-      <c r="I405" s="2" t="n"/>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J405" s="2" t="n"/>
       <c r="K405" s="2" t="n"/>
       <c r="L405" t="n">
@@ -27754,7 +28504,11 @@
       </c>
       <c r="G408" s="2" t="n"/>
       <c r="H408" s="2" t="n"/>
-      <c r="I408" s="2" t="n"/>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J408" s="2" t="n"/>
       <c r="K408" s="2" t="n"/>
       <c r="L408" t="n">
@@ -27817,7 +28571,11 @@
       </c>
       <c r="G409" s="2" t="n"/>
       <c r="H409" s="2" t="n"/>
-      <c r="I409" s="2" t="n"/>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J409" s="2" t="n"/>
       <c r="K409" s="2" t="n"/>
       <c r="L409" t="n">
@@ -27880,7 +28638,11 @@
       </c>
       <c r="G410" s="2" t="n"/>
       <c r="H410" s="2" t="n"/>
-      <c r="I410" s="2" t="n"/>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J410" s="2" t="n"/>
       <c r="K410" s="2" t="n"/>
       <c r="L410" t="n">
@@ -27943,7 +28705,11 @@
       </c>
       <c r="G411" s="2" t="n"/>
       <c r="H411" s="2" t="n"/>
-      <c r="I411" s="2" t="n"/>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J411" s="2" t="n"/>
       <c r="K411" s="2" t="n"/>
       <c r="L411" t="n">
@@ -28006,7 +28772,11 @@
       </c>
       <c r="G412" s="2" t="n"/>
       <c r="H412" s="2" t="n"/>
-      <c r="I412" s="2" t="n"/>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J412" s="2" t="n"/>
       <c r="K412" s="2" t="n"/>
       <c r="L412" t="n">
@@ -28465,7 +29235,11 @@
       </c>
       <c r="G419" s="2" t="n"/>
       <c r="H419" s="2" t="n"/>
-      <c r="I419" s="2" t="n"/>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J419" s="2" t="n"/>
       <c r="K419" s="2" t="n"/>
       <c r="L419" t="n">
@@ -28528,7 +29302,11 @@
       </c>
       <c r="G420" s="2" t="n"/>
       <c r="H420" s="2" t="n"/>
-      <c r="I420" s="2" t="n"/>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J420" s="2" t="n"/>
       <c r="K420" s="2" t="n"/>
       <c r="L420" t="n">
@@ -28591,7 +29369,11 @@
       </c>
       <c r="G421" s="2" t="n"/>
       <c r="H421" s="2" t="n"/>
-      <c r="I421" s="2" t="n"/>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J421" s="2" t="n"/>
       <c r="K421" s="2" t="n"/>
       <c r="L421" t="n">
@@ -28654,7 +29436,11 @@
       </c>
       <c r="G422" s="2" t="n"/>
       <c r="H422" s="2" t="n"/>
-      <c r="I422" s="2" t="n"/>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J422" s="2" t="n"/>
       <c r="K422" s="2" t="n"/>
       <c r="L422" t="n">
@@ -28717,7 +29503,11 @@
       </c>
       <c r="G423" s="2" t="n"/>
       <c r="H423" s="2" t="n"/>
-      <c r="I423" s="2" t="n"/>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J423" s="2" t="n"/>
       <c r="K423" s="2" t="n"/>
       <c r="L423" t="n">
@@ -28780,7 +29570,11 @@
       </c>
       <c r="G424" s="2" t="n"/>
       <c r="H424" s="2" t="n"/>
-      <c r="I424" s="2" t="n"/>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J424" s="2" t="n"/>
       <c r="K424" s="2" t="n"/>
       <c r="L424" t="n">
@@ -29254,7 +30048,11 @@
       </c>
       <c r="G431" s="2" t="n"/>
       <c r="H431" s="2" t="n"/>
-      <c r="I431" s="2" t="n"/>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J431" s="2" t="n"/>
       <c r="K431" s="2" t="n"/>
       <c r="L431" t="n">
@@ -29317,7 +30115,11 @@
       </c>
       <c r="G432" s="2" t="n"/>
       <c r="H432" s="2" t="n"/>
-      <c r="I432" s="2" t="n"/>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J432" s="2" t="n"/>
       <c r="K432" s="2" t="n"/>
       <c r="L432" t="n">
@@ -29380,7 +30182,11 @@
       </c>
       <c r="G433" s="2" t="n"/>
       <c r="H433" s="2" t="n"/>
-      <c r="I433" s="2" t="n"/>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J433" s="2" t="n"/>
       <c r="K433" s="2" t="n"/>
       <c r="L433" t="n">
@@ -29443,7 +30249,11 @@
       </c>
       <c r="G434" s="2" t="n"/>
       <c r="H434" s="2" t="n"/>
-      <c r="I434" s="2" t="n"/>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J434" s="2" t="n"/>
       <c r="K434" s="2" t="n"/>
       <c r="L434" t="n">
@@ -29506,7 +30316,11 @@
       </c>
       <c r="G435" s="2" t="n"/>
       <c r="H435" s="2" t="n"/>
-      <c r="I435" s="2" t="n"/>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J435" s="2" t="n"/>
       <c r="K435" s="2" t="n"/>
       <c r="L435" t="n">
@@ -29569,7 +30383,11 @@
       </c>
       <c r="G436" s="2" t="n"/>
       <c r="H436" s="2" t="n"/>
-      <c r="I436" s="2" t="n"/>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J436" s="2" t="n"/>
       <c r="K436" s="2" t="n"/>
       <c r="L436" t="n">
@@ -29845,7 +30663,11 @@
       </c>
       <c r="G440" s="2" t="n"/>
       <c r="H440" s="2" t="n"/>
-      <c r="I440" s="2" t="n"/>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J440" s="2" t="n"/>
       <c r="K440" s="2" t="n"/>
       <c r="L440" t="n">
@@ -29908,7 +30730,11 @@
       </c>
       <c r="G441" s="2" t="n"/>
       <c r="H441" s="2" t="n"/>
-      <c r="I441" s="2" t="n"/>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J441" s="2" t="n"/>
       <c r="K441" s="2" t="n"/>
       <c r="L441" t="n">
@@ -29959,21 +30785,31 @@
           <t>ASF182</t>
         </is>
       </c>
-      <c r="E442" s="2" t="inlineStr">
+      <c r="E442" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="F442" s="2" t="inlineStr">
+      <c r="F442" t="inlineStr">
         <is>
           <t>ASF182MM</t>
         </is>
       </c>
-      <c r="G442" s="2" t="n"/>
-      <c r="H442" s="2" t="n"/>
-      <c r="I442" s="2" t="n"/>
-      <c r="J442" s="2" t="n"/>
-      <c r="K442" s="2" t="n"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>SANDALIA</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L442" t="n">
         <v>64.34999999999999</v>
       </c>
@@ -30577,7 +31413,11 @@
       </c>
       <c r="G451" s="2" t="n"/>
       <c r="H451" s="2" t="n"/>
-      <c r="I451" s="2" t="n"/>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J451" s="2" t="n"/>
       <c r="K451" s="2" t="n"/>
       <c r="L451" t="n">
@@ -30709,21 +31549,31 @@
           <t>WSC330</t>
         </is>
       </c>
-      <c r="E453" s="2" t="inlineStr">
+      <c r="E453" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="F453" s="2" t="inlineStr">
+      <c r="F453" t="inlineStr">
         <is>
           <t>WSC330OU</t>
         </is>
       </c>
-      <c r="G453" s="2" t="n"/>
-      <c r="H453" s="2" t="n"/>
-      <c r="I453" s="2" t="n"/>
-      <c r="J453" s="2" t="n"/>
-      <c r="K453" s="2" t="n"/>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>FEMININO</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="L453" t="n">
         <v>68.31999999999999</v>
       </c>
@@ -31261,21 +32111,39 @@
           <t>SAF126</t>
         </is>
       </c>
-      <c r="E460" s="2" t="inlineStr">
+      <c r="E460" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="F460" s="2" t="inlineStr">
+      <c r="F460" t="inlineStr">
         <is>
           <t>SAF126BK</t>
         </is>
       </c>
-      <c r="G460" s="2" t="n"/>
-      <c r="H460" s="2" t="n"/>
-      <c r="I460" s="2" t="n"/>
-      <c r="J460" s="2" t="n"/>
-      <c r="K460" s="2" t="n"/>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>MASCULINO</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>TENIS</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
+      <c r="J460" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="L460" t="n">
         <v>135.3</v>
       </c>
@@ -31750,7 +32618,11 @@
       </c>
       <c r="G466" s="2" t="n"/>
       <c r="H466" s="2" t="n"/>
-      <c r="I466" s="2" t="n"/>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J466" s="2" t="n"/>
       <c r="K466" s="2" t="n"/>
       <c r="L466" t="n">
@@ -31894,7 +32766,11 @@
       </c>
       <c r="G468" s="2" t="n"/>
       <c r="H468" s="2" t="n"/>
-      <c r="I468" s="2" t="n"/>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J468" s="2" t="n"/>
       <c r="K468" s="2" t="n"/>
       <c r="L468" t="n">
@@ -32170,7 +33046,11 @@
       </c>
       <c r="G472" s="2" t="n"/>
       <c r="H472" s="2" t="n"/>
-      <c r="I472" s="2" t="n"/>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J472" s="2" t="n"/>
       <c r="K472" s="2" t="n"/>
       <c r="L472" t="n">
@@ -32233,7 +33113,11 @@
       </c>
       <c r="G473" s="2" t="n"/>
       <c r="H473" s="2" t="n"/>
-      <c r="I473" s="2" t="n"/>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J473" s="2" t="n"/>
       <c r="K473" s="2" t="n"/>
       <c r="L473" t="n">
@@ -32296,7 +33180,11 @@
       </c>
       <c r="G474" s="2" t="n"/>
       <c r="H474" s="2" t="n"/>
-      <c r="I474" s="2" t="n"/>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J474" s="2" t="n"/>
       <c r="K474" s="2" t="n"/>
       <c r="L474" t="n">
@@ -32680,7 +33568,11 @@
       </c>
       <c r="G479" s="2" t="n"/>
       <c r="H479" s="2" t="n"/>
-      <c r="I479" s="2" t="n"/>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J479" s="2" t="n"/>
       <c r="K479" s="2" t="n"/>
       <c r="L479" t="n">
@@ -32743,7 +33635,11 @@
       </c>
       <c r="G480" s="2" t="n"/>
       <c r="H480" s="2" t="n"/>
-      <c r="I480" s="2" t="n"/>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J480" s="2" t="n"/>
       <c r="K480" s="2" t="n"/>
       <c r="L480" t="n">
@@ -32806,7 +33702,11 @@
       </c>
       <c r="G481" s="2" t="n"/>
       <c r="H481" s="2" t="n"/>
-      <c r="I481" s="2" t="n"/>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J481" s="2" t="n"/>
       <c r="K481" s="2" t="n"/>
       <c r="L481" t="n">
@@ -33634,7 +34534,11 @@
       </c>
       <c r="G493" s="2" t="n"/>
       <c r="H493" s="2" t="n"/>
-      <c r="I493" s="2" t="n"/>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J493" s="2" t="n"/>
       <c r="K493" s="2" t="n"/>
       <c r="L493" t="n">
@@ -33682,7 +34586,11 @@
       </c>
       <c r="G494" s="2" t="n"/>
       <c r="H494" s="2" t="n"/>
-      <c r="I494" s="2" t="n"/>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J494" s="2" t="n"/>
       <c r="K494" s="2" t="n"/>
       <c r="L494" t="n">
@@ -33730,7 +34638,11 @@
       </c>
       <c r="G495" s="2" t="n"/>
       <c r="H495" s="2" t="n"/>
-      <c r="I495" s="2" t="n"/>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J495" s="2" t="n"/>
       <c r="K495" s="2" t="n"/>
       <c r="L495" t="n">
@@ -33778,7 +34690,11 @@
       </c>
       <c r="G496" s="2" t="n"/>
       <c r="H496" s="2" t="n"/>
-      <c r="I496" s="2" t="n"/>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J496" s="2" t="n"/>
       <c r="K496" s="2" t="n"/>
       <c r="L496" t="n">
@@ -33826,7 +34742,11 @@
       </c>
       <c r="G497" s="2" t="n"/>
       <c r="H497" s="2" t="n"/>
-      <c r="I497" s="2" t="n"/>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J497" s="2" t="n"/>
       <c r="K497" s="2" t="n"/>
       <c r="L497" t="n">
@@ -34006,7 +34926,11 @@
       </c>
       <c r="G500" s="2" t="n"/>
       <c r="H500" s="2" t="n"/>
-      <c r="I500" s="2" t="n"/>
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J500" s="2" t="n"/>
       <c r="K500" s="2" t="n"/>
       <c r="L500" t="n">
@@ -34054,7 +34978,11 @@
       </c>
       <c r="G501" s="2" t="n"/>
       <c r="H501" s="2" t="n"/>
-      <c r="I501" s="2" t="n"/>
+      <c r="I501" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J501" s="2" t="n"/>
       <c r="K501" s="2" t="n"/>
       <c r="L501" t="n">
@@ -34102,7 +35030,11 @@
       </c>
       <c r="G502" s="2" t="n"/>
       <c r="H502" s="2" t="n"/>
-      <c r="I502" s="2" t="n"/>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J502" s="2" t="n"/>
       <c r="K502" s="2" t="n"/>
       <c r="L502" t="n">
@@ -35383,7 +36315,11 @@
       </c>
       <c r="G521" s="2" t="n"/>
       <c r="H521" s="2" t="n"/>
-      <c r="I521" s="2" t="n"/>
+      <c r="I521" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J521" s="2" t="n"/>
       <c r="K521" s="2" t="n"/>
       <c r="L521" t="n">
@@ -35446,7 +36382,11 @@
       </c>
       <c r="G522" s="2" t="n"/>
       <c r="H522" s="2" t="n"/>
-      <c r="I522" s="2" t="n"/>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J522" s="2" t="n"/>
       <c r="K522" s="2" t="n"/>
       <c r="L522" t="n">
@@ -35509,7 +36449,11 @@
       </c>
       <c r="G523" s="2" t="n"/>
       <c r="H523" s="2" t="n"/>
-      <c r="I523" s="2" t="n"/>
+      <c r="I523" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J523" s="2" t="n"/>
       <c r="K523" s="2" t="n"/>
       <c r="L523" t="n">
@@ -35836,7 +36780,11 @@
       </c>
       <c r="G528" s="2" t="n"/>
       <c r="H528" s="2" t="n"/>
-      <c r="I528" s="2" t="n"/>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J528" s="2" t="n"/>
       <c r="K528" s="2" t="n"/>
       <c r="L528" t="n">
@@ -35899,7 +36847,11 @@
       </c>
       <c r="G529" s="2" t="n"/>
       <c r="H529" s="2" t="n"/>
-      <c r="I529" s="2" t="n"/>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J529" s="2" t="n"/>
       <c r="K529" s="2" t="n"/>
       <c r="L529" t="n">
@@ -35962,7 +36914,11 @@
       </c>
       <c r="G530" s="2" t="n"/>
       <c r="H530" s="2" t="n"/>
-      <c r="I530" s="2" t="n"/>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J530" s="2" t="n"/>
       <c r="K530" s="2" t="n"/>
       <c r="L530" t="n">
@@ -36025,7 +36981,11 @@
       </c>
       <c r="G531" s="2" t="n"/>
       <c r="H531" s="2" t="n"/>
-      <c r="I531" s="2" t="n"/>
+      <c r="I531" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J531" s="2" t="n"/>
       <c r="K531" s="2" t="n"/>
       <c r="L531" t="n">
@@ -36568,7 +37528,11 @@
       </c>
       <c r="G538" s="2" t="n"/>
       <c r="H538" s="2" t="n"/>
-      <c r="I538" s="2" t="n"/>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J538" s="2" t="n"/>
       <c r="K538" s="2" t="n"/>
       <c r="L538" t="n">
@@ -36631,7 +37595,11 @@
       </c>
       <c r="G539" s="2" t="n"/>
       <c r="H539" s="2" t="n"/>
-      <c r="I539" s="2" t="n"/>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J539" s="2" t="n"/>
       <c r="K539" s="2" t="n"/>
       <c r="L539" t="n">
@@ -36694,7 +37662,11 @@
       </c>
       <c r="G540" s="2" t="n"/>
       <c r="H540" s="2" t="n"/>
-      <c r="I540" s="2" t="n"/>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J540" s="2" t="n"/>
       <c r="K540" s="2" t="n"/>
       <c r="L540" t="n">
@@ -37087,7 +38059,11 @@
       </c>
       <c r="G546" s="2" t="n"/>
       <c r="H546" s="2" t="n"/>
-      <c r="I546" s="2" t="n"/>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J546" s="2" t="n"/>
       <c r="K546" s="2" t="n"/>
       <c r="L546" t="n">
@@ -37231,7 +38207,11 @@
       </c>
       <c r="G548" s="2" t="n"/>
       <c r="H548" s="2" t="n"/>
-      <c r="I548" s="2" t="n"/>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J548" s="2" t="n"/>
       <c r="K548" s="2" t="n"/>
       <c r="L548" t="n">
@@ -37294,7 +38274,11 @@
       </c>
       <c r="G549" s="2" t="n"/>
       <c r="H549" s="2" t="n"/>
-      <c r="I549" s="2" t="n"/>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J549" s="2" t="n"/>
       <c r="K549" s="2" t="n"/>
       <c r="L549" t="n">
@@ -37357,7 +38341,11 @@
       </c>
       <c r="G550" s="2" t="n"/>
       <c r="H550" s="2" t="n"/>
-      <c r="I550" s="2" t="n"/>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J550" s="2" t="n"/>
       <c r="K550" s="2" t="n"/>
       <c r="L550" t="n">
@@ -37498,7 +38486,11 @@
       </c>
       <c r="G552" s="2" t="n"/>
       <c r="H552" s="2" t="n"/>
-      <c r="I552" s="2" t="n"/>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J552" s="2" t="n"/>
       <c r="K552" s="2" t="n"/>
       <c r="L552" t="n">
@@ -37564,7 +38556,11 @@
       </c>
       <c r="G553" s="2" t="n"/>
       <c r="H553" s="2" t="n"/>
-      <c r="I553" s="2" t="n"/>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J553" s="2" t="n"/>
       <c r="K553" s="2" t="n"/>
       <c r="L553" t="n">
@@ -37630,7 +38626,11 @@
       </c>
       <c r="G554" s="2" t="n"/>
       <c r="H554" s="2" t="n"/>
-      <c r="I554" s="2" t="n"/>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J554" s="2" t="n"/>
       <c r="K554" s="2" t="n"/>
       <c r="L554" t="n">
@@ -37696,7 +38696,11 @@
       </c>
       <c r="G555" s="2" t="n"/>
       <c r="H555" s="2" t="n"/>
-      <c r="I555" s="2" t="n"/>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J555" s="2" t="n"/>
       <c r="K555" s="2" t="n"/>
       <c r="L555" t="n">
@@ -37762,7 +38766,11 @@
       </c>
       <c r="G556" s="2" t="n"/>
       <c r="H556" s="2" t="n"/>
-      <c r="I556" s="2" t="n"/>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J556" s="2" t="n"/>
       <c r="K556" s="2" t="n"/>
       <c r="L556" t="n">
@@ -37828,7 +38836,11 @@
       </c>
       <c r="G557" s="2" t="n"/>
       <c r="H557" s="2" t="n"/>
-      <c r="I557" s="2" t="n"/>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J557" s="2" t="n"/>
       <c r="K557" s="2" t="n"/>
       <c r="L557" t="n">
@@ -37894,7 +38906,11 @@
       </c>
       <c r="G558" s="2" t="n"/>
       <c r="H558" s="2" t="n"/>
-      <c r="I558" s="2" t="n"/>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J558" s="2" t="n"/>
       <c r="K558" s="2" t="n"/>
       <c r="L558" t="n">
@@ -38038,7 +39054,11 @@
       </c>
       <c r="G560" s="2" t="n"/>
       <c r="H560" s="2" t="n"/>
-      <c r="I560" s="2" t="n"/>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J560" s="2" t="n"/>
       <c r="K560" s="2" t="n"/>
       <c r="L560" t="n">
@@ -38101,7 +39121,11 @@
       </c>
       <c r="G561" s="2" t="n"/>
       <c r="H561" s="2" t="n"/>
-      <c r="I561" s="2" t="n"/>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J561" s="2" t="n"/>
       <c r="K561" s="2" t="n"/>
       <c r="L561" t="n">
@@ -38164,7 +39188,11 @@
       </c>
       <c r="G562" s="2" t="n"/>
       <c r="H562" s="2" t="n"/>
-      <c r="I562" s="2" t="n"/>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J562" s="2" t="n"/>
       <c r="K562" s="2" t="n"/>
       <c r="L562" t="n">
@@ -38227,7 +39255,11 @@
       </c>
       <c r="G563" s="2" t="n"/>
       <c r="H563" s="2" t="n"/>
-      <c r="I563" s="2" t="n"/>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>Inverno26</t>
+        </is>
+      </c>
       <c r="J563" s="2" t="n"/>
       <c r="K563" s="2" t="n"/>
       <c r="L563" t="n">
